--- a/Results/Phase 2/Hydrogen/hydrogen land use results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen land use results.xlsx
@@ -886,7 +886,7 @@
         <v>1.984986328816547</v>
       </c>
       <c r="N5" t="n">
-        <v>50.59692422880062</v>
+        <v>1.984986328816822</v>
       </c>
       <c r="O5" t="n">
         <v>1.984986328816822</v>
@@ -974,7 +974,7 @@
         <v>15.46449644101976</v>
       </c>
       <c r="N6" t="n">
-        <v>50.59692422880062</v>
+        <v>4.024512008631472</v>
       </c>
       <c r="O6" t="n">
         <v>4.024514548134619</v>
@@ -1062,7 +1062,7 @@
         <v>5.665542200565885</v>
       </c>
       <c r="N7" t="n">
-        <v>50.59692422880062</v>
+        <v>5.665542200565885</v>
       </c>
       <c r="O7" t="n">
         <v>5.665538824962428</v>
@@ -1150,7 +1150,7 @@
         <v>24.58643715326048</v>
       </c>
       <c r="N8" t="n">
-        <v>50.59692422880062</v>
+        <v>17.62454380419087</v>
       </c>
       <c r="O8" t="n">
         <v>19.53773254378651</v>
@@ -1238,7 +1238,7 @@
         <v>656.7241814569575</v>
       </c>
       <c r="N9" t="n">
-        <v>50.59692422880062</v>
+        <v>656.7241814569575</v>
       </c>
       <c r="O9" t="n">
         <v>703.7679833006256</v>
@@ -1922,7 +1922,7 @@
         <v>5.972154834159656</v>
       </c>
       <c r="N5" t="n">
-        <v>77.0257709140057</v>
+        <v>5.972154834159385</v>
       </c>
       <c r="O5" t="n">
         <v>5.972154834159385</v>
@@ -2010,7 +2010,7 @@
         <v>9.907768940036732</v>
       </c>
       <c r="N6" t="n">
-        <v>77.0257709140057</v>
+        <v>9.973868501105203</v>
       </c>
       <c r="O6" t="n">
         <v>23.4305690115769</v>
@@ -2098,7 +2098,7 @@
         <v>10.59848534818271</v>
       </c>
       <c r="N7" t="n">
-        <v>77.0257709140057</v>
+        <v>10.59848534818271</v>
       </c>
       <c r="O7" t="n">
         <v>10.59848063023918</v>
@@ -2186,7 +2186,7 @@
         <v>33.08930857350703</v>
       </c>
       <c r="N8" t="n">
-        <v>77.0257709140057</v>
+        <v>24.03451427023067</v>
       </c>
       <c r="O8" t="n">
         <v>26.52285034466054</v>
@@ -2274,7 +2274,7 @@
         <v>577.822861525118</v>
       </c>
       <c r="N9" t="n">
-        <v>77.0257709140057</v>
+        <v>577.822861525118</v>
       </c>
       <c r="O9" t="n">
         <v>619.0904195483747</v>
@@ -2958,7 +2958,7 @@
         <v>2.950901508340083</v>
       </c>
       <c r="N5" t="n">
-        <v>48.53543799241535</v>
+        <v>2.950901508340081</v>
       </c>
       <c r="O5" t="n">
         <v>2.95090150834008</v>
@@ -3046,7 +3046,7 @@
         <v>16.67429622928691</v>
       </c>
       <c r="N6" t="n">
-        <v>48.53543799241535</v>
+        <v>5.266879401936952</v>
       </c>
       <c r="O6" t="n">
         <v>5.153191991252442</v>
@@ -3134,7 +3134,7 @@
         <v>6.914179584575722</v>
       </c>
       <c r="N7" t="n">
-        <v>48.53543799241535</v>
+        <v>6.914179584575722</v>
       </c>
       <c r="O7" t="n">
         <v>6.914258130200103</v>
@@ -3222,7 +3222,7 @@
         <v>26.59011760444909</v>
       </c>
       <c r="N8" t="n">
-        <v>48.53543799241535</v>
+        <v>19.09692909949671</v>
       </c>
       <c r="O8" t="n">
         <v>21.15612235586578</v>
@@ -3310,7 +3310,7 @@
         <v>616.3325975915187</v>
       </c>
       <c r="N9" t="n">
-        <v>48.53543799241535</v>
+        <v>616.3325975915187</v>
       </c>
       <c r="O9" t="n">
         <v>660.4592951358111</v>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.025528041277674</v>
+        <v>8.025528041276885</v>
       </c>
       <c r="C2" t="n">
-        <v>8.047296473428151</v>
+        <v>8.047296473427874</v>
       </c>
       <c r="D2" t="n">
-        <v>8.115566909336456</v>
+        <v>8.115566909336248</v>
       </c>
       <c r="E2" t="n">
-        <v>7.932271134523748</v>
+        <v>7.93227113452368</v>
       </c>
       <c r="F2" t="n">
-        <v>8.008585086103537</v>
+        <v>8.008585086103178</v>
       </c>
       <c r="G2" t="n">
-        <v>8.427877065713634</v>
+        <v>8.427877065713355</v>
       </c>
       <c r="H2" t="n">
-        <v>7.937848804071938</v>
+        <v>7.93784880407157</v>
       </c>
       <c r="I2" t="n">
-        <v>8.5486619095661</v>
+        <v>8.548661909565713</v>
       </c>
       <c r="J2" t="n">
-        <v>8.193818169689463</v>
+        <v>8.193818169688967</v>
       </c>
       <c r="K2" t="n">
-        <v>8.172685822404159</v>
+        <v>8.172685822403865</v>
       </c>
       <c r="L2" t="n">
-        <v>7.965126045633826</v>
+        <v>7.965126045633673</v>
       </c>
       <c r="M2" t="n">
-        <v>8.369901948337604</v>
+        <v>8.369901948336794</v>
       </c>
       <c r="N2" t="n">
-        <v>8.081636768041935</v>
+        <v>8.081636768041845</v>
       </c>
       <c r="O2" t="n">
-        <v>8.102507726951712</v>
+        <v>8.102507726950877</v>
       </c>
       <c r="P2" t="n">
-        <v>8.153773798006416</v>
+        <v>8.153773798006211</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.359480805644774</v>
+        <v>8.359480805644713</v>
       </c>
       <c r="R2" t="n">
-        <v>7.970700540865854</v>
+        <v>7.970700540865551</v>
       </c>
       <c r="S2" t="n">
-        <v>8.179173875644267</v>
+        <v>8.179173875643572</v>
       </c>
       <c r="T2" t="n">
-        <v>8.016649997882613</v>
+        <v>8.01664999788165</v>
       </c>
       <c r="U2" t="n">
-        <v>8.068615896530336</v>
+        <v>8.068615896529977</v>
       </c>
       <c r="V2" t="n">
-        <v>6.524982446529719</v>
+        <v>6.524982446529746</v>
       </c>
       <c r="W2" t="n">
-        <v>8.098716112559924</v>
+        <v>8.098716112559522</v>
       </c>
       <c r="X2" t="n">
-        <v>8.101347601858057</v>
+        <v>8.101347601857817</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.256411226959305</v>
+        <v>8.256411226959083</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.13931703559971</v>
+        <v>8.139317035599381</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.06104308010365</v>
+        <v>8.061043080103451</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.369389624269512</v>
+        <v>8.369389624269521</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="C3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="D3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="E3" t="n">
-        <v>7.945173018811538</v>
+        <v>7.945173018811315</v>
       </c>
       <c r="F3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="G3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="H3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="I3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="J3" t="n">
-        <v>7.931308757570012</v>
+        <v>7.931308757569832</v>
       </c>
       <c r="K3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="L3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="M3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="N3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="O3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="P3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="R3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="S3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="T3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="U3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="V3" t="n">
-        <v>6.372910391765437</v>
+        <v>6.372910391765441</v>
       </c>
       <c r="W3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="X3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.975434789003002</v>
+        <v>7.975434789002846</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.84557543083137</v>
+        <v>36.84557543083136</v>
       </c>
       <c r="C4" t="n">
-        <v>44.14154525449364</v>
+        <v>44.14154525449234</v>
       </c>
       <c r="D4" t="n">
-        <v>63.87188544855585</v>
+        <v>63.87188544855493</v>
       </c>
       <c r="E4" t="n">
-        <v>23.99231929030617</v>
+        <v>23.99231929030554</v>
       </c>
       <c r="F4" t="n">
-        <v>35.84731509793795</v>
+        <v>35.84731509793659</v>
       </c>
       <c r="G4" t="n">
-        <v>131.3397619637778</v>
+        <v>131.3397619637859</v>
       </c>
       <c r="H4" t="n">
-        <v>17.83459172383497</v>
+        <v>17.83459172383539</v>
       </c>
       <c r="I4" t="n">
-        <v>180.406815782491</v>
+        <v>180.4068157824899</v>
       </c>
       <c r="J4" t="n">
-        <v>89.36035065848334</v>
+        <v>89.36035065848486</v>
       </c>
       <c r="K4" t="n">
-        <v>71.88755195808277</v>
+        <v>71.8875519580817</v>
       </c>
       <c r="L4" t="n">
-        <v>23.34150168191663</v>
+        <v>23.34150168191559</v>
       </c>
       <c r="M4" t="n">
-        <v>132.7354246302798</v>
+        <v>132.7354246302784</v>
       </c>
       <c r="N4" t="n">
-        <v>54.01763996605626</v>
+        <v>54.01763996605456</v>
       </c>
       <c r="O4" t="n">
-        <v>52.96300561597567</v>
+        <v>52.96300561597482</v>
       </c>
       <c r="P4" t="n">
-        <v>66.80116544601108</v>
+        <v>66.80116544601009</v>
       </c>
       <c r="Q4" t="n">
-        <v>123.2568912861694</v>
+        <v>123.2568912861684</v>
       </c>
       <c r="R4" t="n">
-        <v>26.42797595150371</v>
+        <v>26.42797595150329</v>
       </c>
       <c r="S4" t="n">
-        <v>73.41056090064474</v>
+        <v>73.41056090064357</v>
       </c>
       <c r="T4" t="n">
-        <v>38.16111081804748</v>
+        <v>38.16111081804706</v>
       </c>
       <c r="U4" t="n">
-        <v>48.25760148065358</v>
+        <v>48.2576014806561</v>
       </c>
       <c r="V4" t="n">
-        <v>53.46263739986055</v>
+        <v>53.46263739986107</v>
       </c>
       <c r="W4" t="n">
-        <v>57.4390367701657</v>
+        <v>57.43903677016486</v>
       </c>
       <c r="X4" t="n">
-        <v>59.40618762949227</v>
+        <v>59.40618762949214</v>
       </c>
       <c r="Y4" t="n">
-        <v>96.74519973975671</v>
+        <v>96.74519973975555</v>
       </c>
       <c r="Z4" t="n">
-        <v>61.13113187539816</v>
+        <v>61.13113187539709</v>
       </c>
       <c r="AA4" t="n">
-        <v>47.95490249397536</v>
+        <v>47.95490249397469</v>
       </c>
       <c r="AB4" t="n">
-        <v>138.4934097780565</v>
+        <v>138.4934097780554</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.437817583692073</v>
+        <v>4.437817583691982</v>
       </c>
       <c r="C5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="D5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="E5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="F5" t="n">
-        <v>4.437817583692151</v>
+        <v>4.437817583691853</v>
       </c>
       <c r="G5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="H5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="I5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="J5" t="n">
-        <v>4.431864064052284</v>
+        <v>4.431864064051478</v>
       </c>
       <c r="K5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="L5" t="n">
-        <v>4.437817583692215</v>
+        <v>4.437817583691489</v>
       </c>
       <c r="M5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="N5" t="n">
-        <v>54.01763996605624</v>
+        <v>4.437817583691852</v>
       </c>
       <c r="O5" t="n">
-        <v>4.437817583692151</v>
+        <v>4.437817583691852</v>
       </c>
       <c r="P5" t="n">
-        <v>4.437817583692152</v>
+        <v>4.437817583691853</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.437817583692151</v>
+        <v>4.437817583691852</v>
       </c>
       <c r="R5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="S5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="T5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="U5" t="n">
-        <v>3.718240677179708</v>
+        <v>3.718240677178946</v>
       </c>
       <c r="V5" t="n">
-        <v>4.402242990799708</v>
+        <v>4.402242990799864</v>
       </c>
       <c r="W5" t="n">
-        <v>4.437817583692151</v>
+        <v>4.437817583691852</v>
       </c>
       <c r="X5" t="n">
-        <v>4.437817583692073</v>
+        <v>4.437817583691981</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.718240677179708</v>
+        <v>3.718240677178945</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.43781758369219</v>
+        <v>4.437817583691364</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.437817583692151</v>
+        <v>4.437817583691852</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.98138035619681</v>
+        <v>18.98138035619447</v>
       </c>
       <c r="C6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="D6" t="n">
-        <v>18.9813803561968</v>
+        <v>18.98138035619449</v>
       </c>
       <c r="E6" t="n">
-        <v>18.9813803561968</v>
+        <v>18.98138035619449</v>
       </c>
       <c r="F6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="G6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="H6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="I6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="J6" t="n">
-        <v>18.97542683655645</v>
+        <v>18.97542683655519</v>
       </c>
       <c r="K6" t="n">
-        <v>18.9813803561968</v>
+        <v>18.98138035619449</v>
       </c>
       <c r="L6" t="n">
-        <v>18.98138035619681</v>
+        <v>18.98138035619447</v>
       </c>
       <c r="M6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="N6" t="n">
-        <v>54.01763996605626</v>
+        <v>7.162753732596817</v>
       </c>
       <c r="O6" t="n">
-        <v>19.60743958794192</v>
+        <v>19.60743958794159</v>
       </c>
       <c r="P6" t="n">
-        <v>19.64774736548283</v>
+        <v>19.64774736548195</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.9813803561968</v>
+        <v>18.98138035619449</v>
       </c>
       <c r="R6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="S6" t="n">
-        <v>18.9813803561968</v>
+        <v>18.98138035619449</v>
       </c>
       <c r="T6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="U6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="V6" t="n">
-        <v>18.94580576330381</v>
+        <v>18.94580576330366</v>
       </c>
       <c r="W6" t="n">
-        <v>19.59562143013311</v>
+        <v>19.59562143013261</v>
       </c>
       <c r="X6" t="n">
-        <v>7.067407958656249</v>
+        <v>7.067407958655185</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.194194820932157</v>
+        <v>7.194194820931068</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.9813803561968</v>
+        <v>18.98138035619449</v>
       </c>
       <c r="AA6" t="n">
-        <v>18.9813803561968</v>
+        <v>18.98138035619449</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.034175800649311</v>
+        <v>7.034175800648751</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.604942125573569</v>
+        <v>8.604942125573157</v>
       </c>
       <c r="C7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="D7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="E7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="F7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="G7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="H7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="I7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="J7" t="n">
-        <v>8.598988605934682</v>
+        <v>8.598988605933487</v>
       </c>
       <c r="K7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="L7" t="n">
-        <v>8.604942125573569</v>
+        <v>8.604942125573157</v>
       </c>
       <c r="M7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="N7" t="n">
-        <v>54.01763996605626</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="O7" t="n">
-        <v>8.604949475048812</v>
+        <v>8.604949475047942</v>
       </c>
       <c r="P7" t="n">
-        <v>8.604949475048812</v>
+        <v>8.604949475047942</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="R7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="S7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="T7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="U7" t="n">
-        <v>8.509467041402253</v>
+        <v>8.509467041402194</v>
       </c>
       <c r="V7" t="n">
-        <v>8.569367532681765</v>
+        <v>8.569367532681788</v>
       </c>
       <c r="W7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="X7" t="n">
-        <v>8.604942125573569</v>
+        <v>8.604942125573157</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.604942125573551</v>
+        <v>8.604942125573048</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.5946929083087</v>
+        <v>18.59469290830915</v>
       </c>
       <c r="C8" t="n">
-        <v>28.90103638389079</v>
+        <v>28.90103638388939</v>
       </c>
       <c r="D8" t="n">
-        <v>28.90103638389079</v>
+        <v>28.90103638388939</v>
       </c>
       <c r="E8" t="n">
-        <v>23.41321250729001</v>
+        <v>23.41321250728937</v>
       </c>
       <c r="F8" t="n">
-        <v>20.20030076600579</v>
+        <v>20.20030076600521</v>
       </c>
       <c r="G8" t="n">
-        <v>31.03812384144431</v>
+        <v>31.03812384144348</v>
       </c>
       <c r="H8" t="n">
-        <v>28.90103638389079</v>
+        <v>28.90103638388939</v>
       </c>
       <c r="I8" t="n">
-        <v>28.90103638389079</v>
+        <v>28.90103638388939</v>
       </c>
       <c r="J8" t="n">
-        <v>28.89508286424964</v>
+        <v>28.89508286425025</v>
       </c>
       <c r="K8" t="n">
-        <v>28.90103638389079</v>
+        <v>28.90103638388939</v>
       </c>
       <c r="L8" t="n">
-        <v>28.90103638389099</v>
+        <v>28.90103638388928</v>
       </c>
       <c r="M8" t="n">
-        <v>28.90103638376194</v>
+        <v>28.9010363837608</v>
       </c>
       <c r="N8" t="n">
-        <v>54.01763996605626</v>
+        <v>20.91189596997703</v>
       </c>
       <c r="O8" t="n">
-        <v>23.10738111001133</v>
+        <v>23.10738111000945</v>
       </c>
       <c r="P8" t="n">
-        <v>22.5692146534814</v>
+        <v>22.5692146534801</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.569261192278</v>
+        <v>16.56926119227775</v>
       </c>
       <c r="R8" t="n">
-        <v>28.90103638389079</v>
+        <v>28.90103638388939</v>
       </c>
       <c r="S8" t="n">
-        <v>28.90103638389079</v>
+        <v>28.90103638388939</v>
       </c>
       <c r="T8" t="n">
-        <v>28.90103638389079</v>
+        <v>28.90103638388939</v>
       </c>
       <c r="U8" t="n">
-        <v>23.79665113239612</v>
+        <v>23.7966511323972</v>
       </c>
       <c r="V8" t="n">
-        <v>25.96696668192149</v>
+        <v>25.96696668192191</v>
       </c>
       <c r="W8" t="n">
-        <v>28.90306184844508</v>
+        <v>28.90306184844425</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5138580340233</v>
+        <v>17.5138580340225</v>
       </c>
       <c r="Y8" t="n">
-        <v>39.02181255134454</v>
+        <v>39.0218125513438</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.40324728953572</v>
+        <v>18.40324728953631</v>
       </c>
       <c r="AA8" t="n">
-        <v>28.90103638389079</v>
+        <v>28.90103638388939</v>
       </c>
       <c r="AB8" t="n">
-        <v>39.66687392054405</v>
+        <v>39.66687392054284</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>452.0252571679476</v>
+        <v>452.0252571679467</v>
       </c>
       <c r="C9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="D9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="E9" t="n">
-        <v>547.6783193786305</v>
+        <v>547.6783193786298</v>
       </c>
       <c r="F9" t="n">
-        <v>289.7102671631993</v>
+        <v>289.7102671631987</v>
       </c>
       <c r="G9" t="n">
-        <v>576.3785527774564</v>
+        <v>576.3785527774554</v>
       </c>
       <c r="H9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="I9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="J9" t="n">
-        <v>576.3725963769258</v>
+        <v>576.3725963769252</v>
       </c>
       <c r="K9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="L9" t="n">
-        <v>576.3785498965657</v>
+        <v>576.3785498965649</v>
       </c>
       <c r="M9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="N9" t="n">
-        <v>54.01763996605626</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="O9" t="n">
-        <v>617.5890721156592</v>
+        <v>617.5890721156587</v>
       </c>
       <c r="P9" t="n">
-        <v>626.5516530183049</v>
+        <v>626.5516530183041</v>
       </c>
       <c r="Q9" t="n">
-        <v>576.3785527774564</v>
+        <v>576.3785527774554</v>
       </c>
       <c r="R9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="S9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="T9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="U9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="V9" t="n">
-        <v>719.8440395971071</v>
+        <v>719.8440395971073</v>
       </c>
       <c r="W9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="X9" t="n">
-        <v>576.3785498965657</v>
+        <v>576.3785498965649</v>
       </c>
       <c r="Y9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="Z9" t="n">
-        <v>501.4045734514081</v>
+        <v>501.4045734514071</v>
       </c>
       <c r="AA9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
       <c r="AB9" t="n">
-        <v>576.3785498965655</v>
+        <v>576.3785498965646</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.195434199286804</v>
+        <v>7.195434199286407</v>
       </c>
       <c r="C10" t="n">
-        <v>7.078996008489211</v>
+        <v>7.078996008489192</v>
       </c>
       <c r="D10" t="n">
-        <v>6.680145227323313</v>
+        <v>6.680145227322998</v>
       </c>
       <c r="E10" t="n">
-        <v>7.534100346828145</v>
+        <v>7.53410034682776</v>
       </c>
       <c r="F10" t="n">
-        <v>7.310090283444693</v>
+        <v>7.310090283444723</v>
       </c>
       <c r="G10" t="n">
-        <v>4.803558452430328</v>
+        <v>4.803558452429835</v>
       </c>
       <c r="H10" t="n">
-        <v>7.722896304484163</v>
+        <v>7.722896304484072</v>
       </c>
       <c r="I10" t="n">
-        <v>4.150463397963241</v>
+        <v>4.150463397962832</v>
       </c>
       <c r="J10" t="n">
-        <v>5.899143203224115</v>
+        <v>5.899143203224283</v>
       </c>
       <c r="K10" t="n">
-        <v>6.343249763651993</v>
+        <v>6.343249763651832</v>
       </c>
       <c r="L10" t="n">
-        <v>7.557457167143538</v>
+        <v>7.557457167143383</v>
       </c>
       <c r="M10" t="n">
-        <v>5.200963748329768</v>
+        <v>5.200963748329743</v>
       </c>
       <c r="N10" t="n">
-        <v>6.874225493889967</v>
+        <v>6.874225493889613</v>
       </c>
       <c r="O10" t="n">
-        <v>6.736113166516187</v>
+        <v>6.736113166515617</v>
       </c>
       <c r="P10" t="n">
-        <v>6.429412676820094</v>
+        <v>6.429412676819818</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.244429472241174</v>
+        <v>5.244429472240974</v>
       </c>
       <c r="R10" t="n">
-        <v>7.530490926851625</v>
+        <v>7.530490926851244</v>
       </c>
       <c r="S10" t="n">
-        <v>6.286619122795632</v>
+        <v>6.286619122795376</v>
       </c>
       <c r="T10" t="n">
-        <v>7.260013038398688</v>
+        <v>7.260013038398052</v>
       </c>
       <c r="U10" t="n">
-        <v>6.944607339690364</v>
+        <v>6.944607339690515</v>
       </c>
       <c r="V10" t="n">
-        <v>5.123843725337252</v>
+        <v>5.123843725337244</v>
       </c>
       <c r="W10" t="n">
-        <v>6.769719921492657</v>
+        <v>6.769719921492877</v>
       </c>
       <c r="X10" t="n">
-        <v>6.762262133116322</v>
+        <v>6.762262133116348</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.842467886181828</v>
+        <v>5.842467886181606</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.520105309106362</v>
+        <v>6.520105309106291</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.992870750413688</v>
+        <v>6.992870750413638</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.194004580620579</v>
+        <v>5.194004580620312</v>
       </c>
     </row>
     <row r="11">
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7.670625287242384</v>
+        <v>7.670625287242056</v>
       </c>
       <c r="C11" t="n">
-        <v>7.639413971513344</v>
+        <v>7.639413971513017</v>
       </c>
       <c r="D11" t="n">
-        <v>7.526206030929369</v>
+        <v>7.526206030929094</v>
       </c>
       <c r="E11" t="n">
-        <v>7.745231758760442</v>
+        <v>7.745231758760249</v>
       </c>
       <c r="F11" t="n">
-        <v>7.705851215747278</v>
+        <v>7.705851215746701</v>
       </c>
       <c r="G11" t="n">
-        <v>6.984663224402811</v>
+        <v>6.984663224402542</v>
       </c>
       <c r="H11" t="n">
-        <v>7.822942988823455</v>
+        <v>7.822942988823203</v>
       </c>
       <c r="I11" t="n">
-        <v>6.808287737182415</v>
+        <v>6.808287737181898</v>
       </c>
       <c r="J11" t="n">
-        <v>7.269176366334715</v>
+        <v>7.269176366334613</v>
       </c>
       <c r="K11" t="n">
-        <v>7.430036434404451</v>
+        <v>7.430036434403903</v>
       </c>
       <c r="L11" t="n">
-        <v>7.774944895672081</v>
+        <v>7.774944895671978</v>
       </c>
       <c r="M11" t="n">
-        <v>7.107508783116728</v>
+        <v>7.107508783115857</v>
       </c>
       <c r="N11" t="n">
-        <v>7.580583029419475</v>
+        <v>7.580583029419413</v>
       </c>
       <c r="O11" t="n">
-        <v>7.538612439236191</v>
+        <v>7.538612439236033</v>
       </c>
       <c r="P11" t="n">
-        <v>7.450328810083108</v>
+        <v>7.450328810082265</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.116864683320636</v>
+        <v>7.116864683320705</v>
       </c>
       <c r="R11" t="n">
-        <v>7.768249665634648</v>
+        <v>7.768249665634278</v>
       </c>
       <c r="S11" t="n">
-        <v>7.41075736558371</v>
+        <v>7.410757365583357</v>
       </c>
       <c r="T11" t="n">
-        <v>7.691130821443209</v>
+        <v>7.691130821442667</v>
       </c>
       <c r="U11" t="n">
-        <v>7.599586122040845</v>
+        <v>7.599586122040709</v>
       </c>
       <c r="V11" t="n">
-        <v>5.956653132765616</v>
+        <v>5.95665313276563</v>
       </c>
       <c r="W11" t="n">
-        <v>7.550112005457383</v>
+        <v>7.550112005456689</v>
       </c>
       <c r="X11" t="n">
-        <v>7.549350177277653</v>
+        <v>7.549350177277555</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.28590448881347</v>
+        <v>7.285904488812649</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.477137484386831</v>
+        <v>7.477137484386554</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.613973311299723</v>
+        <v>7.613973311299395</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.103830015563398</v>
+        <v>7.103830015563109</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.131191443701669</v>
+        <v>9.131191443702203</v>
       </c>
       <c r="C2" t="n">
-        <v>9.056237995155753</v>
+        <v>9.056237995155419</v>
       </c>
       <c r="D2" t="n">
-        <v>9.177436237369481</v>
+        <v>9.177436237370044</v>
       </c>
       <c r="E2" t="n">
-        <v>8.250407001978434</v>
+        <v>8.250407001978699</v>
       </c>
       <c r="F2" t="n">
-        <v>9.199079647240335</v>
+        <v>9.199079647239987</v>
       </c>
       <c r="G2" t="n">
-        <v>9.499317307768441</v>
+        <v>9.499317307768996</v>
       </c>
       <c r="H2" t="n">
-        <v>9.045472429954039</v>
+        <v>9.045472429953694</v>
       </c>
       <c r="I2" t="n">
-        <v>9.444150223668862</v>
+        <v>9.444150223669125</v>
       </c>
       <c r="J2" t="n">
-        <v>9.285725061809272</v>
+        <v>9.285725061809336</v>
       </c>
       <c r="K2" t="n">
-        <v>9.288372019996498</v>
+        <v>9.28837201999692</v>
       </c>
       <c r="L2" t="n">
-        <v>9.112439845886248</v>
+        <v>9.112439845886357</v>
       </c>
       <c r="M2" t="n">
-        <v>9.427262727620114</v>
+        <v>9.427262727619929</v>
       </c>
       <c r="N2" t="n">
-        <v>9.168379027245013</v>
+        <v>9.168379027245347</v>
       </c>
       <c r="O2" t="n">
-        <v>9.180052621661241</v>
+        <v>9.180052621660932</v>
       </c>
       <c r="P2" t="n">
-        <v>9.257293681078711</v>
+        <v>9.257293681078409</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.303330925910434</v>
+        <v>9.303330925910114</v>
       </c>
       <c r="R2" t="n">
-        <v>9.302592921469587</v>
+        <v>9.302592921469605</v>
       </c>
       <c r="S2" t="n">
-        <v>9.299819829477784</v>
+        <v>9.299819829478167</v>
       </c>
       <c r="T2" t="n">
-        <v>9.21915528172336</v>
+        <v>9.219155281723101</v>
       </c>
       <c r="U2" t="n">
-        <v>9.134264343686528</v>
+        <v>9.134264343686851</v>
       </c>
       <c r="V2" t="n">
-        <v>7.759865934246683</v>
+        <v>7.759865934246593</v>
       </c>
       <c r="W2" t="n">
-        <v>9.213706403433491</v>
+        <v>9.213706403433548</v>
       </c>
       <c r="X2" t="n">
-        <v>9.255748212054584</v>
+        <v>9.255748212054295</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.560123737214033</v>
+        <v>9.560123737213607</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.248933740593214</v>
+        <v>9.248933740592982</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.185272084053933</v>
+        <v>9.185272084054194</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.461993986536331</v>
+        <v>9.461993986536582</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="C3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="D3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="E3" t="n">
-        <v>8.336948150657655</v>
+        <v>8.336948150657971</v>
       </c>
       <c r="F3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="G3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="H3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="I3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="J3" t="n">
-        <v>9.033867370202135</v>
+        <v>9.033867370202547</v>
       </c>
       <c r="K3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="L3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="M3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="N3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="O3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="P3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="R3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="S3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="T3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="U3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="V3" t="n">
-        <v>7.582206343624591</v>
+        <v>7.58220634362432</v>
       </c>
       <c r="W3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="X3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.075011390902631</v>
+        <v>9.075011390902983</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.11788027941636</v>
+        <v>40.117880279419</v>
       </c>
       <c r="C4" t="n">
-        <v>24.63525464676201</v>
+        <v>24.63525464676257</v>
       </c>
       <c r="D4" t="n">
-        <v>55.23240350989401</v>
+        <v>55.23240350992393</v>
       </c>
       <c r="E4" t="n">
-        <v>6.338492162269787</v>
+        <v>6.338492162272324</v>
       </c>
       <c r="F4" t="n">
-        <v>61.89945438497469</v>
+        <v>61.89945438496964</v>
       </c>
       <c r="G4" t="n">
-        <v>123.4450357921954</v>
+        <v>123.4450357921916</v>
       </c>
       <c r="H4" t="n">
-        <v>23.03686218938237</v>
+        <v>23.03686218938441</v>
       </c>
       <c r="I4" t="n">
-        <v>126.6912512394624</v>
+        <v>126.6912512394627</v>
       </c>
       <c r="J4" t="n">
-        <v>87.81545013257013</v>
+        <v>87.81545013256182</v>
       </c>
       <c r="K4" t="n">
-        <v>78.36822393293869</v>
+        <v>78.36822393293512</v>
       </c>
       <c r="L4" t="n">
-        <v>37.3165107622057</v>
+        <v>37.31651076220695</v>
       </c>
       <c r="M4" t="n">
-        <v>119.7205019899609</v>
+        <v>119.7205019899533</v>
       </c>
       <c r="N4" t="n">
-        <v>53.65175804660122</v>
+        <v>53.65175804660348</v>
       </c>
       <c r="O4" t="n">
-        <v>50.66137363678272</v>
+        <v>50.66137363678632</v>
       </c>
       <c r="P4" t="n">
-        <v>68.42857299448164</v>
+        <v>68.42857299447262</v>
       </c>
       <c r="Q4" t="n">
-        <v>84.79632875789534</v>
+        <v>84.79632875789615</v>
       </c>
       <c r="R4" t="n">
-        <v>92.42256712792039</v>
+        <v>92.42256712792224</v>
       </c>
       <c r="S4" t="n">
-        <v>80.09745037726883</v>
+        <v>80.09745037728143</v>
       </c>
       <c r="T4" t="n">
-        <v>68.41746179448997</v>
+        <v>68.41746179449179</v>
       </c>
       <c r="U4" t="n">
-        <v>41.85688821100337</v>
+        <v>41.8568882109998</v>
       </c>
       <c r="V4" t="n">
-        <v>61.63913585430625</v>
+        <v>61.6391358543006</v>
       </c>
       <c r="W4" t="n">
-        <v>64.21390454042087</v>
+        <v>64.21390454042252</v>
       </c>
       <c r="X4" t="n">
-        <v>74.44736303269849</v>
+        <v>74.44736303269427</v>
       </c>
       <c r="Y4" t="n">
-        <v>153.5892814360035</v>
+        <v>153.5892814359847</v>
       </c>
       <c r="Z4" t="n">
-        <v>63.00235515667914</v>
+        <v>63.00235515668151</v>
       </c>
       <c r="AA4" t="n">
-        <v>57.22268475286766</v>
+        <v>57.22268475286858</v>
       </c>
       <c r="AB4" t="n">
-        <v>137.6490759173861</v>
+        <v>137.6490759173854</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.557031797125767</v>
+        <v>5.557031797128067</v>
       </c>
       <c r="C5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="D5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="E5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="F5" t="n">
-        <v>5.557031797125441</v>
+        <v>5.557031797126111</v>
       </c>
       <c r="G5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="H5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="I5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="J5" t="n">
-        <v>5.550528693891013</v>
+        <v>5.550528693891954</v>
       </c>
       <c r="K5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="L5" t="n">
-        <v>5.557031797125821</v>
+        <v>5.557031797128325</v>
       </c>
       <c r="M5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="N5" t="n">
-        <v>53.65175804660122</v>
+        <v>5.557031797126111</v>
       </c>
       <c r="O5" t="n">
-        <v>5.557031797125441</v>
+        <v>5.557031797126111</v>
       </c>
       <c r="P5" t="n">
-        <v>5.557031797125441</v>
+        <v>5.557031797126111</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.557031797125441</v>
+        <v>5.557031797126111</v>
       </c>
       <c r="R5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="S5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="T5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="U5" t="n">
-        <v>5.274494261903135</v>
+        <v>5.274494261905272</v>
       </c>
       <c r="V5" t="n">
-        <v>5.517636740665754</v>
+        <v>5.517636740665815</v>
       </c>
       <c r="W5" t="n">
-        <v>5.55703179712544</v>
+        <v>5.557031797126111</v>
       </c>
       <c r="X5" t="n">
-        <v>5.557031797125776</v>
+        <v>5.55703179712613</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.274494261903135</v>
+        <v>5.274494261905272</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.557031797125624</v>
+        <v>5.557031797128179</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.557031797125441</v>
+        <v>5.557031797126111</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="C6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="D6" t="n">
-        <v>21.2045761083734</v>
+        <v>21.20457610837626</v>
       </c>
       <c r="E6" t="n">
-        <v>21.2045761083734</v>
+        <v>21.20457610837626</v>
       </c>
       <c r="F6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="G6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="H6" t="n">
-        <v>21.2045761083734</v>
+        <v>21.20457610837626</v>
       </c>
       <c r="I6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="J6" t="n">
-        <v>21.19807300513898</v>
+        <v>21.19807300513914</v>
       </c>
       <c r="K6" t="n">
-        <v>21.2045761083734</v>
+        <v>21.20457610837626</v>
       </c>
       <c r="L6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="M6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="N6" t="n">
-        <v>53.65175804660122</v>
+        <v>8.664102004565127</v>
       </c>
       <c r="O6" t="n">
-        <v>8.574062375888603</v>
+        <v>8.574062375889975</v>
       </c>
       <c r="P6" t="n">
-        <v>21.82685239096901</v>
+        <v>21.82685239097104</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.2045761083734</v>
+        <v>21.20457610837626</v>
       </c>
       <c r="R6" t="n">
-        <v>21.2045761083734</v>
+        <v>21.20457610837626</v>
       </c>
       <c r="S6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="T6" t="n">
-        <v>21.2045761083734</v>
+        <v>21.20457610837626</v>
       </c>
       <c r="U6" t="n">
-        <v>21.2045761083734</v>
+        <v>21.20457610837626</v>
       </c>
       <c r="V6" t="n">
-        <v>8.565660600521586</v>
+        <v>8.565660600521019</v>
       </c>
       <c r="W6" t="n">
-        <v>8.810623447362067</v>
+        <v>8.810623447362747</v>
       </c>
       <c r="X6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.765400241971189</v>
+        <v>8.765400241971868</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.605055656982014</v>
+        <v>8.605055656982818</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2045761083734</v>
+        <v>21.20457610837626</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.557868436660121</v>
+        <v>8.557868436662545</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.08049977432995</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="C7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="D7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="E7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="F7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="G7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="H7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="I7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="J7" t="n">
-        <v>10.07399667109511</v>
+        <v>10.07399667109579</v>
       </c>
       <c r="K7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="L7" t="n">
-        <v>10.08049977432995</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="M7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="N7" t="n">
-        <v>53.65175804660122</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="O7" t="n">
-        <v>10.08041707573276</v>
+        <v>10.08041707573461</v>
       </c>
       <c r="P7" t="n">
-        <v>10.08041707573276</v>
+        <v>10.08041707573461</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="R7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="S7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="T7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="U7" t="n">
-        <v>10.11210097378667</v>
+        <v>10.11210097378752</v>
       </c>
       <c r="V7" t="n">
-        <v>10.04110471786984</v>
+        <v>10.04110471786932</v>
       </c>
       <c r="W7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="X7" t="n">
-        <v>10.08049977432995</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.08049977432961</v>
+        <v>10.0804997743319</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20.45536562373145</v>
+        <v>20.45536562373211</v>
       </c>
       <c r="C8" t="n">
-        <v>31.55973124565374</v>
+        <v>31.55973124565509</v>
       </c>
       <c r="D8" t="n">
-        <v>31.55973124565374</v>
+        <v>31.55973124565509</v>
       </c>
       <c r="E8" t="n">
-        <v>25.64698411797944</v>
+        <v>25.64698411798083</v>
       </c>
       <c r="F8" t="n">
-        <v>22.18529600426964</v>
+        <v>22.18529600426995</v>
       </c>
       <c r="G8" t="n">
-        <v>33.86229379323125</v>
+        <v>33.86229379323158</v>
       </c>
       <c r="H8" t="n">
-        <v>31.55973124565374</v>
+        <v>31.55973124565509</v>
       </c>
       <c r="I8" t="n">
-        <v>31.55973124565374</v>
+        <v>31.55973124565509</v>
       </c>
       <c r="J8" t="n">
-        <v>31.55322814241967</v>
+        <v>31.55322814241955</v>
       </c>
       <c r="K8" t="n">
-        <v>31.55973124565374</v>
+        <v>31.55973124565509</v>
       </c>
       <c r="L8" t="n">
-        <v>31.55973124565392</v>
+        <v>31.55973124565504</v>
       </c>
       <c r="M8" t="n">
-        <v>31.55973124551928</v>
+        <v>31.55973124552066</v>
       </c>
       <c r="N8" t="n">
-        <v>53.65175804660122</v>
+        <v>22.95199016005724</v>
       </c>
       <c r="O8" t="n">
-        <v>25.31747213164067</v>
+        <v>25.31747213164191</v>
       </c>
       <c r="P8" t="n">
-        <v>24.73763534448756</v>
+        <v>24.73763534448944</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.27310434434334</v>
+        <v>18.27310434434507</v>
       </c>
       <c r="R8" t="n">
-        <v>31.55973124565374</v>
+        <v>31.55973124565509</v>
       </c>
       <c r="S8" t="n">
-        <v>31.55973124565374</v>
+        <v>31.55973124565509</v>
       </c>
       <c r="T8" t="n">
-        <v>31.55973124565374</v>
+        <v>31.55973124565509</v>
       </c>
       <c r="U8" t="n">
-        <v>26.16439281619768</v>
+        <v>26.16439281619698</v>
       </c>
       <c r="V8" t="n">
-        <v>28.51242822206773</v>
+        <v>28.51242822206672</v>
       </c>
       <c r="W8" t="n">
-        <v>31.56191353623934</v>
+        <v>31.56191353624083</v>
       </c>
       <c r="X8" t="n">
-        <v>19.29084149643154</v>
+        <v>19.29084149643339</v>
       </c>
       <c r="Y8" t="n">
-        <v>42.64255438737569</v>
+        <v>42.64255438737605</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.24909633471916</v>
+        <v>20.2490963347214</v>
       </c>
       <c r="AA8" t="n">
-        <v>31.55973124565374</v>
+        <v>31.55973124565509</v>
       </c>
       <c r="AB8" t="n">
-        <v>43.15916963579394</v>
+        <v>43.15916963579406</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>452.9661806449419</v>
+        <v>452.9661806449438</v>
       </c>
       <c r="C9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="D9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="E9" t="n">
-        <v>548.6907639554022</v>
+        <v>548.6907639554036</v>
       </c>
       <c r="F9" t="n">
-        <v>290.5298255074204</v>
+        <v>290.5298255074217</v>
       </c>
       <c r="G9" t="n">
-        <v>577.4124569103481</v>
+        <v>577.4124569103476</v>
       </c>
       <c r="H9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="I9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="J9" t="n">
-        <v>577.4059506866166</v>
+        <v>577.4059506866167</v>
       </c>
       <c r="K9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="L9" t="n">
-        <v>577.4124537898518</v>
+        <v>577.4124537898545</v>
       </c>
       <c r="M9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="N9" t="n">
-        <v>53.65175804660122</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="O9" t="n">
-        <v>618.653789916165</v>
+        <v>618.6537899161657</v>
       </c>
       <c r="P9" t="n">
-        <v>627.6230722628451</v>
+        <v>627.6230722628444</v>
       </c>
       <c r="Q9" t="n">
-        <v>577.4124569103481</v>
+        <v>577.4124569103476</v>
       </c>
       <c r="R9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="S9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="T9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="U9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="V9" t="n">
-        <v>720.9814206183197</v>
+        <v>720.9814206183178</v>
       </c>
       <c r="W9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="X9" t="n">
-        <v>577.4124537898518</v>
+        <v>577.4124537898545</v>
       </c>
       <c r="Y9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="Z9" t="n">
-        <v>502.3824185169559</v>
+        <v>502.3824185169566</v>
       </c>
       <c r="AA9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
       <c r="AB9" t="n">
-        <v>577.4124537898517</v>
+        <v>577.4124537898541</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.209905920651876</v>
+        <v>8.209905920652631</v>
       </c>
       <c r="C10" t="n">
-        <v>8.661892900387626</v>
+        <v>8.661892900388048</v>
       </c>
       <c r="D10" t="n">
-        <v>7.952456168766732</v>
+        <v>7.952456168767768</v>
       </c>
       <c r="E10" t="n">
-        <v>8.377601908990641</v>
+        <v>8.377601908990961</v>
       </c>
       <c r="F10" t="n">
-        <v>7.831809480438104</v>
+        <v>7.83180948043951</v>
       </c>
       <c r="G10" t="n">
-        <v>6.021563941958982</v>
+        <v>6.02156394195981</v>
       </c>
       <c r="H10" t="n">
-        <v>8.727843905641013</v>
+        <v>8.727843905641144</v>
       </c>
       <c r="I10" t="n">
-        <v>6.395209064040068</v>
+        <v>6.395209064040372</v>
       </c>
       <c r="J10" t="n">
-        <v>7.018079110474986</v>
+        <v>7.018079110475541</v>
       </c>
       <c r="K10" t="n">
-        <v>7.30012439686774</v>
+        <v>7.300124396868372</v>
       </c>
       <c r="L10" t="n">
-        <v>8.326233772717696</v>
+        <v>8.32623377271824</v>
       </c>
       <c r="M10" t="n">
-        <v>6.498928678568923</v>
+        <v>6.498928678569557</v>
       </c>
       <c r="N10" t="n">
-        <v>8.000956020568033</v>
+        <v>8.000956020568212</v>
       </c>
       <c r="O10" t="n">
-        <v>7.917956017992909</v>
+        <v>7.917956017993083</v>
       </c>
       <c r="P10" t="n">
-        <v>7.456493041389895</v>
+        <v>7.456493041390546</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.21025044985877</v>
+        <v>7.210250449859195</v>
       </c>
       <c r="R10" t="n">
-        <v>7.226685711279565</v>
+        <v>7.226685711279966</v>
       </c>
       <c r="S10" t="n">
-        <v>7.212495618494947</v>
+        <v>7.212495618495686</v>
       </c>
       <c r="T10" t="n">
-        <v>7.708957930163044</v>
+        <v>7.708957930163861</v>
       </c>
       <c r="U10" t="n">
-        <v>8.196327912729988</v>
+        <v>8.196327912730441</v>
       </c>
       <c r="V10" t="n">
-        <v>6.12305659084635</v>
+        <v>6.123056590846383</v>
       </c>
       <c r="W10" t="n">
-        <v>7.729821339409959</v>
+        <v>7.729821339410408</v>
       </c>
       <c r="X10" t="n">
-        <v>7.492212673537913</v>
+        <v>7.492212673538845</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.690759674461352</v>
+        <v>5.690759674461754</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.511178707670062</v>
+        <v>7.511178707670549</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.8986033718945</v>
+        <v>7.898603371895135</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.286285698181884</v>
+        <v>6.286285698182783</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.737565697809615</v>
+        <v>8.7375656978104</v>
       </c>
       <c r="C11" t="n">
-        <v>8.868267765440796</v>
+        <v>8.868267765440851</v>
       </c>
       <c r="D11" t="n">
-        <v>8.666670033926426</v>
+        <v>8.666670033927398</v>
       </c>
       <c r="E11" t="n">
-        <v>8.268904591575771</v>
+        <v>8.268904591576055</v>
       </c>
       <c r="F11" t="n">
-        <v>8.633418816128966</v>
+        <v>8.633418816129971</v>
       </c>
       <c r="G11" t="n">
-        <v>8.109988987740186</v>
+        <v>8.109988987740117</v>
       </c>
       <c r="H11" t="n">
-        <v>8.887510117802382</v>
+        <v>8.887510117802407</v>
       </c>
       <c r="I11" t="n">
-        <v>8.224831624922979</v>
+        <v>8.224831624922881</v>
       </c>
       <c r="J11" t="n">
-        <v>8.368534979697387</v>
+        <v>8.368534979697548</v>
       </c>
       <c r="K11" t="n">
-        <v>8.480792781481394</v>
+        <v>8.480792781481913</v>
       </c>
       <c r="L11" t="n">
-        <v>8.771743643399354</v>
+        <v>8.771743643399569</v>
       </c>
       <c r="M11" t="n">
-        <v>8.255136884019205</v>
+        <v>8.25513688401969</v>
       </c>
       <c r="N11" t="n">
-        <v>8.679680410931494</v>
+        <v>8.679680410931596</v>
       </c>
       <c r="O11" t="n">
-        <v>8.653588739670594</v>
+        <v>8.653588739670212</v>
       </c>
       <c r="P11" t="n">
-        <v>8.520862674138444</v>
+        <v>8.520862674138488</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.454858755094952</v>
+        <v>8.454858755095001</v>
       </c>
       <c r="R11" t="n">
-        <v>8.461598846976171</v>
+        <v>8.461598846976599</v>
       </c>
       <c r="S11" t="n">
-        <v>8.452369217547252</v>
+        <v>8.452369217547767</v>
       </c>
       <c r="T11" t="n">
-        <v>8.597596603733038</v>
+        <v>8.597596603733201</v>
       </c>
       <c r="U11" t="n">
-        <v>8.734460560919993</v>
+        <v>8.734460560920564</v>
       </c>
       <c r="V11" t="n">
-        <v>7.095948146698205</v>
+        <v>7.095948146698255</v>
       </c>
       <c r="W11" t="n">
-        <v>8.601640643138062</v>
+        <v>8.601640643138069</v>
       </c>
       <c r="X11" t="n">
-        <v>8.53556975157271</v>
+        <v>8.535569751573879</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.02027842126277</v>
+        <v>8.020278421263269</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.5373848860834</v>
+        <v>8.537384886083977</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.650002686415247</v>
+        <v>8.650002686415778</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.193114909206836</v>
+        <v>8.193114909208099</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>4.901288237043024</v>
       </c>
       <c r="N5" t="n">
-        <v>75.47458653156887</v>
+        <v>4.901288237043658</v>
       </c>
       <c r="O5" t="n">
         <v>4.901288237043659</v>
@@ -6154,7 +6154,7 @@
         <v>21.12847787467413</v>
       </c>
       <c r="N6" t="n">
-        <v>75.47458653156887</v>
+        <v>8.049305520758736</v>
       </c>
       <c r="O6" t="n">
         <v>21.4877520183013</v>
@@ -6242,7 +6242,7 @@
         <v>9.637403553848435</v>
       </c>
       <c r="N7" t="n">
-        <v>75.47458653156887</v>
+        <v>9.637403553848435</v>
       </c>
       <c r="O7" t="n">
         <v>9.63734011799866</v>
@@ -6330,7 +6330,7 @@
         <v>32.06775245919152</v>
       </c>
       <c r="N8" t="n">
-        <v>75.47458653156887</v>
+        <v>23.22491840972628</v>
       </c>
       <c r="O8" t="n">
         <v>25.65500597336779</v>
@@ -6418,7 +6418,7 @@
         <v>619.295384127229</v>
       </c>
       <c r="N9" t="n">
-        <v>75.47458653156887</v>
+        <v>619.295384127229</v>
       </c>
       <c r="O9" t="n">
         <v>663.5632659079151</v>
@@ -6990,7 +6990,7 @@
         <v>429.6436985588418</v>
       </c>
       <c r="F4" t="n">
-        <v>284.8270604000222</v>
+        <v>284.8270604000223</v>
       </c>
       <c r="G4" t="n">
         <v>52.11072553472381</v>
@@ -7090,7 +7090,7 @@
         <v>6.25132659336973</v>
       </c>
       <c r="J5" t="n">
-        <v>6.24500180793218</v>
+        <v>6.245001807932179</v>
       </c>
       <c r="K5" t="n">
         <v>6.25132659336973</v>
@@ -7102,7 +7102,7 @@
         <v>6.25132659336973</v>
       </c>
       <c r="N5" t="n">
-        <v>140.4524193501645</v>
+        <v>6.251326593368992</v>
       </c>
       <c r="O5" t="n">
         <v>6.251326593368995</v>
@@ -7129,7 +7129,7 @@
         <v>6.214105785986971</v>
       </c>
       <c r="W5" t="n">
-        <v>6.251326593368994</v>
+        <v>6.251326593368992</v>
       </c>
       <c r="X5" t="n">
         <v>6.251326593368994</v>
@@ -7190,7 +7190,7 @@
         <v>23.95003395284552</v>
       </c>
       <c r="N6" t="n">
-        <v>140.4524193501645</v>
+        <v>10.61294799384092</v>
       </c>
       <c r="O6" t="n">
         <v>24.55088230078371</v>
@@ -7278,7 +7278,7 @@
         <v>11.12324429703351</v>
       </c>
       <c r="N7" t="n">
-        <v>140.4524193501645</v>
+        <v>11.12324429703351</v>
       </c>
       <c r="O7" t="n">
         <v>11.12326610423917</v>
@@ -7366,7 +7366,7 @@
         <v>34.39133243810693</v>
       </c>
       <c r="N8" t="n">
-        <v>140.4524193501645</v>
+        <v>24.98015284882662</v>
       </c>
       <c r="O8" t="n">
         <v>27.56642669356368</v>
@@ -7408,7 +7408,7 @@
         <v>34.3913324381008</v>
       </c>
       <c r="AB8" t="n">
-        <v>47.07345155569032</v>
+        <v>47.07345155569031</v>
       </c>
     </row>
     <row r="9">
@@ -7454,7 +7454,7 @@
         <v>580.0006256717925</v>
       </c>
       <c r="N9" t="n">
-        <v>140.4524193501645</v>
+        <v>580.0006256717925</v>
       </c>
       <c r="O9" t="n">
         <v>621.4160166808091</v>
@@ -7566,7 +7566,7 @@
         <v>9.34681268986253</v>
       </c>
       <c r="V10" t="n">
-        <v>6.352340888729312</v>
+        <v>6.352340888729311</v>
       </c>
       <c r="W10" t="n">
         <v>7.558099108258889</v>
@@ -7663,7 +7663,7 @@
         <v>9.330574318490353</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.720622771224352</v>
+        <v>9.720622771224351</v>
       </c>
       <c r="Z11" t="n">
         <v>8.906375627122177</v>
@@ -8138,7 +8138,7 @@
         <v>6.929700575124895</v>
       </c>
       <c r="N5" t="n">
-        <v>104.4872820939391</v>
+        <v>6.929700575125268</v>
       </c>
       <c r="O5" t="n">
         <v>6.929700575125268</v>
@@ -8226,7 +8226,7 @@
         <v>25.4706770558777</v>
       </c>
       <c r="N6" t="n">
-        <v>104.4872820939391</v>
+        <v>11.67288440929691</v>
       </c>
       <c r="O6" t="n">
         <v>11.56835753058255</v>
@@ -8314,7 +8314,7 @@
         <v>11.9714655515219</v>
       </c>
       <c r="N7" t="n">
-        <v>104.4872820939391</v>
+        <v>11.9714655515219</v>
       </c>
       <c r="O7" t="n">
         <v>11.97151423730464</v>
@@ -8402,7 +8402,7 @@
         <v>36.19161834631175</v>
       </c>
       <c r="N8" t="n">
-        <v>104.4872820939391</v>
+        <v>26.29619569737163</v>
       </c>
       <c r="O8" t="n">
         <v>29.01554373530331</v>
@@ -8490,7 +8490,7 @@
         <v>580.3579769748069</v>
       </c>
       <c r="N9" t="n">
-        <v>104.4872820939391</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="O9" t="n">
         <v>621.7852096219993</v>
@@ -9086,7 +9086,7 @@
         <v>173.2426980289865</v>
       </c>
       <c r="N4" t="n">
-        <v>71.25808425420334</v>
+        <v>71.25808425420331</v>
       </c>
       <c r="O4" t="n">
         <v>42.12146136543176</v>
@@ -9174,7 +9174,7 @@
         <v>3.557623791760276</v>
       </c>
       <c r="N5" t="n">
-        <v>71.25808425420331</v>
+        <v>3.557623791760397</v>
       </c>
       <c r="O5" t="n">
         <v>3.557623791760397</v>
@@ -9262,7 +9262,7 @@
         <v>5.975490565863709</v>
       </c>
       <c r="N6" t="n">
-        <v>71.25808425420334</v>
+        <v>6.045811360617728</v>
       </c>
       <c r="O6" t="n">
         <v>18.54580643741912</v>
@@ -9350,7 +9350,7 @@
         <v>7.689384185215245</v>
       </c>
       <c r="N7" t="n">
-        <v>71.25808425420334</v>
+        <v>7.689384185215245</v>
       </c>
       <c r="O7" t="n">
         <v>7.68940325220599</v>
@@ -9438,7 +9438,7 @@
         <v>28.17941846526736</v>
       </c>
       <c r="N8" t="n">
-        <v>71.25808425420334</v>
+        <v>20.30379722729353</v>
       </c>
       <c r="O8" t="n">
         <v>22.46808631722812</v>
@@ -9526,7 +9526,7 @@
         <v>617.581669209301</v>
       </c>
       <c r="N9" t="n">
-        <v>71.25808425420334</v>
+        <v>617.581669209301</v>
       </c>
       <c r="O9" t="n">
         <v>661.7751060913079</v>
@@ -10210,7 +10210,7 @@
         <v>5.100982690405515</v>
       </c>
       <c r="N5" t="n">
-        <v>73.39507945505002</v>
+        <v>5.100982690405517</v>
       </c>
       <c r="O5" t="n">
         <v>5.100982690405516</v>
@@ -10298,7 +10298,7 @@
         <v>8.387014027765638</v>
       </c>
       <c r="N6" t="n">
-        <v>73.39507945505002</v>
+        <v>8.429610941246526</v>
       </c>
       <c r="O6" t="n">
         <v>21.44781124749703</v>
@@ -10386,7 +10386,7 @@
         <v>9.499623409940378</v>
       </c>
       <c r="N7" t="n">
-        <v>73.39507945505002</v>
+        <v>9.499623409940378</v>
       </c>
       <c r="O7" t="n">
         <v>9.499638024726284</v>
@@ -10474,7 +10474,7 @@
         <v>31.09887498894381</v>
       </c>
       <c r="N8" t="n">
-        <v>73.39507945505002</v>
+        <v>22.52016979338158</v>
       </c>
       <c r="O8" t="n">
         <v>24.87767245131569</v>
@@ -10562,7 +10562,7 @@
         <v>577.8578955605522</v>
       </c>
       <c r="N9" t="n">
-        <v>73.39507945505002</v>
+        <v>577.8578955605522</v>
       </c>
       <c r="O9" t="n">
         <v>619.1573789068503</v>

--- a/Results/Phase 2/Hydrogen/hydrogen land use results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen land use results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.406157661783983</v>
+        <v>5.406157661783939</v>
       </c>
       <c r="C2" t="n">
-        <v>5.395873958782393</v>
+        <v>5.395873958782357</v>
       </c>
       <c r="D2" t="n">
-        <v>5.36173705508544</v>
+        <v>5.361737055085421</v>
       </c>
       <c r="E2" t="n">
-        <v>6.263285471300319</v>
+        <v>6.263285471300303</v>
       </c>
       <c r="F2" t="n">
-        <v>5.315537631897227</v>
+        <v>5.315537631897207</v>
       </c>
       <c r="G2" t="n">
-        <v>5.71796292283415</v>
+        <v>5.717962922834083</v>
       </c>
       <c r="H2" t="n">
-        <v>5.402908343627091</v>
+        <v>5.402908343627105</v>
       </c>
       <c r="I2" t="n">
-        <v>5.437139600761954</v>
+        <v>5.4371396007619</v>
       </c>
       <c r="J2" t="n">
-        <v>5.523674460576252</v>
+        <v>5.523674460576225</v>
       </c>
       <c r="K2" t="n">
-        <v>5.63063351761625</v>
+        <v>5.630633517616188</v>
       </c>
       <c r="L2" t="n">
-        <v>5.367484457321464</v>
+        <v>5.367484457321653</v>
       </c>
       <c r="M2" t="n">
-        <v>5.837246956021763</v>
+        <v>5.837246956021724</v>
       </c>
       <c r="N2" t="n">
-        <v>5.470103299273172</v>
+        <v>5.470103299273159</v>
       </c>
       <c r="O2" t="n">
-        <v>5.536691328417472</v>
+        <v>5.53669132841743</v>
       </c>
       <c r="P2" t="n">
-        <v>5.517753048658475</v>
+        <v>5.517753048658461</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.384897662251671</v>
+        <v>5.384897662251631</v>
       </c>
       <c r="R2" t="n">
-        <v>5.471627003453778</v>
+        <v>5.471627003453774</v>
       </c>
       <c r="S2" t="n">
-        <v>5.568342233041395</v>
+        <v>5.568342233041355</v>
       </c>
       <c r="T2" t="n">
-        <v>5.443438225171759</v>
+        <v>5.443438225171686</v>
       </c>
       <c r="U2" t="n">
-        <v>5.541421838566261</v>
+        <v>5.541421838566228</v>
       </c>
       <c r="V2" t="n">
-        <v>3.729113564039825</v>
+        <v>3.729113564039776</v>
       </c>
       <c r="W2" t="n">
-        <v>5.439552096672499</v>
+        <v>5.439552096672443</v>
       </c>
       <c r="X2" t="n">
-        <v>5.397124822016122</v>
+        <v>5.397124822016012</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.450385646666515</v>
+        <v>5.450385646666461</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.428876028479788</v>
+        <v>5.428876028479744</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.562421333636987</v>
+        <v>5.562421333636918</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.81130141879081</v>
+        <v>5.811301418790816</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="C3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="D3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="E3" t="n">
-        <v>6.498209984042631</v>
+        <v>6.498209984042621</v>
       </c>
       <c r="F3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="G3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="H3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="I3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="J3" t="n">
-        <v>5.335155405945139</v>
+        <v>5.335155405945114</v>
       </c>
       <c r="K3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="L3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="M3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="N3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="O3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="P3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="R3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="S3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="T3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="U3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="V3" t="n">
-        <v>3.554873304064981</v>
+        <v>3.554873304064939</v>
       </c>
       <c r="W3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="X3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.369832531322121</v>
+        <v>5.369832531322061</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.44116861697613</v>
+        <v>29.44116861696634</v>
       </c>
       <c r="C4" t="n">
-        <v>29.06832045690508</v>
+        <v>29.0683204569051</v>
       </c>
       <c r="D4" t="n">
-        <v>18.94789434335485</v>
+        <v>18.94789434335487</v>
       </c>
       <c r="E4" t="n">
-        <v>-40.81325011332909</v>
+        <v>-40.81325011332984</v>
       </c>
       <c r="F4" t="n">
-        <v>5.042047515827387</v>
+        <v>5.042047515827242</v>
       </c>
       <c r="G4" t="n">
-        <v>116.3781693689312</v>
+        <v>116.3781693689308</v>
       </c>
       <c r="H4" t="n">
-        <v>32.70761548009449</v>
+        <v>32.70761548009431</v>
       </c>
       <c r="I4" t="n">
-        <v>42.31644794136194</v>
+        <v>42.31644794136136</v>
       </c>
       <c r="J4" t="n">
-        <v>73.69462503238339</v>
+        <v>73.69462503238431</v>
       </c>
       <c r="K4" t="n">
-        <v>100.0313559632983</v>
+        <v>100.0313559632976</v>
       </c>
       <c r="L4" t="n">
-        <v>19.77494563897329</v>
+        <v>19.77494563889721</v>
       </c>
       <c r="M4" t="n">
         <v>165.2739645355927</v>
       </c>
       <c r="N4" t="n">
-        <v>50.59692422880047</v>
+        <v>50.59692422880065</v>
       </c>
       <c r="O4" t="n">
-        <v>63.28953866444046</v>
+        <v>63.28953866444026</v>
       </c>
       <c r="P4" t="n">
-        <v>60.25974664423905</v>
+        <v>60.25974664423941</v>
       </c>
       <c r="Q4" t="n">
-        <v>25.57950208121136</v>
+        <v>25.57950208120953</v>
       </c>
       <c r="R4" t="n">
-        <v>53.5391268561347</v>
+        <v>53.53912685613524</v>
       </c>
       <c r="S4" t="n">
-        <v>75.05530901079317</v>
+        <v>75.05530901078937</v>
       </c>
       <c r="T4" t="n">
-        <v>43.95914905385516</v>
+        <v>43.95914905385396</v>
       </c>
       <c r="U4" t="n">
-        <v>68.85214336909094</v>
+        <v>68.85214336909088</v>
       </c>
       <c r="V4" t="n">
-        <v>59.71210663472065</v>
+        <v>59.71210663472051</v>
       </c>
       <c r="W4" t="n">
-        <v>40.89680621802063</v>
+        <v>40.8968062180194</v>
       </c>
       <c r="X4" t="n">
-        <v>29.43902548894421</v>
+        <v>29.43902548894526</v>
       </c>
       <c r="Y4" t="n">
-        <v>44.14823032688204</v>
+        <v>44.14823032688209</v>
       </c>
       <c r="Z4" t="n">
-        <v>36.23144696353212</v>
+        <v>36.23144696353894</v>
       </c>
       <c r="AA4" t="n">
-        <v>77.10130722983229</v>
+        <v>77.10130722983239</v>
       </c>
       <c r="AB4" t="n">
-        <v>163.1209981425163</v>
+        <v>163.1209981425162</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.60528768943872</v>
+        <v>15.60528768943864</v>
       </c>
       <c r="C5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326998</v>
       </c>
       <c r="D5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326998</v>
       </c>
       <c r="E5" t="n">
-        <v>19.80423999173225</v>
+        <v>19.80423999173228</v>
       </c>
       <c r="F5" t="n">
-        <v>17.00444581044184</v>
+        <v>17.00444581044191</v>
       </c>
       <c r="G5" t="n">
-        <v>26.44873700108223</v>
+        <v>26.44873700108226</v>
       </c>
       <c r="H5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326998</v>
       </c>
       <c r="I5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326998</v>
       </c>
       <c r="J5" t="n">
-        <v>24.58236491082216</v>
+        <v>24.58236491082206</v>
       </c>
       <c r="K5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326998</v>
       </c>
       <c r="L5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326998</v>
       </c>
       <c r="M5" t="n">
-        <v>24.58643715326079</v>
+        <v>24.58643715326063</v>
       </c>
       <c r="N5" t="n">
-        <v>50.59692422880047</v>
+        <v>17.62454380419119</v>
       </c>
       <c r="O5" t="n">
-        <v>19.53773254378664</v>
+        <v>19.53773254378662</v>
       </c>
       <c r="P5" t="n">
-        <v>19.06876375478459</v>
+        <v>19.06876375478465</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.84028683584749</v>
+        <v>13.8402868358474</v>
       </c>
       <c r="R5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326998</v>
       </c>
       <c r="S5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326998</v>
       </c>
       <c r="T5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326999</v>
       </c>
       <c r="U5" t="n">
-        <v>20.16674853610926</v>
+        <v>20.16674853610915</v>
       </c>
       <c r="V5" t="n">
-        <v>22.06751719120934</v>
+        <v>22.06751719120935</v>
       </c>
       <c r="W5" t="n">
-        <v>24.58820220280118</v>
+        <v>24.58820220280103</v>
       </c>
       <c r="X5" t="n">
-        <v>14.66342702785852</v>
+        <v>14.66342702785848</v>
       </c>
       <c r="Y5" t="n">
-        <v>33.45441690832304</v>
+        <v>33.45441690832285</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.43845822736874</v>
+        <v>15.43845822736868</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.58643715327022</v>
+        <v>24.58643715326998</v>
       </c>
       <c r="AB5" t="n">
-        <v>33.96799875656778</v>
+        <v>33.96799875656771</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>514.7688792695009</v>
+        <v>514.7688792695</v>
       </c>
       <c r="C6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="D6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="E6" t="n">
-        <v>623.9614770684956</v>
+        <v>623.9614770684947</v>
       </c>
       <c r="F6" t="n">
-        <v>329.4784660750024</v>
+        <v>329.4784660750022</v>
       </c>
       <c r="G6" t="n">
-        <v>656.7241818876338</v>
+        <v>656.724181887633</v>
       </c>
       <c r="H6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="I6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="J6" t="n">
-        <v>656.7201092145108</v>
+        <v>656.7201092145106</v>
       </c>
       <c r="K6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="L6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="M6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="N6" t="n">
-        <v>50.59692422880047</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="O6" t="n">
-        <v>703.767983300627</v>
+        <v>703.7679833006259</v>
       </c>
       <c r="P6" t="n">
-        <v>713.999202972276</v>
+        <v>713.9992029722753</v>
       </c>
       <c r="Q6" t="n">
-        <v>656.7241818876338</v>
+        <v>656.724181887633</v>
       </c>
       <c r="R6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="S6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="T6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="U6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="V6" t="n">
-        <v>820.5131798351505</v>
+        <v>820.5131798351504</v>
       </c>
       <c r="W6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="X6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="Y6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="Z6" t="n">
-        <v>571.1377575669165</v>
+        <v>571.1377575669159</v>
       </c>
       <c r="AA6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
       <c r="AB6" t="n">
-        <v>656.7241814569579</v>
+        <v>656.7241814569576</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.829619767132711</v>
+        <v>4.829619767132716</v>
       </c>
       <c r="C7" t="n">
-        <v>4.89771565314101</v>
+        <v>4.897715653140979</v>
       </c>
       <c r="D7" t="n">
-        <v>5.098226806583614</v>
+        <v>5.098226806583589</v>
       </c>
       <c r="E7" t="n">
-        <v>7.450462672969149</v>
+        <v>7.450462672969211</v>
       </c>
       <c r="F7" t="n">
-        <v>5.368875575628451</v>
+        <v>5.368875575628376</v>
       </c>
       <c r="G7" t="n">
-        <v>2.975971384080958</v>
+        <v>2.97597138408095</v>
       </c>
       <c r="H7" t="n">
-        <v>4.86056432802663</v>
+        <v>4.860564328026559</v>
       </c>
       <c r="I7" t="n">
-        <v>4.657900197971466</v>
+        <v>4.657900197971417</v>
       </c>
       <c r="J7" t="n">
-        <v>3.896175154470254</v>
+        <v>3.896175154470212</v>
       </c>
       <c r="K7" t="n">
-        <v>3.520531247629808</v>
+        <v>3.520531247629773</v>
       </c>
       <c r="L7" t="n">
-        <v>5.061676401161433</v>
+        <v>5.061676401161984</v>
       </c>
       <c r="M7" t="n">
-        <v>2.324535605534663</v>
+        <v>2.324535605534639</v>
       </c>
       <c r="N7" t="n">
-        <v>4.459609047116868</v>
+        <v>4.459609047116825</v>
       </c>
       <c r="O7" t="n">
-        <v>4.051611805008932</v>
+        <v>4.051611805008901</v>
       </c>
       <c r="P7" t="n">
-        <v>4.16332588468953</v>
+        <v>4.163325884689487</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.961506149364613</v>
+        <v>4.961506149364599</v>
       </c>
       <c r="R7" t="n">
-        <v>4.458172800087444</v>
+        <v>4.458172800087399</v>
       </c>
       <c r="S7" t="n">
-        <v>3.869420592448684</v>
+        <v>3.869420592448658</v>
       </c>
       <c r="T7" t="n">
-        <v>4.620139820133694</v>
+        <v>4.620139820133716</v>
       </c>
       <c r="U7" t="n">
-        <v>4.032046658253735</v>
+        <v>4.032046658253709</v>
       </c>
       <c r="V7" t="n">
-        <v>2.354358933463146</v>
+        <v>2.354358933463113</v>
       </c>
       <c r="W7" t="n">
-        <v>4.636858614663986</v>
+        <v>4.636858614663943</v>
       </c>
       <c r="X7" t="n">
-        <v>4.890474813935616</v>
+        <v>4.890474813935783</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.574215641397655</v>
+        <v>4.574215641397621</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.69521921581337</v>
+        <v>4.6952192158136</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.912878135391245</v>
+        <v>3.912878135391243</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.465551586725222</v>
+        <v>2.465551586725204</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.16035913252185</v>
+        <v>5.160359132521766</v>
       </c>
       <c r="C8" t="n">
-        <v>5.181059274662765</v>
+        <v>5.181059274662684</v>
       </c>
       <c r="D8" t="n">
-        <v>5.23815558477333</v>
+        <v>5.238155584773255</v>
       </c>
       <c r="E8" t="n">
-        <v>6.696563479411163</v>
+        <v>6.696563479411118</v>
       </c>
       <c r="F8" t="n">
-        <v>5.315102214006968</v>
+        <v>5.315102214006921</v>
       </c>
       <c r="G8" t="n">
-        <v>4.62874847205659</v>
+        <v>4.628748472056546</v>
       </c>
       <c r="H8" t="n">
-        <v>5.171189688186169</v>
+        <v>5.171189688186119</v>
       </c>
       <c r="I8" t="n">
-        <v>5.113208120293665</v>
+        <v>5.113208120293666</v>
       </c>
       <c r="J8" t="n">
-        <v>4.868933860397201</v>
+        <v>4.868933860397147</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7891955401627</v>
+        <v>4.789195540162675</v>
       </c>
       <c r="L8" t="n">
-        <v>5.227272436063034</v>
+        <v>5.227272436062983</v>
       </c>
       <c r="M8" t="n">
-        <v>4.451627150002981</v>
+        <v>4.451627150002977</v>
       </c>
       <c r="N8" t="n">
-        <v>5.055948713249665</v>
+        <v>5.055948713249633</v>
       </c>
       <c r="O8" t="n">
-        <v>4.936896697024752</v>
+        <v>4.936896697024691</v>
       </c>
       <c r="P8" t="n">
-        <v>4.968788679532093</v>
+        <v>4.9687886795321</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.199107857202024</v>
+        <v>5.199107857201994</v>
       </c>
       <c r="R8" t="n">
-        <v>5.056818920454813</v>
+        <v>5.056818920454775</v>
       </c>
       <c r="S8" t="n">
-        <v>4.885650019324848</v>
+        <v>4.885650019324847</v>
       </c>
       <c r="T8" t="n">
-        <v>5.102325652452092</v>
+        <v>5.102325652452047</v>
       </c>
       <c r="U8" t="n">
-        <v>4.932725003049496</v>
+        <v>4.932725003049446</v>
       </c>
       <c r="V8" t="n">
-        <v>3.182875699603687</v>
+        <v>3.182875699603655</v>
       </c>
       <c r="W8" t="n">
-        <v>5.106046628743769</v>
+        <v>5.106046628743742</v>
       </c>
       <c r="X8" t="n">
-        <v>5.179015532982855</v>
+        <v>5.179015532982818</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.088377426270272</v>
+        <v>5.08837742627027</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.121924820058221</v>
+        <v>5.121924820058176</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.899502440450256</v>
+        <v>4.899502440450204</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.489844333605015</v>
+        <v>4.489844333604985</v>
       </c>
     </row>
   </sheetData>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.11172255520954</v>
+        <v>10.11172255520953</v>
       </c>
       <c r="C2" t="n">
-        <v>10.24523315799431</v>
+        <v>10.24523315799432</v>
       </c>
       <c r="D2" t="n">
-        <v>10.06362187595344</v>
+        <v>10.06362187595317</v>
       </c>
       <c r="E2" t="n">
-        <v>9.169459418557972</v>
+        <v>9.169459418557786</v>
       </c>
       <c r="F2" t="n">
         <v>10.50883461029156</v>
       </c>
       <c r="G2" t="n">
-        <v>9.89001462924508</v>
+        <v>9.890014629245128</v>
       </c>
       <c r="H2" t="n">
-        <v>9.787385302869856</v>
+        <v>9.78738530286981</v>
       </c>
       <c r="I2" t="n">
         <v>10.12179122035065</v>
       </c>
       <c r="J2" t="n">
-        <v>9.970970185025193</v>
+        <v>9.970970185024807</v>
       </c>
       <c r="K2" t="n">
-        <v>10.09850350992765</v>
+        <v>10.09850350992764</v>
       </c>
       <c r="L2" t="n">
-        <v>10.42236631417604</v>
+        <v>10.42236631417615</v>
       </c>
       <c r="M2" t="n">
-        <v>9.883418067332441</v>
+        <v>9.883418067332434</v>
       </c>
       <c r="N2" t="n">
-        <v>9.935425476045042</v>
+        <v>9.935425476044941</v>
       </c>
       <c r="O2" t="n">
-        <v>9.811298239417031</v>
+        <v>9.811298239416878</v>
       </c>
       <c r="P2" t="n">
-        <v>9.871784524120642</v>
+        <v>9.87178452412078</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.18450677992714</v>
+        <v>10.18450677992705</v>
       </c>
       <c r="R2" t="n">
-        <v>11.08541712548368</v>
+        <v>11.08541712548342</v>
       </c>
       <c r="S2" t="n">
-        <v>10.26851162328565</v>
+        <v>10.26851162328581</v>
       </c>
       <c r="T2" t="n">
-        <v>9.942484955580342</v>
+        <v>9.942484955580428</v>
       </c>
       <c r="U2" t="n">
-        <v>9.84229866203321</v>
+        <v>9.842298662032958</v>
       </c>
       <c r="V2" t="n">
-        <v>8.391076737572211</v>
+        <v>8.391076737571849</v>
       </c>
       <c r="W2" t="n">
-        <v>10.04803990839942</v>
+        <v>10.0480399083994</v>
       </c>
       <c r="X2" t="n">
-        <v>10.05207365658458</v>
+        <v>10.05207365658512</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.970899210338009</v>
+        <v>9.970899210337928</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.995467561080039</v>
+        <v>9.995467561080224</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.932366150520547</v>
+        <v>9.932366150520421</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.990921982917442</v>
+        <v>9.990921982917371</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="C3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="D3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="E3" t="n">
-        <v>8.842548895945644</v>
+        <v>8.842548895945523</v>
       </c>
       <c r="F3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="G3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="H3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="I3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="J3" t="n">
-        <v>9.726580092264721</v>
+        <v>9.726580092264955</v>
       </c>
       <c r="K3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="L3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="M3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="N3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="O3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="P3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="R3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="S3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="T3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="U3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="V3" t="n">
-        <v>8.16284210943366</v>
+        <v>8.162842109433138</v>
       </c>
       <c r="W3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="X3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.762694555982899</v>
+        <v>9.762694555982785</v>
       </c>
     </row>
     <row r="4">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>109.926437916814</v>
+        <v>109.926437916813</v>
       </c>
       <c r="C4" t="n">
-        <v>149.0541568100581</v>
+        <v>149.0541568100578</v>
       </c>
       <c r="D4" t="n">
-        <v>106.6244821298854</v>
+        <v>106.6244821298844</v>
       </c>
       <c r="E4" t="n">
-        <v>104.0249698675606</v>
+        <v>104.0249698675598</v>
       </c>
       <c r="F4" t="n">
-        <v>222.2918922209695</v>
+        <v>222.2918922209684</v>
       </c>
       <c r="G4" t="n">
-        <v>57.91356735733655</v>
+        <v>57.91356735733578</v>
       </c>
       <c r="H4" t="n">
-        <v>40.5257281934271</v>
+        <v>40.5257281934252</v>
       </c>
       <c r="I4" t="n">
-        <v>125.7259165299024</v>
+        <v>125.7259165299018</v>
       </c>
       <c r="J4" t="n">
-        <v>89.09514257441234</v>
+        <v>89.09514257441189</v>
       </c>
       <c r="K4" t="n">
-        <v>107.2531884048272</v>
+        <v>107.2531884048267</v>
       </c>
       <c r="L4" t="n">
-        <v>180.0503028568372</v>
+        <v>180.0503028568368</v>
       </c>
       <c r="M4" t="n">
-        <v>62.96385642802407</v>
+        <v>62.96385642802422</v>
       </c>
       <c r="N4" t="n">
-        <v>77.02577091400541</v>
+        <v>77.02577091400546</v>
       </c>
       <c r="O4" t="n">
-        <v>40.33486056030804</v>
+        <v>40.33486056030647</v>
       </c>
       <c r="P4" t="n">
-        <v>54.11247080251088</v>
+        <v>54.11247080251027</v>
       </c>
       <c r="Q4" t="n">
-        <v>132.2734613188964</v>
+        <v>132.2734613188961</v>
       </c>
       <c r="R4" t="n">
-        <v>386.5909304438778</v>
+        <v>386.5909304438779</v>
       </c>
       <c r="S4" t="n">
-        <v>143.5385388903619</v>
+        <v>143.5385388903613</v>
       </c>
       <c r="T4" t="n">
-        <v>80.02583839626736</v>
+        <v>80.02583839626671</v>
       </c>
       <c r="U4" t="n">
-        <v>47.81123131892986</v>
+        <v>47.8112313189277</v>
       </c>
       <c r="V4" t="n">
-        <v>75.64091458350158</v>
+        <v>75.64091458350099</v>
       </c>
       <c r="W4" t="n">
-        <v>103.4387195392291</v>
+        <v>103.4387195392286</v>
       </c>
       <c r="X4" t="n">
-        <v>102.1501949018049</v>
+        <v>102.1501949018051</v>
       </c>
       <c r="Y4" t="n">
-        <v>85.40865382172103</v>
+        <v>85.40865382172133</v>
       </c>
       <c r="Z4" t="n">
-        <v>78.92140730618014</v>
+        <v>78.92140730618023</v>
       </c>
       <c r="AA4" t="n">
-        <v>75.21342055951671</v>
+        <v>75.21342055951615</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.72824553521849</v>
+        <v>95.72824553521814</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.408224585975</v>
+        <v>21.40822458597476</v>
       </c>
       <c r="C5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="D5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="E5" t="n">
-        <v>26.86947592955977</v>
+        <v>26.86947592955974</v>
       </c>
       <c r="F5" t="n">
-        <v>23.2280009469891</v>
+        <v>23.22800094698847</v>
       </c>
       <c r="G5" t="n">
-        <v>35.51145743081215</v>
+        <v>35.51145743081074</v>
       </c>
       <c r="H5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="I5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="J5" t="n">
-        <v>33.08386372190611</v>
+        <v>33.08386372190571</v>
       </c>
       <c r="K5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="L5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="M5" t="n">
-        <v>33.08930857350735</v>
+        <v>33.08930857350612</v>
       </c>
       <c r="N5" t="n">
-        <v>77.02577091400541</v>
+        <v>24.03451427023008</v>
       </c>
       <c r="O5" t="n">
-        <v>26.52285034466135</v>
+        <v>26.52285034466029</v>
       </c>
       <c r="P5" t="n">
-        <v>25.91289904860371</v>
+        <v>25.91289904860284</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.11262498636902</v>
+        <v>19.11262498636921</v>
       </c>
       <c r="R5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="S5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="T5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="U5" t="n">
-        <v>27.33167050996989</v>
+        <v>27.33167050996946</v>
       </c>
       <c r="V5" t="n">
-        <v>29.80271375163723</v>
+        <v>29.80271375163657</v>
       </c>
       <c r="W5" t="n">
-        <v>33.09160419993367</v>
+        <v>33.09160419993289</v>
       </c>
       <c r="X5" t="n">
-        <v>20.18321951900722</v>
+        <v>20.18321951900726</v>
       </c>
       <c r="Y5" t="n">
-        <v>44.60730538817399</v>
+        <v>44.60730538817283</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.19124245781945</v>
+        <v>21.19124245781863</v>
       </c>
       <c r="AA5" t="n">
-        <v>33.08930857360735</v>
+        <v>33.08930857360583</v>
       </c>
       <c r="AB5" t="n">
-        <v>45.29117751549576</v>
+        <v>45.29117751549445</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>453.2974695332482</v>
+        <v>453.297469533248</v>
       </c>
       <c r="C6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="D6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="E6" t="n">
-        <v>549.0829125474593</v>
+        <v>549.0829125474592</v>
       </c>
       <c r="F6" t="n">
-        <v>290.7578407317355</v>
+        <v>290.7578407317362</v>
       </c>
       <c r="G6" t="n">
-        <v>577.8228661588018</v>
+        <v>577.8228661588014</v>
       </c>
       <c r="H6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="I6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="J6" t="n">
-        <v>577.8174166734184</v>
+        <v>577.8174166734179</v>
       </c>
       <c r="K6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="L6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="M6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="N6" t="n">
-        <v>77.02577091400541</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="O6" t="n">
-        <v>619.0904195483755</v>
+        <v>619.0904195483741</v>
       </c>
       <c r="P6" t="n">
         <v>628.0654043786526</v>
       </c>
       <c r="Q6" t="n">
-        <v>577.8228661588018</v>
+        <v>577.8228661588014</v>
       </c>
       <c r="R6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="S6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="T6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="U6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="V6" t="n">
-        <v>721.4905982769166</v>
+        <v>721.4905982769161</v>
       </c>
       <c r="W6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="X6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="Y6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="Z6" t="n">
-        <v>502.7451252238959</v>
+        <v>502.7451252238963</v>
       </c>
       <c r="AA6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
       <c r="AB6" t="n">
-        <v>577.8228615251189</v>
+        <v>577.8228615251184</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.092662040145996</v>
+        <v>7.0926620401458</v>
       </c>
       <c r="C7" t="n">
-        <v>6.347892913630117</v>
+        <v>6.347892913629877</v>
       </c>
       <c r="D7" t="n">
-        <v>7.41564979764673</v>
+        <v>7.415649797646718</v>
       </c>
       <c r="E7" t="n">
-        <v>6.393614879284117</v>
+        <v>6.393614879283972</v>
       </c>
       <c r="F7" t="n">
-        <v>4.832015354728462</v>
+        <v>4.832015354728383</v>
       </c>
       <c r="G7" t="n">
-        <v>8.412396326275525</v>
+        <v>8.412396326275351</v>
       </c>
       <c r="H7" t="n">
-        <v>9.038679550766478</v>
+        <v>9.038679550766307</v>
       </c>
       <c r="I7" t="n">
-        <v>7.079965306996539</v>
+        <v>7.079965306996331</v>
       </c>
       <c r="J7" t="n">
-        <v>7.696578024776719</v>
+        <v>7.696578024776678</v>
       </c>
       <c r="K7" t="n">
-        <v>7.207702940685069</v>
+        <v>7.207702940685145</v>
       </c>
       <c r="L7" t="n">
-        <v>5.272985516269084</v>
+        <v>5.27298551626904</v>
       </c>
       <c r="M7" t="n">
-        <v>8.476126707372638</v>
+        <v>8.476126707372588</v>
       </c>
       <c r="N7" t="n">
-        <v>8.159782504011956</v>
+        <v>8.159782504011513</v>
       </c>
       <c r="O7" t="n">
-        <v>8.878969198468116</v>
+        <v>8.878969198468241</v>
       </c>
       <c r="P7" t="n">
-        <v>8.517623145347903</v>
+        <v>8.517623145347732</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.699732637677602</v>
+        <v>6.699732637678151</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46331084618219</v>
+        <v>1.46331084618215</v>
       </c>
       <c r="S7" t="n">
-        <v>6.171041562481538</v>
+        <v>6.171041562481581</v>
       </c>
       <c r="T7" t="n">
-        <v>8.126257393943908</v>
+        <v>8.126257393943733</v>
       </c>
       <c r="U7" t="n">
-        <v>8.701186665803597</v>
+        <v>8.701186665803755</v>
       </c>
       <c r="V7" t="n">
-        <v>6.351956780810199</v>
+        <v>6.351956780809656</v>
       </c>
       <c r="W7" t="n">
-        <v>7.489752952068481</v>
+        <v>7.489752952068344</v>
       </c>
       <c r="X7" t="n">
-        <v>7.481093345283096</v>
+        <v>7.481093345282905</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.947981871464356</v>
+        <v>7.947981871464148</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.786482785355485</v>
+        <v>7.786482785355448</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.173755676448778</v>
+        <v>8.17375567644857</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.841928734419135</v>
+        <v>7.841928734419036</v>
       </c>
     </row>
     <row r="8">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.896849251615</v>
+        <v>8.896849251614796</v>
       </c>
       <c r="C8" t="n">
-        <v>8.691487528396665</v>
+        <v>8.69148752839665</v>
       </c>
       <c r="D8" t="n">
-        <v>8.995709031322615</v>
+        <v>8.995709031322518</v>
       </c>
       <c r="E8" t="n">
-        <v>8.055186636687287</v>
+        <v>8.055186636687107</v>
       </c>
       <c r="F8" t="n">
-        <v>8.265359860578501</v>
+        <v>8.265359860578412</v>
       </c>
       <c r="G8" t="n">
-        <v>9.275624631583085</v>
+        <v>9.275624631582794</v>
       </c>
       <c r="H8" t="n">
-        <v>9.457956168197368</v>
+        <v>9.457956168197628</v>
       </c>
       <c r="I8" t="n">
-        <v>8.90114086271098</v>
+        <v>8.901140862710896</v>
       </c>
       <c r="J8" t="n">
-        <v>9.047312775085011</v>
+        <v>9.047312775084981</v>
       </c>
       <c r="K8" t="n">
-        <v>8.935974182692414</v>
+        <v>8.935974182692103</v>
       </c>
       <c r="L8" t="n">
-        <v>8.379534393252362</v>
+        <v>8.379534393252612</v>
       </c>
       <c r="M8" t="n">
-        <v>9.298025596166203</v>
+        <v>9.298025596166303</v>
       </c>
       <c r="N8" t="n">
-        <v>9.206095384220619</v>
+        <v>9.20609538422022</v>
       </c>
       <c r="O8" t="n">
-        <v>9.409200385482228</v>
+        <v>9.409200385482421</v>
       </c>
       <c r="P8" t="n">
-        <v>9.30527306447428</v>
+        <v>9.305273064474621</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.790849346017922</v>
+        <v>8.790849346018062</v>
       </c>
       <c r="R8" t="n">
-        <v>7.309171088957283</v>
+        <v>7.309171088957754</v>
       </c>
       <c r="S8" t="n">
-        <v>8.63429806532378</v>
+        <v>8.634298065323838</v>
       </c>
       <c r="T8" t="n">
-        <v>9.197900831837307</v>
+        <v>9.197900831836765</v>
       </c>
       <c r="U8" t="n">
-        <v>9.359309189176683</v>
+        <v>9.35930918917629</v>
       </c>
       <c r="V8" t="n">
-        <v>7.567118142099356</v>
+        <v>7.56711814209902</v>
       </c>
       <c r="W8" t="n">
-        <v>9.013844235183246</v>
+        <v>9.013844235183289</v>
       </c>
       <c r="X8" t="n">
-        <v>9.013937834684853</v>
+        <v>9.01393783468499</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.145199155735943</v>
+        <v>9.145199155735771</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.096284907631338</v>
+        <v>9.0962849076315</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.209393896683784</v>
+        <v>9.209393896684206</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.116967412988444</v>
+        <v>9.116967412988473</v>
       </c>
     </row>
   </sheetData>
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.399891699405963</v>
+        <v>6.399891699406092</v>
       </c>
       <c r="C2" t="n">
-        <v>6.410961265364898</v>
+        <v>6.410961265365064</v>
       </c>
       <c r="D2" t="n">
-        <v>6.443207071441376</v>
+        <v>6.44320707144144</v>
       </c>
       <c r="E2" t="n">
-        <v>7.009993527475399</v>
+        <v>7.00999352747588</v>
       </c>
       <c r="F2" t="n">
-        <v>6.29487864830808</v>
+        <v>6.294878648308162</v>
       </c>
       <c r="G2" t="n">
-        <v>6.823753605097954</v>
+        <v>6.823753605098076</v>
       </c>
       <c r="H2" t="n">
-        <v>6.354098686987696</v>
+        <v>6.354098686987782</v>
       </c>
       <c r="I2" t="n">
-        <v>6.487733058090861</v>
+        <v>6.487733058091171</v>
       </c>
       <c r="J2" t="n">
-        <v>6.575039103525465</v>
+        <v>6.575039103525628</v>
       </c>
       <c r="K2" t="n">
-        <v>6.582947639982092</v>
+        <v>6.582947639982344</v>
       </c>
       <c r="L2" t="n">
-        <v>6.366422438264914</v>
+        <v>6.366422438265037</v>
       </c>
       <c r="M2" t="n">
-        <v>6.788625031766363</v>
+        <v>6.78862503176653</v>
       </c>
       <c r="N2" t="n">
-        <v>6.465933256607745</v>
+        <v>6.465933256607946</v>
       </c>
       <c r="O2" t="n">
-        <v>6.519004973781001</v>
+        <v>6.519004973781181</v>
       </c>
       <c r="P2" t="n">
-        <v>6.558188651094571</v>
+        <v>6.558188651094754</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.413874156852992</v>
+        <v>6.413874156853211</v>
       </c>
       <c r="R2" t="n">
-        <v>6.409317348586601</v>
+        <v>6.409317348586725</v>
       </c>
       <c r="S2" t="n">
-        <v>6.585673183023721</v>
+        <v>6.58567318302384</v>
       </c>
       <c r="T2" t="n">
-        <v>6.454440412899866</v>
+        <v>6.454440412900108</v>
       </c>
       <c r="U2" t="n">
-        <v>6.55123381787176</v>
+        <v>6.551233817871892</v>
       </c>
       <c r="V2" t="n">
-        <v>4.833062281086544</v>
+        <v>4.833062281086577</v>
       </c>
       <c r="W2" t="n">
-        <v>6.480079000472526</v>
+        <v>6.480079000472706</v>
       </c>
       <c r="X2" t="n">
-        <v>6.468163679466002</v>
+        <v>6.468163679466139</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.516195017869505</v>
+        <v>6.516195017869629</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.471995950724342</v>
+        <v>6.471995950724647</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.483243112474905</v>
+        <v>6.483243112475079</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.803312900992943</v>
+        <v>6.803312900993059</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="C3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="D3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1365306123433</v>
+        <v>7.136530612343503</v>
       </c>
       <c r="F3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="G3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="H3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="I3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="J3" t="n">
-        <v>6.33391327472731</v>
+        <v>6.333913274727594</v>
       </c>
       <c r="K3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="L3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="M3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="N3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="O3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="P3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="R3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="S3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="T3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="U3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="V3" t="n">
-        <v>4.663410329800332</v>
+        <v>4.663410329800356</v>
       </c>
       <c r="W3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="X3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.375069699857965</v>
+        <v>6.375069699857981</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.10230372996754</v>
+        <v>28.1023037299661</v>
       </c>
       <c r="C4" t="n">
-        <v>33.4165811614832</v>
+        <v>33.41658116148308</v>
       </c>
       <c r="D4" t="n">
-        <v>43.33128767851201</v>
+        <v>43.33128767851179</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.537818446479613</v>
+        <v>-6.537818446476394</v>
       </c>
       <c r="F4" t="n">
-        <v>1.483965056686877</v>
+        <v>1.483965056686448</v>
       </c>
       <c r="G4" t="n">
-        <v>137.3280202829208</v>
+        <v>137.3280202829211</v>
       </c>
       <c r="H4" t="n">
-        <v>18.67608984839257</v>
+        <v>18.6760898483935</v>
       </c>
       <c r="I4" t="n">
-        <v>56.58480612204516</v>
+        <v>56.5848061220463</v>
       </c>
       <c r="J4" t="n">
-        <v>85.88648572408283</v>
+        <v>85.88648572408242</v>
       </c>
       <c r="K4" t="n">
-        <v>77.90562840796457</v>
+        <v>77.90562840796488</v>
       </c>
       <c r="L4" t="n">
-        <v>20.52041154912862</v>
+        <v>20.52041154915127</v>
       </c>
       <c r="M4" t="n">
-        <v>142.4161415398423</v>
+        <v>142.416141539842</v>
       </c>
       <c r="N4" t="n">
-        <v>48.53543799241513</v>
+        <v>48.53543799241536</v>
       </c>
       <c r="O4" t="n">
-        <v>56.69445012411519</v>
+        <v>56.6944501241151</v>
       </c>
       <c r="P4" t="n">
-        <v>68.83973106041408</v>
+        <v>68.83973106041509</v>
       </c>
       <c r="Q4" t="n">
-        <v>34.2587838026454</v>
+        <v>34.2587838026478</v>
       </c>
       <c r="R4" t="n">
-        <v>34.39841192354844</v>
+        <v>34.39841192354831</v>
       </c>
       <c r="S4" t="n">
-        <v>76.32555311577354</v>
+        <v>76.32555311577498</v>
       </c>
       <c r="T4" t="n">
-        <v>46.52543321986805</v>
+        <v>46.52543321986965</v>
       </c>
       <c r="U4" t="n">
-        <v>69.18427492075899</v>
+        <v>69.18427492075926</v>
       </c>
       <c r="V4" t="n">
-        <v>57.09715507205399</v>
+        <v>57.09715507205395</v>
       </c>
       <c r="W4" t="n">
-        <v>51.62115563299647</v>
+        <v>51.62115563299642</v>
       </c>
       <c r="X4" t="n">
-        <v>49.68973932146312</v>
+        <v>49.68973932146542</v>
       </c>
       <c r="Y4" t="n">
-        <v>61.01900426384541</v>
+        <v>61.01900426384503</v>
       </c>
       <c r="Z4" t="n">
-        <v>47.04981070607755</v>
+        <v>47.04981070607596</v>
       </c>
       <c r="AA4" t="n">
-        <v>52.46919388696168</v>
+        <v>52.46919388696303</v>
       </c>
       <c r="AB4" t="n">
-        <v>152.9000101851929</v>
+        <v>152.9000101851935</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.92357396024424</v>
+        <v>16.92357396024445</v>
       </c>
       <c r="C5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.59011760451538</v>
       </c>
       <c r="D5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.59011760451538</v>
       </c>
       <c r="E5" t="n">
-        <v>21.44296826223079</v>
+        <v>21.44296826223197</v>
       </c>
       <c r="F5" t="n">
-        <v>18.42950848316663</v>
+        <v>18.42950848316665</v>
       </c>
       <c r="G5" t="n">
-        <v>28.5945384003666</v>
+        <v>28.59453840036678</v>
       </c>
       <c r="H5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.59011760451538</v>
       </c>
       <c r="I5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.59011760451538</v>
       </c>
       <c r="J5" t="n">
-        <v>26.58503417192569</v>
+        <v>26.58503417192607</v>
       </c>
       <c r="K5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.59011760451538</v>
       </c>
       <c r="L5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.59011760451538</v>
       </c>
       <c r="M5" t="n">
-        <v>26.59011760444931</v>
+        <v>26.59011760444965</v>
       </c>
       <c r="N5" t="n">
-        <v>48.53543799241513</v>
+        <v>19.09692909949761</v>
       </c>
       <c r="O5" t="n">
-        <v>21.15612235586601</v>
+        <v>21.15612235586638</v>
       </c>
       <c r="P5" t="n">
-        <v>20.65136433245796</v>
+        <v>20.65136433245839</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.02387750967923</v>
+        <v>15.02387750967905</v>
       </c>
       <c r="R5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.59011760451528</v>
       </c>
       <c r="S5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.59011760451538</v>
       </c>
       <c r="T5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.5901176045154</v>
       </c>
       <c r="U5" t="n">
-        <v>21.7595439114505</v>
+        <v>21.75954391145119</v>
       </c>
       <c r="V5" t="n">
-        <v>23.79393923310919</v>
+        <v>23.7939392331093</v>
       </c>
       <c r="W5" t="n">
-        <v>26.59201734386105</v>
+        <v>26.59201734386175</v>
       </c>
       <c r="X5" t="n">
-        <v>15.90983543423932</v>
+        <v>15.90983543423907</v>
       </c>
       <c r="Y5" t="n">
-        <v>36.00895087620846</v>
+        <v>36.00895087620973</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.74401295039974</v>
+        <v>16.74401295040066</v>
       </c>
       <c r="AA5" t="n">
-        <v>26.59011760451503</v>
+        <v>26.59011760451538</v>
       </c>
       <c r="AB5" t="n">
-        <v>36.68763073149869</v>
+        <v>36.68763073149947</v>
       </c>
     </row>
     <row r="6">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>483.1797025318084</v>
+        <v>483.1797025318077</v>
       </c>
       <c r="C6" t="n">
         <v>616.3325975915187</v>
@@ -2491,13 +2491,13 @@
         <v>616.3325975915187</v>
       </c>
       <c r="E6" t="n">
-        <v>585.6014539597444</v>
+        <v>585.601453959744</v>
       </c>
       <c r="F6" t="n">
         <v>309.3788311840902</v>
       </c>
       <c r="G6" t="n">
-        <v>616.332599447004</v>
+        <v>616.3325994470044</v>
       </c>
       <c r="H6" t="n">
         <v>616.3325975915187</v>
@@ -2506,7 +2506,7 @@
         <v>616.3325975915187</v>
       </c>
       <c r="J6" t="n">
-        <v>616.3275141589288</v>
+        <v>616.327514158929</v>
       </c>
       <c r="K6" t="n">
         <v>616.3325975915187</v>
@@ -2518,16 +2518,16 @@
         <v>616.3325975915187</v>
       </c>
       <c r="N6" t="n">
-        <v>48.53543799241513</v>
+        <v>616.3325975915187</v>
       </c>
       <c r="O6" t="n">
-        <v>660.4592951358111</v>
+        <v>660.4592951358119</v>
       </c>
       <c r="P6" t="n">
-        <v>670.0560943615552</v>
+        <v>670.0560943615553</v>
       </c>
       <c r="Q6" t="n">
-        <v>616.332599447004</v>
+        <v>616.3325994470044</v>
       </c>
       <c r="R6" t="n">
         <v>616.3325975915187</v>
@@ -2542,7 +2542,7 @@
         <v>616.3325975915187</v>
       </c>
       <c r="V6" t="n">
-        <v>769.9580923723264</v>
+        <v>769.9580923723265</v>
       </c>
       <c r="W6" t="n">
         <v>616.3325975915187</v>
@@ -2554,7 +2554,7 @@
         <v>616.3325975915187</v>
       </c>
       <c r="Z6" t="n">
-        <v>536.0532430247031</v>
+        <v>536.0532430247039</v>
       </c>
       <c r="AA6" t="n">
         <v>616.3325975915187</v>
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.83295955450405</v>
+        <v>5.832959554504005</v>
       </c>
       <c r="C7" t="n">
-        <v>5.775864896457348</v>
+        <v>5.775864896457976</v>
       </c>
       <c r="D7" t="n">
-        <v>5.58768481780156</v>
+        <v>5.587684817802129</v>
       </c>
       <c r="E7" t="n">
-        <v>7.411600336155108</v>
+        <v>7.411600336155181</v>
       </c>
       <c r="F7" t="n">
-        <v>6.456156820838816</v>
+        <v>6.45615682083886</v>
       </c>
       <c r="G7" t="n">
-        <v>3.313038622410776</v>
+        <v>3.313038622410857</v>
       </c>
       <c r="H7" t="n">
-        <v>6.111474121199183</v>
+        <v>6.111474121199526</v>
       </c>
       <c r="I7" t="n">
-        <v>5.328846204088229</v>
+        <v>5.328846204088628</v>
       </c>
       <c r="J7" t="n">
-        <v>4.513268872079518</v>
+        <v>4.513268872079671</v>
       </c>
       <c r="K7" t="n">
-        <v>4.766864846730623</v>
+        <v>4.766864846730675</v>
       </c>
       <c r="L7" t="n">
-        <v>6.034265355796501</v>
+        <v>6.034265355796984</v>
       </c>
       <c r="M7" t="n">
-        <v>3.575078089909185</v>
+        <v>3.57507808990919</v>
       </c>
       <c r="N7" t="n">
-        <v>5.450645155065208</v>
+        <v>5.450645155065511</v>
       </c>
       <c r="O7" t="n">
-        <v>5.122965011265152</v>
+        <v>5.122965011265599</v>
       </c>
       <c r="P7" t="n">
-        <v>4.888275917299893</v>
+        <v>4.888275917299969</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.757913116739918</v>
+        <v>5.757913116740416</v>
       </c>
       <c r="R7" t="n">
-        <v>5.788539957826383</v>
+        <v>5.788539957826507</v>
       </c>
       <c r="S7" t="n">
-        <v>4.732818590500648</v>
+        <v>4.732818590500724</v>
       </c>
       <c r="T7" t="n">
-        <v>5.522430987185798</v>
+        <v>5.522430987186176</v>
       </c>
       <c r="U7" t="n">
-        <v>4.940253180183221</v>
+        <v>4.940253180183582</v>
       </c>
       <c r="V7" t="n">
-        <v>3.408314701064241</v>
+        <v>3.408314701064301</v>
       </c>
       <c r="W7" t="n">
-        <v>5.36404580622691</v>
+        <v>5.36404580622701</v>
       </c>
       <c r="X7" t="n">
-        <v>5.440595841552073</v>
+        <v>5.440595841552142</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.152876855623815</v>
+        <v>5.152876855623812</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.405081773009169</v>
+        <v>5.405081773009085</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.346214124865686</v>
+        <v>5.34621412486599</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.479013795799972</v>
+        <v>3.479013795799959</v>
       </c>
     </row>
     <row r="8">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.153229855667409</v>
+        <v>6.153229855667569</v>
       </c>
       <c r="C8" t="n">
-        <v>6.13832117026521</v>
+        <v>6.138321170265656</v>
       </c>
       <c r="D8" t="n">
-        <v>6.084944440858981</v>
+        <v>6.084944440859116</v>
       </c>
       <c r="E8" t="n">
-        <v>7.135151128404964</v>
+        <v>7.135151128405372</v>
       </c>
       <c r="F8" t="n">
-        <v>6.331773546763693</v>
+        <v>6.331773546763746</v>
       </c>
       <c r="G8" t="n">
-        <v>5.430519706745425</v>
+        <v>5.430519706745547</v>
       </c>
       <c r="H8" t="n">
-        <v>6.234161858668682</v>
+        <v>6.234161858668937</v>
       </c>
       <c r="I8" t="n">
-        <v>6.011698033399171</v>
+        <v>6.011698033399115</v>
       </c>
       <c r="J8" t="n">
-        <v>5.74664009827127</v>
+        <v>5.746640098271561</v>
       </c>
       <c r="K8" t="n">
-        <v>5.851209306764374</v>
+        <v>5.851209306764694</v>
       </c>
       <c r="L8" t="n">
-        <v>6.211355375637939</v>
+        <v>6.211355375638457</v>
       </c>
       <c r="M8" t="n">
-        <v>5.514619926195846</v>
+        <v>5.514619926196051</v>
       </c>
       <c r="N8" t="n">
-        <v>6.045317142760813</v>
+        <v>6.045317142761179</v>
       </c>
       <c r="O8" t="n">
-        <v>5.949293350250387</v>
+        <v>5.949293350250487</v>
       </c>
       <c r="P8" t="n">
-        <v>5.881692741899995</v>
+        <v>5.881692741900428</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.133065944772951</v>
+        <v>6.133065944773317</v>
       </c>
       <c r="R8" t="n">
-        <v>6.142444446802841</v>
+        <v>6.142444446802746</v>
       </c>
       <c r="S8" t="n">
-        <v>5.838443694722387</v>
+        <v>5.838443694722971</v>
       </c>
       <c r="T8" t="n">
-        <v>6.066487081435677</v>
+        <v>6.066487081435912</v>
       </c>
       <c r="U8" t="n">
-        <v>5.898387728930802</v>
+        <v>5.898387728930818</v>
       </c>
       <c r="V8" t="n">
-        <v>4.261989770259177</v>
+        <v>4.261989770259235</v>
       </c>
       <c r="W8" t="n">
-        <v>6.020059906928418</v>
+        <v>6.02005990692834</v>
       </c>
       <c r="X8" t="n">
-        <v>6.042975095945335</v>
+        <v>6.042975095945421</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.96009337884547</v>
+        <v>5.960093378845507</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.030648352840028</v>
+        <v>6.030648352840461</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.015110547085237</v>
+        <v>6.015110547085645</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.485598235463994</v>
+        <v>5.485598235464075</v>
       </c>
     </row>
   </sheetData>
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.025528041277232</v>
+        <v>8.025528041277447</v>
       </c>
       <c r="C2" t="n">
-        <v>8.047296473427886</v>
+        <v>8.047296473427842</v>
       </c>
       <c r="D2" t="n">
-        <v>8.115566909335957</v>
+        <v>8.115566909336545</v>
       </c>
       <c r="E2" t="n">
-        <v>7.932271134523769</v>
+        <v>7.932271134523987</v>
       </c>
       <c r="F2" t="n">
-        <v>8.008585086102954</v>
+        <v>8.00858508610311</v>
       </c>
       <c r="G2" t="n">
-        <v>8.427877065713252</v>
+        <v>8.427877065713394</v>
       </c>
       <c r="H2" t="n">
-        <v>7.937848804071423</v>
+        <v>7.937848804071673</v>
       </c>
       <c r="I2" t="n">
-        <v>8.548661909565691</v>
+        <v>8.54866190956578</v>
       </c>
       <c r="J2" t="n">
-        <v>8.193818169689223</v>
+        <v>8.193818169689289</v>
       </c>
       <c r="K2" t="n">
-        <v>8.172685822403594</v>
+        <v>8.172685822403892</v>
       </c>
       <c r="L2" t="n">
-        <v>7.965126045633541</v>
+        <v>7.965126045633625</v>
       </c>
       <c r="M2" t="n">
-        <v>8.369901948337327</v>
+        <v>8.369901948337342</v>
       </c>
       <c r="N2" t="n">
-        <v>8.081636768041761</v>
+        <v>8.081636768041763</v>
       </c>
       <c r="O2" t="n">
-        <v>8.102507726951307</v>
+        <v>8.102507726951396</v>
       </c>
       <c r="P2" t="n">
-        <v>8.153773798005872</v>
+        <v>8.153773798006121</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.359480805644672</v>
+        <v>8.359480805644786</v>
       </c>
       <c r="R2" t="n">
-        <v>7.970700540865365</v>
+        <v>7.970700540865537</v>
       </c>
       <c r="S2" t="n">
-        <v>8.179173875643867</v>
+        <v>8.179173875643983</v>
       </c>
       <c r="T2" t="n">
-        <v>8.016649997881927</v>
+        <v>8.016649997882071</v>
       </c>
       <c r="U2" t="n">
-        <v>8.06861589653003</v>
+        <v>8.068615896530252</v>
       </c>
       <c r="V2" t="n">
-        <v>6.524982446529649</v>
+        <v>6.524982446529755</v>
       </c>
       <c r="W2" t="n">
-        <v>8.098716112559401</v>
+        <v>8.098716112559645</v>
       </c>
       <c r="X2" t="n">
-        <v>8.101347601857388</v>
+        <v>8.101347601857741</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.256411226958988</v>
+        <v>8.256411226959086</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.139317035599223</v>
+        <v>8.139317035599394</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.061043080103298</v>
+        <v>8.061043080103403</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.36938962426934</v>
+        <v>8.369389624269385</v>
       </c>
     </row>
     <row r="3">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="C3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="D3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="E3" t="n">
-        <v>7.945173018811484</v>
+        <v>7.94517301881144</v>
       </c>
       <c r="F3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="G3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="H3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="I3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="J3" t="n">
-        <v>7.931308757570219</v>
+        <v>7.931308757570097</v>
       </c>
       <c r="K3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="L3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="M3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="N3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="O3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="P3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="R3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="S3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="T3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="U3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="V3" t="n">
-        <v>6.372910391765343</v>
+        <v>6.372910391765443</v>
       </c>
       <c r="W3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="X3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.975434789003043</v>
+        <v>7.975434789003173</v>
       </c>
     </row>
     <row r="4">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.84557543082966</v>
+        <v>36.84557543083105</v>
       </c>
       <c r="C4" t="n">
-        <v>44.14154525449262</v>
+        <v>44.1415452544931</v>
       </c>
       <c r="D4" t="n">
-        <v>63.87188544855508</v>
+        <v>63.87188544855548</v>
       </c>
       <c r="E4" t="n">
-        <v>23.99231929030594</v>
+        <v>23.99231929030598</v>
       </c>
       <c r="F4" t="n">
-        <v>35.84731509793685</v>
+        <v>35.84731509793726</v>
       </c>
       <c r="G4" t="n">
-        <v>131.3397619637854</v>
+        <v>131.3397619637865</v>
       </c>
       <c r="H4" t="n">
-        <v>17.83459172383496</v>
+        <v>17.83459172383564</v>
       </c>
       <c r="I4" t="n">
-        <v>180.4068157824898</v>
+        <v>180.40681578249</v>
       </c>
       <c r="J4" t="n">
-        <v>89.36035065848462</v>
+        <v>89.3603506584853</v>
       </c>
       <c r="K4" t="n">
-        <v>71.88755195808136</v>
+        <v>71.88755195808217</v>
       </c>
       <c r="L4" t="n">
-        <v>23.34150168191565</v>
+        <v>23.34150168191616</v>
       </c>
       <c r="M4" t="n">
-        <v>132.7354246302788</v>
+        <v>132.7354246302795</v>
       </c>
       <c r="N4" t="n">
-        <v>54.01763996605573</v>
+        <v>54.01763996605539</v>
       </c>
       <c r="O4" t="n">
-        <v>52.96300561597473</v>
+        <v>52.96300561597506</v>
       </c>
       <c r="P4" t="n">
-        <v>66.80116544601107</v>
+        <v>66.80116544601056</v>
       </c>
       <c r="Q4" t="n">
-        <v>123.2568912861681</v>
+        <v>123.2568912861688</v>
       </c>
       <c r="R4" t="n">
-        <v>26.42797595150262</v>
+        <v>26.42797595150356</v>
       </c>
       <c r="S4" t="n">
-        <v>73.41056090064362</v>
+        <v>73.41056090064423</v>
       </c>
       <c r="T4" t="n">
-        <v>38.16111081804644</v>
+        <v>38.16111081804705</v>
       </c>
       <c r="U4" t="n">
-        <v>48.25760148065223</v>
+        <v>48.25760148065329</v>
       </c>
       <c r="V4" t="n">
-        <v>53.46263739985896</v>
+        <v>53.46263739986057</v>
       </c>
       <c r="W4" t="n">
-        <v>57.43903677016484</v>
+        <v>57.43903677016528</v>
       </c>
       <c r="X4" t="n">
-        <v>59.40618762949136</v>
+        <v>59.40618762949211</v>
       </c>
       <c r="Y4" t="n">
-        <v>96.74519973975482</v>
+        <v>96.74519973975588</v>
       </c>
       <c r="Z4" t="n">
-        <v>61.13113187539717</v>
+        <v>61.13113187539744</v>
       </c>
       <c r="AA4" t="n">
-        <v>47.95490249397511</v>
+        <v>47.95490249397531</v>
       </c>
       <c r="AB4" t="n">
-        <v>138.4934097780556</v>
+        <v>138.493409778056</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.59469290830831</v>
+        <v>18.594692908309</v>
       </c>
       <c r="C5" t="n">
-        <v>28.90103638388982</v>
+        <v>28.90103638389046</v>
       </c>
       <c r="D5" t="n">
-        <v>28.90103638388982</v>
+        <v>28.90103638389046</v>
       </c>
       <c r="E5" t="n">
-        <v>23.41321250728946</v>
+        <v>23.41321250728968</v>
       </c>
       <c r="F5" t="n">
-        <v>20.20030076600515</v>
+        <v>20.20030076600546</v>
       </c>
       <c r="G5" t="n">
-        <v>31.03812384144287</v>
+        <v>31.0381238414441</v>
       </c>
       <c r="H5" t="n">
-        <v>28.90103638388982</v>
+        <v>28.90103638389046</v>
       </c>
       <c r="I5" t="n">
-        <v>28.90103638388982</v>
+        <v>28.90103638389046</v>
       </c>
       <c r="J5" t="n">
-        <v>28.89508286425039</v>
+        <v>28.89508286425069</v>
       </c>
       <c r="K5" t="n">
-        <v>28.90103638388982</v>
+        <v>28.90103638389046</v>
       </c>
       <c r="L5" t="n">
-        <v>28.90103638388977</v>
+        <v>28.90103638389041</v>
       </c>
       <c r="M5" t="n">
-        <v>28.90103638376153</v>
+        <v>28.90103638376207</v>
       </c>
       <c r="N5" t="n">
-        <v>54.01763996605561</v>
+        <v>20.91189596997701</v>
       </c>
       <c r="O5" t="n">
-        <v>23.10738111000991</v>
+        <v>23.10738111001062</v>
       </c>
       <c r="P5" t="n">
-        <v>22.56921465348016</v>
+        <v>22.56921465348021</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.56926119227638</v>
+        <v>16.56926119227774</v>
       </c>
       <c r="R5" t="n">
-        <v>28.90103638388982</v>
+        <v>28.90103638389046</v>
       </c>
       <c r="S5" t="n">
-        <v>28.90103638388982</v>
+        <v>28.90103638389046</v>
       </c>
       <c r="T5" t="n">
-        <v>28.90103638388982</v>
+        <v>28.90103638389046</v>
       </c>
       <c r="U5" t="n">
-        <v>23.79665113239619</v>
+        <v>23.79665113239697</v>
       </c>
       <c r="V5" t="n">
-        <v>25.96696668192131</v>
+        <v>25.96696668192192</v>
       </c>
       <c r="W5" t="n">
-        <v>28.90306184844416</v>
+        <v>28.90306184844445</v>
       </c>
       <c r="X5" t="n">
-        <v>17.51385803402285</v>
+        <v>17.51385803402287</v>
       </c>
       <c r="Y5" t="n">
-        <v>39.02181255134273</v>
+        <v>39.02181255134398</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.40324728953621</v>
+        <v>18.40324728953649</v>
       </c>
       <c r="AA5" t="n">
-        <v>28.90103638388982</v>
+        <v>28.90103638389046</v>
       </c>
       <c r="AB5" t="n">
-        <v>39.66687392054321</v>
+        <v>39.66687392054305</v>
       </c>
     </row>
     <row r="6">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>452.0252571679474</v>
+        <v>452.0252571679475</v>
       </c>
       <c r="C6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="D6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="E6" t="n">
-        <v>547.6783193786301</v>
+        <v>547.6783193786302</v>
       </c>
       <c r="F6" t="n">
-        <v>289.7102671631989</v>
+        <v>289.7102671631991</v>
       </c>
       <c r="G6" t="n">
-        <v>576.3785527774567</v>
+        <v>576.3785527774562</v>
       </c>
       <c r="H6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="I6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="J6" t="n">
-        <v>576.3725963769255</v>
+        <v>576.3725963769256</v>
       </c>
       <c r="K6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="L6" t="n">
-        <v>576.3785498965652</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="M6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="N6" t="n">
-        <v>54.01763996605573</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="O6" t="n">
         <v>617.5890721156588</v>
       </c>
       <c r="P6" t="n">
-        <v>626.5516530183038</v>
+        <v>626.5516530183043</v>
       </c>
       <c r="Q6" t="n">
-        <v>576.3785527774567</v>
+        <v>576.3785527774562</v>
       </c>
       <c r="R6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="S6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="T6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="U6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="V6" t="n">
-        <v>719.8440395971069</v>
+        <v>719.8440395971073</v>
       </c>
       <c r="W6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="X6" t="n">
-        <v>576.3785498965652</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="Y6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="Z6" t="n">
-        <v>501.4045734514074</v>
+        <v>501.404573451408</v>
       </c>
       <c r="AA6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
       <c r="AB6" t="n">
-        <v>576.3785498965651</v>
+        <v>576.3785498965656</v>
       </c>
     </row>
     <row r="7">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.195434199286414</v>
+        <v>7.195434199286883</v>
       </c>
       <c r="C7" t="n">
-        <v>7.078996008489056</v>
+        <v>7.078996008489438</v>
       </c>
       <c r="D7" t="n">
-        <v>6.680145227322763</v>
+        <v>6.680145227323086</v>
       </c>
       <c r="E7" t="n">
-        <v>7.534100346827841</v>
+        <v>7.534100346828064</v>
       </c>
       <c r="F7" t="n">
-        <v>7.310090283444655</v>
+        <v>7.310090283444799</v>
       </c>
       <c r="G7" t="n">
-        <v>4.803558452429911</v>
+        <v>4.803558452430103</v>
       </c>
       <c r="H7" t="n">
-        <v>7.722896304484378</v>
+        <v>7.722896304484287</v>
       </c>
       <c r="I7" t="n">
-        <v>4.15046339796348</v>
+        <v>4.150463397963319</v>
       </c>
       <c r="J7" t="n">
-        <v>5.899143203224309</v>
+        <v>5.899143203224393</v>
       </c>
       <c r="K7" t="n">
-        <v>6.343249763651903</v>
+        <v>6.343249763652118</v>
       </c>
       <c r="L7" t="n">
-        <v>7.55745716714344</v>
+        <v>7.557457167143659</v>
       </c>
       <c r="M7" t="n">
-        <v>5.200963748329706</v>
+        <v>5.200963748329901</v>
       </c>
       <c r="N7" t="n">
-        <v>6.874225493889625</v>
+        <v>6.874225493889893</v>
       </c>
       <c r="O7" t="n">
-        <v>6.736113166515893</v>
+        <v>6.736113166515846</v>
       </c>
       <c r="P7" t="n">
-        <v>6.429412676819758</v>
+        <v>6.429412676819849</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.24442947224126</v>
+        <v>5.244429472241309</v>
       </c>
       <c r="R7" t="n">
-        <v>7.530490926851122</v>
+        <v>7.530490926851556</v>
       </c>
       <c r="S7" t="n">
-        <v>6.286619122795653</v>
+        <v>6.286619122795736</v>
       </c>
       <c r="T7" t="n">
-        <v>7.260013038398291</v>
+        <v>7.260013038398284</v>
       </c>
       <c r="U7" t="n">
-        <v>6.944607339690217</v>
+        <v>6.944607339690444</v>
       </c>
       <c r="V7" t="n">
-        <v>5.123843725337172</v>
+        <v>5.123843725337253</v>
       </c>
       <c r="W7" t="n">
-        <v>6.769719921492714</v>
+        <v>6.769719921492827</v>
       </c>
       <c r="X7" t="n">
-        <v>6.762262133116573</v>
+        <v>6.7622621331164</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.842467886181302</v>
+        <v>5.842467886181826</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.52010530910655</v>
+        <v>6.520105309106506</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.992870750413653</v>
+        <v>6.992870750413774</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.194004580620817</v>
+        <v>5.194004580620657</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.670625287241721</v>
+        <v>7.670625287242149</v>
       </c>
       <c r="C8" t="n">
-        <v>7.639413971512969</v>
+        <v>7.639413971513204</v>
       </c>
       <c r="D8" t="n">
-        <v>7.526206030928954</v>
+        <v>7.526206030929194</v>
       </c>
       <c r="E8" t="n">
-        <v>7.745231758760425</v>
+        <v>7.745231758760672</v>
       </c>
       <c r="F8" t="n">
-        <v>7.705851215746819</v>
+        <v>7.705851215746925</v>
       </c>
       <c r="G8" t="n">
-        <v>6.984663224402215</v>
+        <v>6.98466322440253</v>
       </c>
       <c r="H8" t="n">
-        <v>7.82294298882337</v>
+        <v>7.822942988823183</v>
       </c>
       <c r="I8" t="n">
-        <v>6.808287737182029</v>
+        <v>6.808287737182072</v>
       </c>
       <c r="J8" t="n">
-        <v>7.269176366334465</v>
+        <v>7.269176366334614</v>
       </c>
       <c r="K8" t="n">
-        <v>7.430036434404038</v>
+        <v>7.430036434404102</v>
       </c>
       <c r="L8" t="n">
-        <v>7.77494489567172</v>
+        <v>7.774944895671905</v>
       </c>
       <c r="M8" t="n">
-        <v>7.107508783116428</v>
+        <v>7.10750878311641</v>
       </c>
       <c r="N8" t="n">
-        <v>7.580583029419049</v>
+        <v>7.58058302941942</v>
       </c>
       <c r="O8" t="n">
-        <v>7.538612439235725</v>
+        <v>7.538612439235997</v>
       </c>
       <c r="P8" t="n">
-        <v>7.450328810082692</v>
+        <v>7.450328810082567</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.116864683320166</v>
+        <v>7.116864683320582</v>
       </c>
       <c r="R8" t="n">
-        <v>7.768249665634305</v>
+        <v>7.768249665634596</v>
       </c>
       <c r="S8" t="n">
-        <v>7.410757365583228</v>
+        <v>7.410757365583394</v>
       </c>
       <c r="T8" t="n">
-        <v>7.691130821442623</v>
+        <v>7.691130821443006</v>
       </c>
       <c r="U8" t="n">
-        <v>7.599586122040876</v>
+        <v>7.599586122040794</v>
       </c>
       <c r="V8" t="n">
-        <v>5.956653132765544</v>
+        <v>5.956653132765635</v>
       </c>
       <c r="W8" t="n">
-        <v>7.550112005456945</v>
+        <v>7.550112005457139</v>
       </c>
       <c r="X8" t="n">
-        <v>7.549350177276866</v>
+        <v>7.549350177277404</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.285904488812783</v>
+        <v>7.285904488813165</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.477137484386438</v>
+        <v>7.477137484386547</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.613973311299252</v>
+        <v>7.613973311299427</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.103830015562798</v>
+        <v>7.103830015563201</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.131191443701622</v>
+        <v>9.131191443701566</v>
       </c>
       <c r="C2" t="n">
-        <v>9.056237995155708</v>
+        <v>9.056237995155769</v>
       </c>
       <c r="D2" t="n">
-        <v>9.177436237369939</v>
+        <v>9.177436237370086</v>
       </c>
       <c r="E2" t="n">
-        <v>8.250407001978616</v>
+        <v>8.250407001978497</v>
       </c>
       <c r="F2" t="n">
-        <v>9.199079647240362</v>
+        <v>9.199079647240536</v>
       </c>
       <c r="G2" t="n">
-        <v>9.499317307769241</v>
+        <v>9.499317307769379</v>
       </c>
       <c r="H2" t="n">
-        <v>9.045472429954049</v>
+        <v>9.045472429954103</v>
       </c>
       <c r="I2" t="n">
-        <v>9.444150223668766</v>
+        <v>9.444150223668879</v>
       </c>
       <c r="J2" t="n">
-        <v>9.285725061809414</v>
+        <v>9.285725061809316</v>
       </c>
       <c r="K2" t="n">
-        <v>9.288372019996519</v>
+        <v>9.288372019996959</v>
       </c>
       <c r="L2" t="n">
-        <v>9.112439845886232</v>
+        <v>9.112439845886158</v>
       </c>
       <c r="M2" t="n">
-        <v>9.427262727620224</v>
+        <v>9.427262727620333</v>
       </c>
       <c r="N2" t="n">
-        <v>9.168379027245575</v>
+        <v>9.168379027245766</v>
       </c>
       <c r="O2" t="n">
-        <v>9.180052621661117</v>
+        <v>9.180052621660884</v>
       </c>
       <c r="P2" t="n">
-        <v>9.25729368107865</v>
+        <v>9.257293681078597</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.303330925910419</v>
+        <v>9.303330925910556</v>
       </c>
       <c r="R2" t="n">
-        <v>9.302592921469444</v>
+        <v>9.302592921469548</v>
       </c>
       <c r="S2" t="n">
-        <v>9.299819829478468</v>
+        <v>9.299819829478643</v>
       </c>
       <c r="T2" t="n">
-        <v>9.219155281723411</v>
+        <v>9.219155281723511</v>
       </c>
       <c r="U2" t="n">
-        <v>9.1342643436871</v>
+        <v>9.134264343686938</v>
       </c>
       <c r="V2" t="n">
-        <v>7.759865934246713</v>
+        <v>7.759865934246672</v>
       </c>
       <c r="W2" t="n">
-        <v>9.213706403433493</v>
+        <v>9.213706403433607</v>
       </c>
       <c r="X2" t="n">
-        <v>9.255748212054588</v>
+        <v>9.255748212054531</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.560123737214115</v>
+        <v>9.5601237372139</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.248933740593223</v>
+        <v>9.248933740593323</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.185272084053922</v>
+        <v>9.185272084054024</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.461993986536875</v>
+        <v>9.461993986536944</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="C3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="D3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="E3" t="n">
-        <v>8.336948150657657</v>
+        <v>8.336948150657811</v>
       </c>
       <c r="F3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="G3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="H3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="I3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="J3" t="n">
-        <v>9.033867370202429</v>
+        <v>9.033867370202508</v>
       </c>
       <c r="K3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="L3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="M3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="N3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="O3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="P3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="R3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="S3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="T3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="U3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="V3" t="n">
-        <v>7.582206343624429</v>
+        <v>7.582206343624291</v>
       </c>
       <c r="W3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="X3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.075011390902851</v>
+        <v>9.075011390903121</v>
       </c>
     </row>
     <row r="4">
@@ -3850,85 +3850,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.1178802794172</v>
+        <v>40.11788027941742</v>
       </c>
       <c r="C4" t="n">
-        <v>24.63525464676239</v>
+        <v>24.63525464676277</v>
       </c>
       <c r="D4" t="n">
-        <v>55.23240350989472</v>
+        <v>55.23240350989466</v>
       </c>
       <c r="E4" t="n">
-        <v>6.338492162270263</v>
+        <v>6.33849216227064</v>
       </c>
       <c r="F4" t="n">
-        <v>61.89945438497511</v>
+        <v>61.89945438497518</v>
       </c>
       <c r="G4" t="n">
-        <v>123.4450357921907</v>
+        <v>123.4450357921899</v>
       </c>
       <c r="H4" t="n">
-        <v>23.03686218938272</v>
+        <v>23.03686218938244</v>
       </c>
       <c r="I4" t="n">
         <v>126.6912512394632</v>
       </c>
       <c r="J4" t="n">
-        <v>87.81545013256391</v>
+        <v>87.81545013256401</v>
       </c>
       <c r="K4" t="n">
-        <v>78.36822393293937</v>
+        <v>78.36822393293983</v>
       </c>
       <c r="L4" t="n">
-        <v>37.31651076220608</v>
+        <v>37.31651076220719</v>
       </c>
       <c r="M4" t="n">
-        <v>119.7205019899616</v>
+        <v>119.7205019899617</v>
       </c>
       <c r="N4" t="n">
-        <v>53.65175804660212</v>
+        <v>53.65175804660257</v>
       </c>
       <c r="O4" t="n">
-        <v>50.6613736367835</v>
+        <v>50.66137363678367</v>
       </c>
       <c r="P4" t="n">
-        <v>68.42857299448262</v>
+        <v>68.42857299448255</v>
       </c>
       <c r="Q4" t="n">
-        <v>84.79632875789622</v>
+        <v>84.79632875789581</v>
       </c>
       <c r="R4" t="n">
-        <v>92.4225671279211</v>
+        <v>92.42256712792096</v>
       </c>
       <c r="S4" t="n">
-        <v>80.09745037726937</v>
+        <v>80.0974503772693</v>
       </c>
       <c r="T4" t="n">
-        <v>68.41746179449063</v>
+        <v>68.41746179449075</v>
       </c>
       <c r="U4" t="n">
-        <v>41.85688821100302</v>
+        <v>41.85688821100351</v>
       </c>
       <c r="V4" t="n">
-        <v>61.63913585430584</v>
+        <v>61.63913585430632</v>
       </c>
       <c r="W4" t="n">
-        <v>64.21390454042113</v>
+        <v>64.21390454042157</v>
       </c>
       <c r="X4" t="n">
-        <v>74.44736303269866</v>
+        <v>74.44736303269899</v>
       </c>
       <c r="Y4" t="n">
-        <v>153.5892814360047</v>
+        <v>153.5892814360045</v>
       </c>
       <c r="Z4" t="n">
-        <v>63.00235515667998</v>
+        <v>63.00235515668022</v>
       </c>
       <c r="AA4" t="n">
-        <v>57.22268475286837</v>
+        <v>57.22268475286855</v>
       </c>
       <c r="AB4" t="n">
-        <v>137.6490759173867</v>
+        <v>137.6490759173863</v>
       </c>
     </row>
     <row r="5">
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.45536562373207</v>
+        <v>20.45536562373214</v>
       </c>
       <c r="C5" t="n">
-        <v>31.55973124565509</v>
+        <v>31.55973124565528</v>
       </c>
       <c r="D5" t="n">
-        <v>31.55973124565509</v>
+        <v>31.55973124565528</v>
       </c>
       <c r="E5" t="n">
-        <v>25.64698411798063</v>
+        <v>25.64698411798096</v>
       </c>
       <c r="F5" t="n">
-        <v>22.18529600427031</v>
+        <v>22.18529600427025</v>
       </c>
       <c r="G5" t="n">
-        <v>33.86229379323196</v>
+        <v>33.862293793232</v>
       </c>
       <c r="H5" t="n">
-        <v>31.55973124565509</v>
+        <v>31.55973124565528</v>
       </c>
       <c r="I5" t="n">
-        <v>31.55973124565509</v>
+        <v>31.55973124565528</v>
       </c>
       <c r="J5" t="n">
-        <v>31.55322814241998</v>
+        <v>31.5532281424202</v>
       </c>
       <c r="K5" t="n">
-        <v>31.55973124565509</v>
+        <v>31.55973124565528</v>
       </c>
       <c r="L5" t="n">
-        <v>31.5597312456551</v>
+        <v>31.5597312456553</v>
       </c>
       <c r="M5" t="n">
-        <v>31.55973124552052</v>
+        <v>31.55973124552038</v>
       </c>
       <c r="N5" t="n">
-        <v>53.65175804660212</v>
+        <v>22.95199016005822</v>
       </c>
       <c r="O5" t="n">
-        <v>25.31747213164219</v>
+        <v>25.31747213164251</v>
       </c>
       <c r="P5" t="n">
-        <v>24.73763534448841</v>
+        <v>24.73763534448836</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.27310434434412</v>
+        <v>18.27310434434458</v>
       </c>
       <c r="R5" t="n">
-        <v>31.55973124565509</v>
+        <v>31.55973124565528</v>
       </c>
       <c r="S5" t="n">
-        <v>31.55973124565509</v>
+        <v>31.55973124565528</v>
       </c>
       <c r="T5" t="n">
-        <v>31.55973124565509</v>
+        <v>31.55973124565528</v>
       </c>
       <c r="U5" t="n">
-        <v>26.16439281619812</v>
+        <v>26.16439281619829</v>
       </c>
       <c r="V5" t="n">
-        <v>28.51242822206776</v>
+        <v>28.51242822206765</v>
       </c>
       <c r="W5" t="n">
-        <v>31.56191353624056</v>
+        <v>31.56191353624062</v>
       </c>
       <c r="X5" t="n">
-        <v>19.29084149643293</v>
+        <v>19.29084149643364</v>
       </c>
       <c r="Y5" t="n">
-        <v>42.64255438737589</v>
+        <v>42.64255438737632</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.24909633472035</v>
+        <v>20.24909633472087</v>
       </c>
       <c r="AA5" t="n">
-        <v>31.55973124565509</v>
+        <v>31.55973124565528</v>
       </c>
       <c r="AB5" t="n">
-        <v>43.15916963579472</v>
+        <v>43.15916963579476</v>
       </c>
     </row>
     <row r="6">
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>452.9661806449426</v>
+        <v>452.9661806449428</v>
       </c>
       <c r="C6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="D6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="E6" t="n">
-        <v>548.6907639554025</v>
+        <v>548.6907639554029</v>
       </c>
       <c r="F6" t="n">
-        <v>290.5298255074217</v>
+        <v>290.5298255074212</v>
       </c>
       <c r="G6" t="n">
-        <v>577.4124569103478</v>
+        <v>577.4124569103471</v>
       </c>
       <c r="H6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="I6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="J6" t="n">
-        <v>577.405950686617</v>
+        <v>577.4059506866163</v>
       </c>
       <c r="K6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="L6" t="n">
-        <v>577.4124537898529</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="M6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="N6" t="n">
-        <v>53.65175804660212</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="O6" t="n">
         <v>618.6537899161652</v>
       </c>
       <c r="P6" t="n">
-        <v>627.6230722628446</v>
+        <v>627.6230722628439</v>
       </c>
       <c r="Q6" t="n">
-        <v>577.4124569103478</v>
+        <v>577.4124569103471</v>
       </c>
       <c r="R6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="S6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="T6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="U6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="V6" t="n">
         <v>720.9814206183186</v>
       </c>
       <c r="W6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="X6" t="n">
-        <v>577.4124537898529</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="Y6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="Z6" t="n">
-        <v>502.3824185169565</v>
+        <v>502.3824185169567</v>
       </c>
       <c r="AA6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
       <c r="AB6" t="n">
-        <v>577.4124537898526</v>
+        <v>577.4124537898517</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.209905920652357</v>
+        <v>8.209905920652526</v>
       </c>
       <c r="C7" t="n">
-        <v>8.661892900387778</v>
+        <v>8.661892900387906</v>
       </c>
       <c r="D7" t="n">
-        <v>7.952456168766903</v>
+        <v>7.952456168767085</v>
       </c>
       <c r="E7" t="n">
-        <v>8.37760190899068</v>
+        <v>8.377601908990691</v>
       </c>
       <c r="F7" t="n">
-        <v>7.831809480438381</v>
+        <v>7.831809480438578</v>
       </c>
       <c r="G7" t="n">
-        <v>6.021563941959757</v>
+        <v>6.021563941959942</v>
       </c>
       <c r="H7" t="n">
-        <v>8.72784390564097</v>
+        <v>8.727843905641432</v>
       </c>
       <c r="I7" t="n">
-        <v>6.395209064040209</v>
+        <v>6.395209064040531</v>
       </c>
       <c r="J7" t="n">
-        <v>7.018079110475417</v>
+        <v>7.018079110475317</v>
       </c>
       <c r="K7" t="n">
-        <v>7.30012439686804</v>
+        <v>7.300124396868003</v>
       </c>
       <c r="L7" t="n">
-        <v>8.326233772718098</v>
+        <v>8.326233772718329</v>
       </c>
       <c r="M7" t="n">
-        <v>6.498928678569195</v>
+        <v>6.498928678569381</v>
       </c>
       <c r="N7" t="n">
-        <v>8.00095602056804</v>
+        <v>8.000956020568193</v>
       </c>
       <c r="O7" t="n">
-        <v>7.917956017992982</v>
+        <v>7.917956017992791</v>
       </c>
       <c r="P7" t="n">
-        <v>7.456493041390103</v>
+        <v>7.456493041390039</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.210250449859006</v>
+        <v>7.21025044985918</v>
       </c>
       <c r="R7" t="n">
-        <v>7.226685711279798</v>
+        <v>7.226685711279803</v>
       </c>
       <c r="S7" t="n">
-        <v>7.212495618495113</v>
+        <v>7.212495618495265</v>
       </c>
       <c r="T7" t="n">
-        <v>7.708957930163442</v>
+        <v>7.708957930163558</v>
       </c>
       <c r="U7" t="n">
-        <v>8.196327912730231</v>
+        <v>8.196327912730384</v>
       </c>
       <c r="V7" t="n">
-        <v>6.123056590846151</v>
+        <v>6.123056590846019</v>
       </c>
       <c r="W7" t="n">
-        <v>7.729821339410188</v>
+        <v>7.729821339410154</v>
       </c>
       <c r="X7" t="n">
-        <v>7.492212673538494</v>
+        <v>7.492212673538666</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.690759674461385</v>
+        <v>5.690759674461522</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.511178707670306</v>
+        <v>7.511178707670507</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.898603371894756</v>
+        <v>7.898603371894897</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.286285698182144</v>
+        <v>6.286285698182369</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.73756569781005</v>
+        <v>8.737565697810057</v>
       </c>
       <c r="C8" t="n">
-        <v>8.868267765440864</v>
+        <v>8.868267765440967</v>
       </c>
       <c r="D8" t="n">
-        <v>8.666670033926845</v>
+        <v>8.666670033926897</v>
       </c>
       <c r="E8" t="n">
-        <v>8.268904591575978</v>
+        <v>8.268904591576087</v>
       </c>
       <c r="F8" t="n">
-        <v>8.633418816129621</v>
+        <v>8.633418816129831</v>
       </c>
       <c r="G8" t="n">
-        <v>8.109988987740469</v>
+        <v>8.109988987740561</v>
       </c>
       <c r="H8" t="n">
-        <v>8.887510117802774</v>
+        <v>8.887510117802657</v>
       </c>
       <c r="I8" t="n">
-        <v>8.224831624922965</v>
+        <v>8.224831624922748</v>
       </c>
       <c r="J8" t="n">
-        <v>8.368534979697584</v>
+        <v>8.368534979697561</v>
       </c>
       <c r="K8" t="n">
-        <v>8.480792781481419</v>
+        <v>8.4807927814816</v>
       </c>
       <c r="L8" t="n">
-        <v>8.771743643399487</v>
+        <v>8.77174364339934</v>
       </c>
       <c r="M8" t="n">
-        <v>8.255136884019898</v>
+        <v>8.255136884019832</v>
       </c>
       <c r="N8" t="n">
-        <v>8.679680410931915</v>
+        <v>8.679680410931701</v>
       </c>
       <c r="O8" t="n">
-        <v>8.653588739670472</v>
+        <v>8.65358873967053</v>
       </c>
       <c r="P8" t="n">
-        <v>8.520862674138415</v>
+        <v>8.520862674138321</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.454858755094973</v>
+        <v>8.454858755094699</v>
       </c>
       <c r="R8" t="n">
-        <v>8.461598846976527</v>
+        <v>8.461598846976326</v>
       </c>
       <c r="S8" t="n">
-        <v>8.452369217547378</v>
+        <v>8.452369217547446</v>
       </c>
       <c r="T8" t="n">
-        <v>8.597596603732883</v>
+        <v>8.597596603732869</v>
       </c>
       <c r="U8" t="n">
-        <v>8.734460560920462</v>
+        <v>8.734460560920521</v>
       </c>
       <c r="V8" t="n">
-        <v>7.095948146698247</v>
+        <v>7.095948146698206</v>
       </c>
       <c r="W8" t="n">
-        <v>8.601640643137999</v>
+        <v>8.601640643137547</v>
       </c>
       <c r="X8" t="n">
-        <v>8.535569751573627</v>
+        <v>8.535569751573801</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.020278421262912</v>
+        <v>8.020278421262809</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.537384886083357</v>
+        <v>8.537384886083442</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.650002686415375</v>
+        <v>8.650002686415549</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.193114909207473</v>
+        <v>8.193114909207642</v>
       </c>
     </row>
   </sheetData>
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.258675039099764</v>
+        <v>8.258675039099801</v>
       </c>
       <c r="C2" t="n">
         <v>8.331569480118256</v>
       </c>
       <c r="D2" t="n">
-        <v>8.184198201206639</v>
+        <v>8.18419820120663</v>
       </c>
       <c r="E2" t="n">
-        <v>9.048364395893255</v>
+        <v>9.048364395893262</v>
       </c>
       <c r="F2" t="n">
-        <v>8.574378190946922</v>
+        <v>8.574378190946895</v>
       </c>
       <c r="G2" t="n">
-        <v>8.34297732122363</v>
+        <v>8.342977321223666</v>
       </c>
       <c r="H2" t="n">
-        <v>8.275870589995122</v>
+        <v>8.275870589995156</v>
       </c>
       <c r="I2" t="n">
-        <v>8.537963340871535</v>
+        <v>8.537963340871544</v>
       </c>
       <c r="J2" t="n">
-        <v>8.331496196622693</v>
+        <v>8.331496196622656</v>
       </c>
       <c r="K2" t="n">
-        <v>8.570837175939859</v>
+        <v>8.57083717593985</v>
       </c>
       <c r="L2" t="n">
-        <v>8.995109122584301</v>
+        <v>8.995109122584289</v>
       </c>
       <c r="M2" t="n">
-        <v>8.390586800140211</v>
+        <v>8.390586800140177</v>
       </c>
       <c r="N2" t="n">
-        <v>8.344718691118748</v>
+        <v>8.344718691118759</v>
       </c>
       <c r="O2" t="n">
-        <v>8.182302968819297</v>
+        <v>8.182302968819293</v>
       </c>
       <c r="P2" t="n">
-        <v>8.251015518582545</v>
+        <v>8.251015518582543</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.506007452966697</v>
+        <v>8.506007452966706</v>
       </c>
       <c r="R2" t="n">
-        <v>8.576798221825387</v>
+        <v>8.576798221825383</v>
       </c>
       <c r="S2" t="n">
-        <v>8.689757719363806</v>
+        <v>8.689757719363813</v>
       </c>
       <c r="T2" t="n">
-        <v>8.276493139532006</v>
+        <v>8.276493139532036</v>
       </c>
       <c r="U2" t="n">
-        <v>8.228692255426886</v>
+        <v>8.228692255426893</v>
       </c>
       <c r="V2" t="n">
-        <v>6.638644119817935</v>
+        <v>6.638644119817884</v>
       </c>
       <c r="W2" t="n">
-        <v>8.282689175794552</v>
+        <v>8.282689175794554</v>
       </c>
       <c r="X2" t="n">
-        <v>8.507432051268761</v>
+        <v>8.50743205126877</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.230253383649972</v>
+        <v>8.230253383649995</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.321885075525655</v>
+        <v>8.321885075525648</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.198447705049235</v>
+        <v>8.198447705049222</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.263691238982249</v>
+        <v>8.263691238982206</v>
       </c>
     </row>
     <row r="3">
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="C3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="D3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="E3" t="n">
-        <v>8.318819691115587</v>
+        <v>8.318819691115614</v>
       </c>
       <c r="F3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="G3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="H3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="I3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="J3" t="n">
-        <v>8.132111597965894</v>
+        <v>8.132111597965846</v>
       </c>
       <c r="K3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="L3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="M3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="N3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="O3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="P3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="R3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="S3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="T3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="U3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="V3" t="n">
-        <v>6.500997318421958</v>
+        <v>6.500997318421966</v>
       </c>
       <c r="W3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="X3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.169435556558954</v>
+        <v>8.16943555655897</v>
       </c>
     </row>
     <row r="4">
@@ -4622,85 +4622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.09087345351776</v>
+        <v>49.09087345351782</v>
       </c>
       <c r="C4" t="n">
-        <v>73.13892927429487</v>
+        <v>73.13892927429482</v>
       </c>
       <c r="D4" t="n">
-        <v>33.77034248317555</v>
+        <v>33.77034248317621</v>
       </c>
       <c r="E4" t="n">
-        <v>227.0709753623436</v>
+        <v>227.0709753623435</v>
       </c>
       <c r="F4" t="n">
-        <v>141.8559884784889</v>
+        <v>141.855988478489</v>
       </c>
       <c r="G4" t="n">
-        <v>66.98362021112796</v>
+        <v>66.98362021112794</v>
       </c>
       <c r="H4" t="n">
-        <v>62.01355359211871</v>
+        <v>62.01355359211864</v>
       </c>
       <c r="I4" t="n">
-        <v>134.5346708898849</v>
+        <v>134.5346708898851</v>
       </c>
       <c r="J4" t="n">
-        <v>77.13392749975864</v>
+        <v>77.13392749975878</v>
       </c>
       <c r="K4" t="n">
-        <v>130.0250403612391</v>
+        <v>130.0250403612393</v>
       </c>
       <c r="L4" t="n">
         <v>222.1156992726206</v>
       </c>
       <c r="M4" t="n">
-        <v>85.80086997869012</v>
+        <v>85.80086997869022</v>
       </c>
       <c r="N4" t="n">
-        <v>75.47458653156858</v>
+        <v>75.47458653156889</v>
       </c>
       <c r="O4" t="n">
-        <v>29.95391682061844</v>
+        <v>29.95391682061859</v>
       </c>
       <c r="P4" t="n">
-        <v>47.86949085348438</v>
+        <v>47.86949085348458</v>
       </c>
       <c r="Q4" t="n">
         <v>116.9226646612632</v>
       </c>
       <c r="R4" t="n">
-        <v>149.0394669098479</v>
+        <v>149.039466909848</v>
       </c>
       <c r="S4" t="n">
         <v>140.947369169935</v>
       </c>
       <c r="T4" t="n">
-        <v>58.05647170608833</v>
+        <v>58.05647170608839</v>
       </c>
       <c r="U4" t="n">
-        <v>43.16590917140144</v>
+        <v>43.16590917140164</v>
       </c>
       <c r="V4" t="n">
-        <v>54.51159297987312</v>
+        <v>54.5115929798731</v>
       </c>
       <c r="W4" t="n">
-        <v>59.47614462630882</v>
+        <v>59.47614462630902</v>
       </c>
       <c r="X4" t="n">
-        <v>122.5993879375322</v>
+        <v>122.5993879375325</v>
       </c>
       <c r="Y4" t="n">
-        <v>45.00141864241427</v>
+        <v>45.00141864241449</v>
       </c>
       <c r="Z4" t="n">
-        <v>63.32026815792412</v>
+        <v>63.32026815792413</v>
       </c>
       <c r="AA4" t="n">
-        <v>36.58901196753835</v>
+        <v>36.58901196753846</v>
       </c>
       <c r="AB4" t="n">
-        <v>57.51567166225513</v>
+        <v>57.5156716622551</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.66010654251439</v>
+        <v>20.66010654251436</v>
       </c>
       <c r="C5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="D5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="E5" t="n">
-        <v>25.99351751934688</v>
+        <v>25.99351751934669</v>
       </c>
       <c r="F5" t="n">
-        <v>22.43728444937869</v>
+        <v>22.43728444937872</v>
       </c>
       <c r="G5" t="n">
-        <v>34.43320215254713</v>
+        <v>34.43320215254718</v>
       </c>
       <c r="H5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="I5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="J5" t="n">
-        <v>32.06250723801268</v>
+        <v>32.06250723801267</v>
       </c>
       <c r="K5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="L5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="M5" t="n">
-        <v>32.06775245919216</v>
+        <v>32.06775245919203</v>
       </c>
       <c r="N5" t="n">
-        <v>75.47458653156858</v>
+        <v>23.22491840972781</v>
       </c>
       <c r="O5" t="n">
-        <v>25.65500597336825</v>
+        <v>25.65500597336816</v>
       </c>
       <c r="P5" t="n">
-        <v>25.05933279391538</v>
+        <v>25.05933279391522</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.41824376079355</v>
+        <v>18.41824376079353</v>
       </c>
       <c r="R5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="S5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="T5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="U5" t="n">
-        <v>26.48752248268542</v>
+        <v>26.48752248268519</v>
       </c>
       <c r="V5" t="n">
-        <v>28.90518082491085</v>
+        <v>28.90518082491078</v>
       </c>
       <c r="W5" t="n">
-        <v>32.0699943614749</v>
+        <v>32.06999436147497</v>
       </c>
       <c r="X5" t="n">
         <v>19.46377715973262</v>
       </c>
       <c r="Y5" t="n">
-        <v>43.389055884199</v>
+        <v>43.38905588419885</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.44820366553825</v>
+        <v>20.44820366553822</v>
       </c>
       <c r="AA5" t="n">
-        <v>32.06775245928394</v>
+        <v>32.06775245928378</v>
       </c>
       <c r="AB5" t="n">
-        <v>43.98399248527591</v>
+        <v>43.9839924852759</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>485.7164707816066</v>
+        <v>485.7164707816069</v>
       </c>
       <c r="C6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="D6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="E6" t="n">
-        <v>588.4659185613652</v>
+        <v>588.4659185613657</v>
       </c>
       <c r="F6" t="n">
-        <v>311.3595270108901</v>
+        <v>311.3595270108898</v>
       </c>
       <c r="G6" t="n">
         <v>619.2953877359587</v>
       </c>
       <c r="H6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="I6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="J6" t="n">
-        <v>619.290138905958</v>
+        <v>619.2901389059582</v>
       </c>
       <c r="K6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="L6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="M6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="N6" t="n">
-        <v>75.47458653156858</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="O6" t="n">
-        <v>663.5632659079167</v>
+        <v>663.5632659079173</v>
       </c>
       <c r="P6" t="n">
-        <v>673.1907699014615</v>
+        <v>673.1907699014622</v>
       </c>
       <c r="Q6" t="n">
         <v>619.2953877359587</v>
       </c>
       <c r="R6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="S6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="T6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="U6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="V6" t="n">
-        <v>773.4115079204266</v>
+        <v>773.4115079204267</v>
       </c>
       <c r="W6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="X6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="Y6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="Z6" t="n">
         <v>538.759179113227</v>
       </c>
       <c r="AA6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
       <c r="AB6" t="n">
-        <v>619.2953841272298</v>
+        <v>619.2953841272308</v>
       </c>
     </row>
     <row r="7">
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.147542830808932</v>
+        <v>7.14754283080892</v>
       </c>
       <c r="C7" t="n">
-        <v>6.734735791147281</v>
+        <v>6.734735791147263</v>
       </c>
       <c r="D7" t="n">
-        <v>7.599636715953664</v>
+        <v>7.599636715953634</v>
       </c>
       <c r="E7" t="n">
-        <v>3.493783794649263</v>
+        <v>3.493783794649244</v>
       </c>
       <c r="F7" t="n">
-        <v>5.328111269732667</v>
+        <v>5.328111269732656</v>
       </c>
       <c r="G7" t="n">
-        <v>6.646864963786863</v>
+        <v>6.646864963786895</v>
       </c>
       <c r="H7" t="n">
-        <v>7.070173533922672</v>
+        <v>7.070173533922674</v>
       </c>
       <c r="I7" t="n">
-        <v>5.532404245431838</v>
+        <v>5.532404245431833</v>
       </c>
       <c r="J7" t="n">
-        <v>6.465540610470621</v>
+        <v>6.465540610470597</v>
       </c>
       <c r="K7" t="n">
-        <v>5.330859100370827</v>
+        <v>5.330859100370859</v>
       </c>
       <c r="L7" t="n">
-        <v>2.800317480567527</v>
+        <v>2.800317480567547</v>
       </c>
       <c r="M7" t="n">
-        <v>6.397484228490872</v>
+        <v>6.397484228490851</v>
       </c>
       <c r="N7" t="n">
-        <v>6.652966640179663</v>
+        <v>6.652966640179646</v>
       </c>
       <c r="O7" t="n">
-        <v>7.601267941904456</v>
+        <v>7.601267941904381</v>
       </c>
       <c r="P7" t="n">
-        <v>7.191166192484637</v>
+        <v>7.191166192484653</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.708334712493053</v>
+        <v>5.708334712493015</v>
       </c>
       <c r="R7" t="n">
-        <v>5.31130255125704</v>
+        <v>5.311302551257014</v>
       </c>
       <c r="S7" t="n">
-        <v>4.594050741884145</v>
+        <v>4.594050741884111</v>
       </c>
       <c r="T7" t="n">
-        <v>7.059725626652519</v>
+        <v>7.05972562665253</v>
       </c>
       <c r="U7" t="n">
-        <v>7.330407392186961</v>
+        <v>7.330407392186964</v>
       </c>
       <c r="V7" t="n">
-        <v>5.336660052574935</v>
+        <v>5.336660052574845</v>
       </c>
       <c r="W7" t="n">
-        <v>7.01397136394984</v>
+        <v>7.013971363949788</v>
       </c>
       <c r="X7" t="n">
-        <v>5.70390729383271</v>
+        <v>5.703907293832705</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.32482294578364</v>
+        <v>7.324822945783683</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.773051619415559</v>
+        <v>6.773051619415567</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.511703800171018</v>
+        <v>7.511703800171039</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.134238403137086</v>
+        <v>7.134238403137076</v>
       </c>
     </row>
     <row r="8">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.793710592304594</v>
+        <v>7.793710592304583</v>
       </c>
       <c r="C8" t="n">
         <v>7.678776514739056</v>
       </c>
       <c r="D8" t="n">
-        <v>7.924937912890034</v>
+        <v>7.924937912890046</v>
       </c>
       <c r="E8" t="n">
-        <v>6.852957686524011</v>
+        <v>6.852957686524005</v>
       </c>
       <c r="F8" t="n">
-        <v>7.281566585677727</v>
+        <v>7.281566585677655</v>
       </c>
       <c r="G8" t="n">
-        <v>7.650202849367805</v>
+        <v>7.650202849367806</v>
       </c>
       <c r="H8" t="n">
-        <v>7.775702866555447</v>
+        <v>7.77570286655544</v>
       </c>
       <c r="I8" t="n">
-        <v>7.338105690588479</v>
+        <v>7.338105690588534</v>
       </c>
       <c r="J8" t="n">
-        <v>7.573201086265697</v>
+        <v>7.573201086265673</v>
       </c>
       <c r="K8" t="n">
-        <v>7.279275842367871</v>
+        <v>7.279275842367859</v>
       </c>
       <c r="L8" t="n">
-        <v>6.552143287644135</v>
+        <v>6.552143287644141</v>
       </c>
       <c r="M8" t="n">
-        <v>7.584343298995343</v>
+        <v>7.58434329899536</v>
       </c>
       <c r="N8" t="n">
-        <v>7.654720501466461</v>
+        <v>7.65472050146648</v>
       </c>
       <c r="O8" t="n">
         <v>7.923784893508744</v>
       </c>
       <c r="P8" t="n">
-        <v>7.805899840369231</v>
+        <v>7.80589984036922</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.386198725853674</v>
+        <v>7.386198725853667</v>
       </c>
       <c r="R8" t="n">
-        <v>7.276338596083544</v>
+        <v>7.276338596083517</v>
       </c>
       <c r="S8" t="n">
-        <v>7.062946234611398</v>
+        <v>7.062946234611409</v>
       </c>
       <c r="T8" t="n">
-        <v>7.771571584988926</v>
+        <v>7.771571584988849</v>
       </c>
       <c r="U8" t="n">
-        <v>7.846931766813507</v>
+        <v>7.846931766813519</v>
       </c>
       <c r="V8" t="n">
-        <v>6.108866953334781</v>
+        <v>6.108866953334741</v>
       </c>
       <c r="W8" t="n">
-        <v>7.756949285911451</v>
+        <v>7.756949285911459</v>
       </c>
       <c r="X8" t="n">
-        <v>7.385608834555935</v>
+        <v>7.385608834555931</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.845951954126516</v>
+        <v>7.845951954126535</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.686525934113807</v>
+        <v>7.686525934113845</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.899177659825964</v>
+        <v>7.899177659825947</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.792673235197685</v>
+        <v>7.792673235197663</v>
       </c>
     </row>
   </sheetData>
@@ -5218,85 +5218,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.01731981520169</v>
+        <v>11.01731981520177</v>
       </c>
       <c r="C2" t="n">
-        <v>10.58408194350753</v>
+        <v>10.58408194350757</v>
       </c>
       <c r="D2" t="n">
-        <v>10.17557786249582</v>
+        <v>10.17557786249583</v>
       </c>
       <c r="E2" t="n">
-        <v>11.27554971574192</v>
+        <v>11.27554971574177</v>
       </c>
       <c r="F2" t="n">
-        <v>11.19456975301518</v>
+        <v>11.1945697530153</v>
       </c>
       <c r="G2" t="n">
-        <v>10.29654701271296</v>
+        <v>10.29654701271312</v>
       </c>
       <c r="H2" t="n">
-        <v>10.33819702280195</v>
+        <v>10.33819702280192</v>
       </c>
       <c r="I2" t="n">
-        <v>10.87845029667239</v>
+        <v>10.87845029667265</v>
       </c>
       <c r="J2" t="n">
-        <v>10.4882928143484</v>
+        <v>10.48829281434865</v>
       </c>
       <c r="K2" t="n">
-        <v>10.53844378769313</v>
+        <v>10.53844378769314</v>
       </c>
       <c r="L2" t="n">
-        <v>10.87517361138763</v>
+        <v>10.87517361138775</v>
       </c>
       <c r="M2" t="n">
-        <v>10.29262519861655</v>
+        <v>10.29262519861666</v>
       </c>
       <c r="N2" t="n">
-        <v>10.6357689396853</v>
+        <v>10.63576893968546</v>
       </c>
       <c r="O2" t="n">
-        <v>10.62972856831172</v>
+        <v>10.62972856831188</v>
       </c>
       <c r="P2" t="n">
-        <v>10.26962879423254</v>
+        <v>10.2696287942326</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.59327613023243</v>
+        <v>10.59327613023241</v>
       </c>
       <c r="R2" t="n">
-        <v>11.27552640354322</v>
+        <v>11.27552640354329</v>
       </c>
       <c r="S2" t="n">
-        <v>10.70855648663556</v>
+        <v>10.70855648663609</v>
       </c>
       <c r="T2" t="n">
-        <v>10.41889228050869</v>
+        <v>10.41889228050881</v>
       </c>
       <c r="U2" t="n">
-        <v>10.23174208168088</v>
+        <v>10.23174208168087</v>
       </c>
       <c r="V2" t="n">
-        <v>8.72425498865673</v>
+        <v>8.724254988656879</v>
       </c>
       <c r="W2" t="n">
-        <v>10.53519802901783</v>
+        <v>10.53519802901782</v>
       </c>
       <c r="X2" t="n">
-        <v>10.54306115766322</v>
+        <v>10.5430611576636</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.30742770239973</v>
+        <v>10.30742770239974</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.7823555863051</v>
+        <v>10.78235558630526</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.23948178412961</v>
+        <v>10.23948178412971</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.28920508969899</v>
+        <v>10.28920508969907</v>
       </c>
     </row>
     <row r="3">
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="C3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="D3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="E3" t="n">
-        <v>9.682258947265627</v>
+        <v>9.682258947265945</v>
       </c>
       <c r="F3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="G3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="H3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="I3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="J3" t="n">
-        <v>10.15400254631041</v>
+        <v>10.15400254631061</v>
       </c>
       <c r="K3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="L3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="M3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="N3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="O3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="P3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="R3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="S3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="T3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="U3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="V3" t="n">
-        <v>8.451317617596981</v>
+        <v>8.451317617596866</v>
       </c>
       <c r="W3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="X3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.19416351563052</v>
+        <v>10.19416351563081</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>224.243180027112</v>
+        <v>224.2431800271125</v>
       </c>
       <c r="C4" t="n">
         <v>128.4189130118672</v>
       </c>
       <c r="D4" t="n">
-        <v>29.26086179936851</v>
+        <v>29.26086179936864</v>
       </c>
       <c r="E4" t="n">
-        <v>429.6436985588411</v>
+        <v>429.6436985588416</v>
       </c>
       <c r="F4" t="n">
-        <v>284.8270604000215</v>
+        <v>284.8270604000217</v>
       </c>
       <c r="G4" t="n">
-        <v>52.11072553472287</v>
+        <v>52.11072553472351</v>
       </c>
       <c r="H4" t="n">
-        <v>74.46263992616983</v>
+        <v>74.4626399261701</v>
       </c>
       <c r="I4" t="n">
-        <v>209.6116949516411</v>
+        <v>209.6116949516418</v>
       </c>
       <c r="J4" t="n">
-        <v>108.7389563119598</v>
+        <v>108.7389563119594</v>
       </c>
       <c r="K4" t="n">
-        <v>111.5234624233645</v>
+        <v>111.5234624233646</v>
       </c>
       <c r="L4" t="n">
-        <v>164.3723556495408</v>
+        <v>164.3723556495403</v>
       </c>
       <c r="M4" t="n">
-        <v>54.8623806178045</v>
+        <v>54.86238061780459</v>
       </c>
       <c r="N4" t="n">
-        <v>140.4524193501637</v>
+        <v>140.452419350164</v>
       </c>
       <c r="O4" t="n">
-        <v>127.2133132687375</v>
+        <v>127.2133132687378</v>
       </c>
       <c r="P4" t="n">
-        <v>48.9464348904801</v>
+        <v>48.94643489048049</v>
       </c>
       <c r="Q4" t="n">
-        <v>120.3141808018748</v>
+        <v>120.3141808018753</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3832101369778</v>
+        <v>318.3832101369779</v>
       </c>
       <c r="S4" t="n">
-        <v>137.5396954680929</v>
+        <v>137.5396954680932</v>
       </c>
       <c r="T4" t="n">
-        <v>88.23298647576691</v>
+        <v>88.23298647576709</v>
       </c>
       <c r="U4" t="n">
-        <v>39.11549970318256</v>
+        <v>39.11549970318283</v>
       </c>
       <c r="V4" t="n">
-        <v>85.31066720609034</v>
+        <v>85.31066720609091</v>
       </c>
       <c r="W4" t="n">
-        <v>113.5370209213247</v>
+        <v>113.5370209213252</v>
       </c>
       <c r="X4" t="n">
-        <v>117.271758873731</v>
+        <v>117.271758873732</v>
       </c>
       <c r="Y4" t="n">
-        <v>62.19680681582293</v>
+        <v>62.19680681582309</v>
       </c>
       <c r="Z4" t="n">
-        <v>160.2258592299973</v>
+        <v>160.2258592299971</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.90614246808286</v>
+        <v>44.90614246808394</v>
       </c>
       <c r="AB4" t="n">
-        <v>58.85133625128065</v>
+        <v>58.85133625128096</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.25049571420602</v>
+        <v>22.25049571420626</v>
       </c>
       <c r="C5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="D5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="E5" t="n">
-        <v>27.92669502419951</v>
+        <v>27.92669502419978</v>
       </c>
       <c r="F5" t="n">
-        <v>24.14189617813175</v>
+        <v>24.14189617813243</v>
       </c>
       <c r="G5" t="n">
-        <v>36.90881402009991</v>
+        <v>36.90881402009997</v>
       </c>
       <c r="H5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="I5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="J5" t="n">
-        <v>34.38500765266339</v>
+        <v>34.38500765266308</v>
       </c>
       <c r="K5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="L5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="M5" t="n">
-        <v>34.39133243810723</v>
+        <v>34.39133243810684</v>
       </c>
       <c r="N5" t="n">
-        <v>140.4524193501637</v>
+        <v>24.98015284882647</v>
       </c>
       <c r="O5" t="n">
-        <v>27.56642669356351</v>
+        <v>27.56642669356303</v>
       </c>
       <c r="P5" t="n">
-        <v>26.93246848347906</v>
+        <v>26.93246848347913</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.86454420890099</v>
+        <v>19.86454420890195</v>
       </c>
       <c r="R5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="S5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="T5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="U5" t="n">
-        <v>28.38070320128106</v>
+        <v>28.38070320128142</v>
       </c>
       <c r="V5" t="n">
-        <v>30.94225207073802</v>
+        <v>30.94225207073804</v>
       </c>
       <c r="W5" t="n">
-        <v>34.39371841769523</v>
+        <v>34.39371841769518</v>
       </c>
       <c r="X5" t="n">
-        <v>20.97727599257119</v>
+        <v>20.97727599257089</v>
       </c>
       <c r="Y5" t="n">
-        <v>46.31753834334217</v>
+        <v>46.31753834334243</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.02497344306116</v>
+        <v>22.02497344306147</v>
       </c>
       <c r="AA5" t="n">
-        <v>34.39133243810068</v>
+        <v>34.39133243810034</v>
       </c>
       <c r="AB5" t="n">
-        <v>47.0734515556901</v>
+        <v>47.07345155568997</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>455.0291549419579</v>
+        <v>455.0291549419582</v>
       </c>
       <c r="C6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="D6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="E6" t="n">
-        <v>551.1577253181175</v>
+        <v>551.1577253181183</v>
       </c>
       <c r="F6" t="n">
-        <v>291.9072686252376</v>
+        <v>291.9072686252384</v>
       </c>
       <c r="G6" t="n">
-        <v>580.0006326158949</v>
+        <v>580.0006326158958</v>
       </c>
       <c r="H6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="I6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="J6" t="n">
-        <v>579.9943008863551</v>
+        <v>579.9943008863553</v>
       </c>
       <c r="K6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="L6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="M6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="N6" t="n">
-        <v>140.4524193501637</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="O6" t="n">
-        <v>621.4160166808077</v>
+        <v>621.4160166808086</v>
       </c>
       <c r="P6" t="n">
-        <v>630.4231521466278</v>
+        <v>630.4231521466282</v>
       </c>
       <c r="Q6" t="n">
-        <v>580.0006326158949</v>
+        <v>580.0006326158958</v>
       </c>
       <c r="R6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="S6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="T6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="U6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="V6" t="n">
-        <v>724.1778382241937</v>
+        <v>724.1778382241943</v>
       </c>
       <c r="W6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="X6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="Y6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="Z6" t="n">
-        <v>504.6539444758901</v>
+        <v>504.6539444758908</v>
       </c>
       <c r="AA6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
       <c r="AB6" t="n">
-        <v>580.0006256717912</v>
+        <v>580.0006256717928</v>
       </c>
     </row>
     <row r="7">
@@ -5658,85 +5658,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.668736039628945</v>
+        <v>4.668736039628901</v>
       </c>
       <c r="C7" t="n">
-        <v>7.288290684576229</v>
+        <v>7.28829068457634</v>
       </c>
       <c r="D7" t="n">
-        <v>9.68448992179321</v>
+        <v>9.684489921793352</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.324407593843099</v>
+        <v>-0.3244075938432153</v>
       </c>
       <c r="F7" t="n">
-        <v>3.747361330230362</v>
+        <v>3.747361330230509</v>
       </c>
       <c r="G7" t="n">
-        <v>8.957430721440396</v>
+        <v>8.957430721440538</v>
       </c>
       <c r="H7" t="n">
-        <v>8.741854174978565</v>
+        <v>8.74185417497875</v>
       </c>
       <c r="I7" t="n">
-        <v>5.576066717691046</v>
+        <v>5.576066717691011</v>
       </c>
       <c r="J7" t="n">
-        <v>7.555504301489536</v>
+        <v>7.555504301489757</v>
       </c>
       <c r="K7" t="n">
-        <v>7.555245711796216</v>
+        <v>7.555245711796469</v>
       </c>
       <c r="L7" t="n">
-        <v>5.543801064757249</v>
+        <v>5.543801064757404</v>
       </c>
       <c r="M7" t="n">
-        <v>9.003444377239861</v>
+        <v>9.003444377239903</v>
       </c>
       <c r="N7" t="n">
-        <v>6.975316060799535</v>
+        <v>6.975316060799623</v>
       </c>
       <c r="O7" t="n">
-        <v>6.971069632061936</v>
+        <v>6.971069632062134</v>
       </c>
       <c r="P7" t="n">
-        <v>9.114734412524674</v>
+        <v>9.114734412524593</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.230231286735187</v>
+        <v>7.230231286734995</v>
       </c>
       <c r="R7" t="n">
-        <v>3.268930303499031</v>
+        <v>3.268930303499032</v>
       </c>
       <c r="S7" t="n">
-        <v>6.517032695483139</v>
+        <v>6.517032695483427</v>
       </c>
       <c r="T7" t="n">
-        <v>8.260501263633977</v>
+        <v>8.260501263634433</v>
       </c>
       <c r="U7" t="n">
-        <v>9.346812689862327</v>
+        <v>9.346812689862574</v>
       </c>
       <c r="V7" t="n">
-        <v>6.352340888729421</v>
+        <v>6.352340888729299</v>
       </c>
       <c r="W7" t="n">
-        <v>7.558099108259106</v>
+        <v>7.558099108258928</v>
       </c>
       <c r="X7" t="n">
-        <v>7.52937593980822</v>
+        <v>7.529375939808451</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.904491381050491</v>
+        <v>8.904491381050372</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.071159515743021</v>
+        <v>6.071159515743121</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.30413979434943</v>
+        <v>9.304139794349561</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.019181331859604</v>
+        <v>9.019181331859809</v>
       </c>
     </row>
     <row r="8">
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.503232705128251</v>
+        <v>8.503232705128326</v>
       </c>
       <c r="C8" t="n">
-        <v>9.261900544910358</v>
+        <v>9.261900544910537</v>
       </c>
       <c r="D8" t="n">
-        <v>9.943674753066322</v>
+        <v>9.943674753066411</v>
       </c>
       <c r="E8" t="n">
-        <v>6.722484550182867</v>
+        <v>6.722484550182959</v>
       </c>
       <c r="F8" t="n">
-        <v>8.261254213918507</v>
+        <v>8.261254213918615</v>
       </c>
       <c r="G8" t="n">
-        <v>9.733829650122848</v>
+        <v>9.733829650122983</v>
       </c>
       <c r="H8" t="n">
-        <v>9.677391644569932</v>
+        <v>9.677391644569971</v>
       </c>
       <c r="I8" t="n">
-        <v>8.77720153660878</v>
+        <v>8.777201536608766</v>
       </c>
       <c r="J8" t="n">
-        <v>9.305967832032241</v>
+        <v>9.305967832032591</v>
       </c>
       <c r="K8" t="n">
-        <v>9.337727777216207</v>
+        <v>9.33772777721645</v>
       </c>
       <c r="L8" t="n">
-        <v>8.759243876414445</v>
+        <v>8.759243876414534</v>
       </c>
       <c r="M8" t="n">
-        <v>9.75084419605183</v>
+        <v>9.750844196052055</v>
       </c>
       <c r="N8" t="n">
-        <v>9.171183089879152</v>
+        <v>9.171183089879078</v>
       </c>
       <c r="O8" t="n">
-        <v>9.163210579897237</v>
+        <v>9.16321057989736</v>
       </c>
       <c r="P8" t="n">
-        <v>9.778485112382425</v>
+        <v>9.778485112382819</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.244677520593207</v>
+        <v>9.244677520593237</v>
       </c>
       <c r="R8" t="n">
-        <v>8.124523222614403</v>
+        <v>8.124523222614545</v>
       </c>
       <c r="S8" t="n">
-        <v>9.03545024514813</v>
+        <v>9.035450245148404</v>
       </c>
       <c r="T8" t="n">
-        <v>9.539069793634063</v>
+        <v>9.539069793634507</v>
       </c>
       <c r="U8" t="n">
-        <v>9.84619475560938</v>
+        <v>9.846194755609451</v>
       </c>
       <c r="V8" t="n">
-        <v>7.769213887980039</v>
+        <v>7.769213887980194</v>
       </c>
       <c r="W8" t="n">
-        <v>9.335780323024688</v>
+        <v>9.335780323024794</v>
       </c>
       <c r="X8" t="n">
-        <v>9.330574318489981</v>
+        <v>9.330574318490289</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.720622771224198</v>
+        <v>9.7206227712244</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.906375627122188</v>
+        <v>8.906375627122205</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.834518154609349</v>
+        <v>9.834518154609421</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.754584451637218</v>
+        <v>9.754584451637212</v>
       </c>
     </row>
   </sheetData>
@@ -5990,85 +5990,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.28590620414736</v>
+        <v>12.28590620414735</v>
       </c>
       <c r="C2" t="n">
-        <v>11.53215546846686</v>
+        <v>11.53215546846685</v>
       </c>
       <c r="D2" t="n">
-        <v>11.37650426139171</v>
+        <v>11.37650426139174</v>
       </c>
       <c r="E2" t="n">
-        <v>11.49449078424323</v>
+        <v>11.49449078424319</v>
       </c>
       <c r="F2" t="n">
-        <v>11.70485038135381</v>
+        <v>11.70485038135379</v>
       </c>
       <c r="G2" t="n">
-        <v>11.11301478247616</v>
+        <v>11.11301478247604</v>
       </c>
       <c r="H2" t="n">
-        <v>11.00374311942988</v>
+        <v>11.00374311942997</v>
       </c>
       <c r="I2" t="n">
-        <v>11.24736886874601</v>
+        <v>11.24736886874604</v>
       </c>
       <c r="J2" t="n">
-        <v>11.23715365856637</v>
+        <v>11.23715365856608</v>
       </c>
       <c r="K2" t="n">
-        <v>11.12320956405868</v>
+        <v>11.12320956405881</v>
       </c>
       <c r="L2" t="n">
         <v>11.50143380674358</v>
       </c>
       <c r="M2" t="n">
-        <v>10.9921466169524</v>
+        <v>10.99214661695243</v>
       </c>
       <c r="N2" t="n">
-        <v>11.2275029682067</v>
+        <v>11.22750296820666</v>
       </c>
       <c r="O2" t="n">
-        <v>11.38472111496409</v>
+        <v>11.38472111496423</v>
       </c>
       <c r="P2" t="n">
-        <v>11.09980765975819</v>
+        <v>11.09980765975826</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.41708052117027</v>
+        <v>11.41708052117025</v>
       </c>
       <c r="R2" t="n">
-        <v>12.23844648906658</v>
+        <v>12.23844648906665</v>
       </c>
       <c r="S2" t="n">
-        <v>11.39341420993271</v>
+        <v>11.39341420993257</v>
       </c>
       <c r="T2" t="n">
-        <v>11.04809804461225</v>
+        <v>11.04809804461244</v>
       </c>
       <c r="U2" t="n">
-        <v>10.98845878006046</v>
+        <v>10.98845878006042</v>
       </c>
       <c r="V2" t="n">
-        <v>9.615579692959763</v>
+        <v>9.615579692959766</v>
       </c>
       <c r="W2" t="n">
-        <v>11.37582162067835</v>
+        <v>11.37582162067839</v>
       </c>
       <c r="X2" t="n">
-        <v>11.28681205200628</v>
+        <v>11.28681205200624</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.13726430264964</v>
+        <v>11.13726430264961</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.4856595914136</v>
+        <v>11.48565959141369</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.01747151242635</v>
+        <v>11.01747151242665</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.12115610526943</v>
+        <v>11.12115610526946</v>
       </c>
     </row>
     <row r="3">
@@ -6078,85 +6078,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="C3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="D3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="E3" t="n">
-        <v>10.00725567882942</v>
+        <v>10.00725567882907</v>
       </c>
       <c r="F3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="G3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="H3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="I3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="J3" t="n">
-        <v>10.91197580576821</v>
+        <v>10.91197580576799</v>
       </c>
       <c r="K3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="L3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="M3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="N3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="O3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="P3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="R3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="S3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="T3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="U3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="V3" t="n">
-        <v>9.298993710127323</v>
+        <v>9.298993710127313</v>
       </c>
       <c r="W3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="X3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.95224744358461</v>
+        <v>10.95224744358456</v>
       </c>
     </row>
     <row r="4">
@@ -6166,85 +6166,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>342.3062070706803</v>
+        <v>342.3062070706807</v>
       </c>
       <c r="C4" t="n">
-        <v>179.0159045667244</v>
+        <v>179.0159045667246</v>
       </c>
       <c r="D4" t="n">
-        <v>142.0386463420246</v>
+        <v>142.0386463420241</v>
       </c>
       <c r="E4" t="n">
-        <v>378.860476347798</v>
+        <v>378.8604763477982</v>
       </c>
       <c r="F4" t="n">
         <v>231.1369399547593</v>
       </c>
       <c r="G4" t="n">
-        <v>68.89860731967575</v>
+        <v>68.89860731967592</v>
       </c>
       <c r="H4" t="n">
-        <v>51.84267898269693</v>
+        <v>51.84267898269673</v>
       </c>
       <c r="I4" t="n">
-        <v>113.7054109140687</v>
+        <v>113.7054109140682</v>
       </c>
       <c r="J4" t="n">
-        <v>110.5475660736097</v>
+        <v>110.5475660736102</v>
       </c>
       <c r="K4" t="n">
-        <v>76.70937616765896</v>
+        <v>76.70937616765892</v>
       </c>
       <c r="L4" t="n">
         <v>150.2229373374542</v>
       </c>
       <c r="M4" t="n">
-        <v>46.28981416094185</v>
+        <v>46.28981416094155</v>
       </c>
       <c r="N4" t="n">
-        <v>104.4872820939393</v>
+        <v>104.4872820939395</v>
       </c>
       <c r="O4" t="n">
-        <v>129.4346935509295</v>
+        <v>129.434693550929</v>
       </c>
       <c r="P4" t="n">
-        <v>66.45777821178687</v>
+        <v>66.45777821178679</v>
       </c>
       <c r="Q4" t="n">
-        <v>145.3639159869947</v>
+        <v>145.3639159869949</v>
       </c>
       <c r="R4" t="n">
-        <v>379.2946863763549</v>
+        <v>379.2946863763544</v>
       </c>
       <c r="S4" t="n">
-        <v>132.0248601241813</v>
+        <v>132.0248601241814</v>
       </c>
       <c r="T4" t="n">
-        <v>60.92239617332969</v>
+        <v>60.92239617332959</v>
       </c>
       <c r="U4" t="n">
-        <v>41.71019057454306</v>
+        <v>41.71019057454328</v>
       </c>
       <c r="V4" t="n">
-        <v>99.46486133234656</v>
+        <v>99.4648613323466</v>
       </c>
       <c r="W4" t="n">
-        <v>137.788022856282</v>
+        <v>137.7880228562816</v>
       </c>
       <c r="X4" t="n">
-        <v>114.5597040541106</v>
+        <v>114.5597040541103</v>
       </c>
       <c r="Y4" t="n">
-        <v>83.60339748811425</v>
+        <v>83.60339748811417</v>
       </c>
       <c r="Z4" t="n">
-        <v>147.2384841132322</v>
+        <v>147.2384841132317</v>
       </c>
       <c r="AA4" t="n">
-        <v>52.45926788222297</v>
+        <v>52.45926788222258</v>
       </c>
       <c r="AB4" t="n">
-        <v>82.96317487909137</v>
+        <v>82.96317487909093</v>
       </c>
     </row>
     <row r="5">
@@ -6257,82 +6257,82 @@
         <v>23.42608672122078</v>
       </c>
       <c r="C5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="D5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="E5" t="n">
-        <v>29.39434932646338</v>
+        <v>29.39434932646311</v>
       </c>
       <c r="F5" t="n">
-        <v>25.41480734892455</v>
+        <v>25.41480734892475</v>
       </c>
       <c r="G5" t="n">
         <v>38.83863448482361</v>
       </c>
       <c r="H5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="I5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="J5" t="n">
-        <v>36.1854065666246</v>
+        <v>36.18540656662486</v>
       </c>
       <c r="K5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="L5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="M5" t="n">
-        <v>36.19161834631171</v>
+        <v>36.19161834631151</v>
       </c>
       <c r="N5" t="n">
-        <v>104.4872820939394</v>
+        <v>26.29619569737227</v>
       </c>
       <c r="O5" t="n">
-        <v>29.0155437353035</v>
+        <v>29.01554373530333</v>
       </c>
       <c r="P5" t="n">
-        <v>28.34896582539787</v>
+        <v>28.34896582539723</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.91736841214415</v>
+        <v>20.91736841214438</v>
       </c>
       <c r="R5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="S5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="T5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="U5" t="n">
-        <v>29.83900555237185</v>
+        <v>29.8390055523717</v>
       </c>
       <c r="V5" t="n">
-        <v>32.53192256236731</v>
+        <v>32.5319225623673</v>
       </c>
       <c r="W5" t="n">
-        <v>36.19412708819951</v>
+        <v>36.19412708819959</v>
       </c>
       <c r="X5" t="n">
-        <v>22.08735471980098</v>
+        <v>22.08735471980076</v>
       </c>
       <c r="Y5" t="n">
-        <v>48.67551397181676</v>
+        <v>48.67551397181733</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.18896042233667</v>
+        <v>23.18896042233666</v>
       </c>
       <c r="AA5" t="n">
-        <v>36.19161834624307</v>
+        <v>36.19161834624289</v>
       </c>
       <c r="AB5" t="n">
-        <v>49.52628351649864</v>
+        <v>49.52628351649827</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>455.3507758099723</v>
+        <v>455.3507758099726</v>
       </c>
       <c r="C6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="D6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="E6" t="n">
-        <v>551.5068305399848</v>
+        <v>551.5068305399842</v>
       </c>
       <c r="F6" t="n">
-        <v>292.1822509171564</v>
+        <v>292.1822509171561</v>
       </c>
       <c r="G6" t="n">
-        <v>580.3579843836861</v>
+        <v>580.3579843836857</v>
       </c>
       <c r="H6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="I6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="J6" t="n">
-        <v>580.3517651951908</v>
+        <v>580.3517651951898</v>
       </c>
       <c r="K6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="L6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="M6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="N6" t="n">
-        <v>104.4872820939393</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="O6" t="n">
-        <v>621.7852096220001</v>
+        <v>621.7852096219993</v>
       </c>
       <c r="P6" t="n">
-        <v>630.7949203398722</v>
+        <v>630.7949203398708</v>
       </c>
       <c r="Q6" t="n">
-        <v>580.3579843836861</v>
+        <v>580.3579843836857</v>
       </c>
       <c r="R6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="S6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="T6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="U6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="V6" t="n">
-        <v>724.5774418387232</v>
+        <v>724.5774418387226</v>
       </c>
       <c r="W6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="X6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="Y6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="Z6" t="n">
-        <v>504.9897536884315</v>
+        <v>504.989753688431</v>
       </c>
       <c r="AA6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
       <c r="AB6" t="n">
-        <v>580.3579769748081</v>
+        <v>580.3579769748069</v>
       </c>
     </row>
     <row r="7">
@@ -6430,85 +6430,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.339420054394299</v>
+        <v>2.339420054394318</v>
       </c>
       <c r="C7" t="n">
-        <v>6.882601776468994</v>
+        <v>6.882601776469214</v>
       </c>
       <c r="D7" t="n">
-        <v>7.799055607638274</v>
+        <v>7.799055607638217</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6171615136913382</v>
+        <v>0.6171615136910273</v>
       </c>
       <c r="F7" t="n">
-        <v>5.900565997597949</v>
+        <v>5.900565997597861</v>
       </c>
       <c r="G7" t="n">
-        <v>9.318067934961025</v>
+        <v>9.318067934961142</v>
       </c>
       <c r="H7" t="n">
-        <v>9.989106854265756</v>
+        <v>9.989106854265744</v>
       </c>
       <c r="I7" t="n">
-        <v>8.559970391513357</v>
+        <v>8.559970391513149</v>
       </c>
       <c r="J7" t="n">
-        <v>8.317728107625925</v>
+        <v>8.3177281076256</v>
       </c>
       <c r="K7" t="n">
-        <v>9.280360507700166</v>
+        <v>9.280360507700196</v>
       </c>
       <c r="L7" t="n">
-        <v>7.031190253644662</v>
+        <v>7.031190253644531</v>
       </c>
       <c r="M7" t="n">
-        <v>10.0538924030595</v>
+        <v>10.05389240305951</v>
       </c>
       <c r="N7" t="n">
-        <v>8.662157314387649</v>
+        <v>8.662157314387738</v>
       </c>
       <c r="O7" t="n">
-        <v>7.697177481272922</v>
+        <v>7.697177481272872</v>
       </c>
       <c r="P7" t="n">
-        <v>9.392632422096131</v>
+        <v>9.392632422096076</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.552689552770313</v>
+        <v>7.55268955277023</v>
       </c>
       <c r="R7" t="n">
-        <v>2.782549026304701</v>
+        <v>2.782549026304705</v>
       </c>
       <c r="S7" t="n">
-        <v>7.65923061352955</v>
+        <v>7.659230613529513</v>
       </c>
       <c r="T7" t="n">
-        <v>9.723490841552232</v>
+        <v>9.723490841552229</v>
       </c>
       <c r="U7" t="n">
-        <v>10.06292201385676</v>
+        <v>10.06292201385673</v>
       </c>
       <c r="V7" t="n">
-        <v>6.882103878934254</v>
+        <v>6.88210387893423</v>
       </c>
       <c r="W7" t="n">
-        <v>7.779104274450932</v>
+        <v>7.779104274450805</v>
       </c>
       <c r="X7" t="n">
-        <v>8.321894473917871</v>
+        <v>8.321894473917958</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.189925842677955</v>
+        <v>9.189925842677845</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.104501351008129</v>
+        <v>7.104501351008202</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.894944672901401</v>
+        <v>9.894944672901067</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.295142123414518</v>
+        <v>9.295142123414433</v>
       </c>
     </row>
     <row r="8">
@@ -6518,85 +6518,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.367042294613455</v>
+        <v>8.367042294613512</v>
       </c>
       <c r="C8" t="n">
-        <v>9.68045372073802</v>
+        <v>9.680453720738123</v>
       </c>
       <c r="D8" t="n">
-        <v>9.941791927409996</v>
+        <v>9.941791927409959</v>
       </c>
       <c r="E8" t="n">
-        <v>7.221968014650839</v>
+        <v>7.221968014650831</v>
       </c>
       <c r="F8" t="n">
-        <v>9.406319224676288</v>
+        <v>9.406319224676212</v>
       </c>
       <c r="G8" t="n">
-        <v>10.36945789823136</v>
+        <v>10.36945789823143</v>
       </c>
       <c r="H8" t="n">
-        <v>10.56551108194286</v>
+        <v>10.56551108194287</v>
       </c>
       <c r="I8" t="n">
-        <v>10.15887518631897</v>
+        <v>10.15887518631898</v>
       </c>
       <c r="J8" t="n">
-        <v>10.05676268853475</v>
+        <v>10.05676268853476</v>
       </c>
       <c r="K8" t="n">
-        <v>10.36249568024369</v>
+        <v>10.36249568024403</v>
       </c>
       <c r="L8" t="n">
-        <v>9.717340289653073</v>
+        <v>9.717340289653123</v>
       </c>
       <c r="M8" t="n">
-        <v>10.58339221062586</v>
+        <v>10.58339221062587</v>
       </c>
       <c r="N8" t="n">
-        <v>10.18550466133783</v>
+        <v>10.18550466133779</v>
       </c>
       <c r="O8" t="n">
-        <v>9.903653908819836</v>
+        <v>9.903653908820193</v>
       </c>
       <c r="P8" t="n">
-        <v>10.39017785478275</v>
+        <v>10.39017785478279</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.870270847101537</v>
+        <v>9.870270847101414</v>
       </c>
       <c r="R8" t="n">
-        <v>8.521207673920138</v>
+        <v>8.521207673920399</v>
       </c>
       <c r="S8" t="n">
-        <v>9.895081058035643</v>
+        <v>9.895081058035579</v>
       </c>
       <c r="T8" t="n">
-        <v>10.48900987487259</v>
+        <v>10.48900987487237</v>
       </c>
       <c r="U8" t="n">
-        <v>10.5838128754223</v>
+        <v>10.58381287542226</v>
       </c>
       <c r="V8" t="n">
-        <v>8.51588711759605</v>
+        <v>8.515887117596021</v>
       </c>
       <c r="W8" t="n">
-        <v>9.932031366515224</v>
+        <v>9.932031366515288</v>
       </c>
       <c r="X8" t="n">
-        <v>10.08999306837034</v>
+        <v>10.08999306836995</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.33540235805142</v>
+        <v>10.33540235805133</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.734922857252055</v>
+        <v>9.734922857252196</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.53639538234148</v>
+        <v>10.53639538234137</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.36716790371073</v>
+        <v>10.36716790371052</v>
       </c>
     </row>
   </sheetData>
@@ -6762,85 +6762,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.046119890478547</v>
+        <v>7.046119890478169</v>
       </c>
       <c r="C2" t="n">
-        <v>7.032076313242017</v>
+        <v>7.032076313241649</v>
       </c>
       <c r="D2" t="n">
-        <v>6.901514132730655</v>
+        <v>6.901514132730928</v>
       </c>
       <c r="E2" t="n">
-        <v>8.00020707213015</v>
+        <v>8.00020707213007</v>
       </c>
       <c r="F2" t="n">
-        <v>7.208791836634554</v>
+        <v>7.208791836634204</v>
       </c>
       <c r="G2" t="n">
-        <v>7.345396116590504</v>
+        <v>7.345396116590647</v>
       </c>
       <c r="H2" t="n">
-        <v>6.923673197425207</v>
+        <v>6.923673197424782</v>
       </c>
       <c r="I2" t="n">
-        <v>7.338598200587849</v>
+        <v>7.338598200587517</v>
       </c>
       <c r="J2" t="n">
-        <v>7.139135036335727</v>
+        <v>7.13913503633559</v>
       </c>
       <c r="K2" t="n">
-        <v>7.369407325953157</v>
+        <v>7.369407325953249</v>
       </c>
       <c r="L2" t="n">
-        <v>7.164375922185807</v>
+        <v>7.164375922185696</v>
       </c>
       <c r="M2" t="n">
-        <v>7.457931233446187</v>
+        <v>7.457931233445747</v>
       </c>
       <c r="N2" t="n">
-        <v>7.059793775814567</v>
+        <v>7.059793775814806</v>
       </c>
       <c r="O2" t="n">
-        <v>6.970836054384344</v>
+        <v>6.970836054383899</v>
       </c>
       <c r="P2" t="n">
-        <v>7.049707046492851</v>
+        <v>7.049707046492785</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.206736953446069</v>
+        <v>7.206736953446008</v>
       </c>
       <c r="R2" t="n">
-        <v>7.213265577596247</v>
+        <v>7.213265577595839</v>
       </c>
       <c r="S2" t="n">
-        <v>7.293386655268947</v>
+        <v>7.293386655268738</v>
       </c>
       <c r="T2" t="n">
-        <v>7.038690330003875</v>
+        <v>7.038690330003448</v>
       </c>
       <c r="U2" t="n">
-        <v>7.019317673946937</v>
+        <v>7.019317673947056</v>
       </c>
       <c r="V2" t="n">
-        <v>5.333664057964938</v>
+        <v>5.33366405796496</v>
       </c>
       <c r="W2" t="n">
-        <v>6.953282216986326</v>
+        <v>6.953282216985905</v>
       </c>
       <c r="X2" t="n">
-        <v>7.219560984218388</v>
+        <v>7.219560984218305</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.034209019649951</v>
+        <v>7.03420901964964</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.955463321952229</v>
+        <v>6.955463321951847</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.979214954150637</v>
+        <v>6.979214954150302</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.257719344029097</v>
+        <v>7.257719344028578</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="C3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="D3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="E3" t="n">
-        <v>7.629724785231989</v>
+        <v>7.629724785232148</v>
       </c>
       <c r="F3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="G3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="H3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="I3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="J3" t="n">
-        <v>6.849839981243583</v>
+        <v>6.849839981243814</v>
       </c>
       <c r="K3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="L3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="M3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="N3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="O3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="P3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="R3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="S3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="T3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="U3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="V3" t="n">
-        <v>5.196014577666878</v>
+        <v>5.196014577666892</v>
       </c>
       <c r="W3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="X3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.892045509967283</v>
+        <v>6.89204550996761</v>
       </c>
     </row>
     <row r="4">
@@ -6938,85 +6938,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.47002236582917</v>
+        <v>61.47002236583047</v>
       </c>
       <c r="C4" t="n">
-        <v>63.13906607312224</v>
+        <v>63.13906607312199</v>
       </c>
       <c r="D4" t="n">
-        <v>28.17248193970284</v>
+        <v>28.17248193970289</v>
       </c>
       <c r="E4" t="n">
-        <v>128.7891389444833</v>
+        <v>128.7891389444829</v>
       </c>
       <c r="F4" t="n">
-        <v>114.1936577315241</v>
+        <v>114.1936577315243</v>
       </c>
       <c r="G4" t="n">
-        <v>134.2257782267871</v>
+        <v>134.2257782267868</v>
       </c>
       <c r="H4" t="n">
-        <v>35.72585453453525</v>
+        <v>35.72585453453473</v>
       </c>
       <c r="I4" t="n">
-        <v>152.4641508934737</v>
+        <v>152.4641508934733</v>
       </c>
       <c r="J4" t="n">
-        <v>97.27955933905274</v>
+        <v>97.27955933905309</v>
       </c>
       <c r="K4" t="n">
-        <v>144.7548291937265</v>
+        <v>144.7548291937262</v>
       </c>
       <c r="L4" t="n">
-        <v>94.86929003144232</v>
+        <v>94.86929003144502</v>
       </c>
       <c r="M4" t="n">
-        <v>173.2426980289855</v>
+        <v>173.2426980289876</v>
       </c>
       <c r="N4" t="n">
-        <v>71.25808425420391</v>
+        <v>71.25808425420416</v>
       </c>
       <c r="O4" t="n">
-        <v>42.12146136543276</v>
+        <v>42.12146136543281</v>
       </c>
       <c r="P4" t="n">
-        <v>63.69041883789545</v>
+        <v>63.69041883789652</v>
       </c>
       <c r="Q4" t="n">
-        <v>109.5896973511764</v>
+        <v>109.5896973511769</v>
       </c>
       <c r="R4" t="n">
-        <v>119.5710179093631</v>
+        <v>119.5710179093625</v>
       </c>
       <c r="S4" t="n">
-        <v>119.0287277600539</v>
+        <v>119.0287277600535</v>
       </c>
       <c r="T4" t="n">
-        <v>67.12518504537132</v>
+        <v>67.12518504537124</v>
       </c>
       <c r="U4" t="n">
-        <v>57.46728526073904</v>
+        <v>57.46728526075054</v>
       </c>
       <c r="V4" t="n">
-        <v>50.69406404438421</v>
+        <v>50.69406404438676</v>
       </c>
       <c r="W4" t="n">
-        <v>41.1936911326556</v>
+        <v>41.19369113265481</v>
       </c>
       <c r="X4" t="n">
-        <v>116.5705421310873</v>
+        <v>116.5705421310897</v>
       </c>
       <c r="Y4" t="n">
         <v>62.64928088512006</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.23274551712774</v>
+        <v>39.23274551712768</v>
       </c>
       <c r="AA4" t="n">
-        <v>48.22393641779803</v>
+        <v>48.22393641779831</v>
       </c>
       <c r="AB4" t="n">
-        <v>135.3425727055481</v>
+        <v>135.3425727055473</v>
       </c>
     </row>
     <row r="5">
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.01951973006251</v>
+        <v>18.01951973006272</v>
       </c>
       <c r="C5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531431</v>
       </c>
       <c r="D5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531431</v>
       </c>
       <c r="E5" t="n">
-        <v>22.76957209125128</v>
+        <v>22.76957209125121</v>
       </c>
       <c r="F5" t="n">
-        <v>19.60231320977481</v>
+        <v>19.60231320977464</v>
       </c>
       <c r="G5" t="n">
-        <v>30.28613965293993</v>
+        <v>30.28613965293977</v>
       </c>
       <c r="H5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531429</v>
       </c>
       <c r="I5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531431</v>
       </c>
       <c r="J5" t="n">
-        <v>28.17321997097284</v>
+        <v>28.17321997097257</v>
       </c>
       <c r="K5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531431</v>
       </c>
       <c r="L5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531431</v>
       </c>
       <c r="M5" t="n">
-        <v>28.17941846526719</v>
+        <v>28.17941846526714</v>
       </c>
       <c r="N5" t="n">
-        <v>71.25808425420377</v>
+        <v>20.30379722729449</v>
       </c>
       <c r="O5" t="n">
-        <v>22.4680863172289</v>
+        <v>22.46808631722891</v>
       </c>
       <c r="P5" t="n">
-        <v>21.93756676575719</v>
+        <v>21.9375667657571</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.02286774498884</v>
+        <v>16.02286774498913</v>
       </c>
       <c r="R5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531429</v>
       </c>
       <c r="S5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531428</v>
       </c>
       <c r="T5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531431</v>
       </c>
       <c r="U5" t="n">
-        <v>23.15019888954982</v>
+        <v>23.15019888954981</v>
       </c>
       <c r="V5" t="n">
-        <v>25.28764021471644</v>
+        <v>25.28764021471645</v>
       </c>
       <c r="W5" t="n">
-        <v>28.18141515908187</v>
+        <v>28.1814151590817</v>
       </c>
       <c r="X5" t="n">
-        <v>16.95404264152155</v>
+        <v>16.95404264152132</v>
       </c>
       <c r="Y5" t="n">
-        <v>38.16089696762772</v>
+        <v>38.16089696762744</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.83079439653744</v>
+        <v>17.83079439653746</v>
       </c>
       <c r="AA5" t="n">
-        <v>28.17941846531448</v>
+        <v>28.17941846531429</v>
       </c>
       <c r="AB5" t="n">
-        <v>38.79228223464391</v>
+        <v>38.7922822346436</v>
       </c>
     </row>
     <row r="6">
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>484.2273864400573</v>
+        <v>484.2273864400564</v>
       </c>
       <c r="C6" t="n">
         <v>617.5816692093008</v>
@@ -7126,10 +7126,10 @@
         <v>586.8040459506499</v>
       </c>
       <c r="F6" t="n">
-        <v>310.1636494473997</v>
+        <v>310.1636494473999</v>
       </c>
       <c r="G6" t="n">
-        <v>617.5816708503266</v>
+        <v>617.5816708503276</v>
       </c>
       <c r="H6" t="n">
         <v>617.5816692093008</v>
@@ -7138,7 +7138,7 @@
         <v>617.5816692093008</v>
       </c>
       <c r="J6" t="n">
-        <v>617.5754707149581</v>
+        <v>617.5754707149586</v>
       </c>
       <c r="K6" t="n">
         <v>617.5816692093008</v>
@@ -7150,16 +7150,16 @@
         <v>617.5816692093008</v>
       </c>
       <c r="N6" t="n">
-        <v>71.25808425420391</v>
+        <v>617.5816692093008</v>
       </c>
       <c r="O6" t="n">
         <v>661.7751060913092</v>
       </c>
       <c r="P6" t="n">
-        <v>671.3864200245926</v>
+        <v>671.3864200245924</v>
       </c>
       <c r="Q6" t="n">
-        <v>617.5816708503266</v>
+        <v>617.5816708503276</v>
       </c>
       <c r="R6" t="n">
         <v>617.5816692093008</v>
@@ -7174,7 +7174,7 @@
         <v>617.5816692093008</v>
       </c>
       <c r="V6" t="n">
-        <v>771.4323064362595</v>
+        <v>771.4323064362598</v>
       </c>
       <c r="W6" t="n">
         <v>617.5816692093008</v>
@@ -7186,7 +7186,7 @@
         <v>617.5816692093008</v>
       </c>
       <c r="Z6" t="n">
-        <v>537.1808956765708</v>
+        <v>537.180895676571</v>
       </c>
       <c r="AA6" t="n">
         <v>617.5816692093008</v>
@@ -7202,85 +7202,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.557042099233002</v>
+        <v>5.557042099233091</v>
       </c>
       <c r="C7" t="n">
-        <v>5.658529632462065</v>
+        <v>5.658529632462061</v>
       </c>
       <c r="D7" t="n">
-        <v>6.424737398042627</v>
+        <v>6.424737398042629</v>
       </c>
       <c r="E7" t="n">
-        <v>4.945245591646159</v>
+        <v>4.945245591646236</v>
       </c>
       <c r="F7" t="n">
-        <v>4.635943631921488</v>
+        <v>4.635943631921755</v>
       </c>
       <c r="G7" t="n">
-        <v>3.77833180960823</v>
+        <v>3.778331809608017</v>
       </c>
       <c r="H7" t="n">
-        <v>6.299011828652105</v>
+        <v>6.299011828651982</v>
       </c>
       <c r="I7" t="n">
-        <v>3.870182900175815</v>
+        <v>3.870182900175836</v>
       </c>
       <c r="J7" t="n">
-        <v>4.723056236787742</v>
+        <v>4.723056236787897</v>
       </c>
       <c r="K7" t="n">
-        <v>3.679481530239595</v>
+        <v>3.679481530239382</v>
       </c>
       <c r="L7" t="n">
-        <v>4.866349148285537</v>
+        <v>4.866349148285548</v>
       </c>
       <c r="M7" t="n">
-        <v>3.179672731738917</v>
+        <v>3.179672731739042</v>
       </c>
       <c r="N7" t="n">
-        <v>5.491683413808288</v>
+        <v>5.491683413808307</v>
       </c>
       <c r="O7" t="n">
-        <v>6.003945428505436</v>
+        <v>6.003945428505724</v>
       </c>
       <c r="P7" t="n">
-        <v>5.533005794086646</v>
+        <v>5.533005794086799</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.631102130497566</v>
+        <v>4.631102130497351</v>
       </c>
       <c r="R7" t="n">
-        <v>4.607705395906917</v>
+        <v>4.607705395906769</v>
       </c>
       <c r="S7" t="n">
-        <v>4.094692353546215</v>
+        <v>4.094692353546481</v>
       </c>
       <c r="T7" t="n">
-        <v>5.622034584493175</v>
+        <v>5.62203458449322</v>
       </c>
       <c r="U7" t="n">
-        <v>5.722737777191821</v>
+        <v>5.722737777191512</v>
       </c>
       <c r="V7" t="n">
-        <v>4.105352359881389</v>
+        <v>4.105352359881441</v>
       </c>
       <c r="W7" t="n">
-        <v>6.115609081442727</v>
+        <v>6.115609081442733</v>
       </c>
       <c r="X7" t="n">
-        <v>4.559519113028861</v>
+        <v>4.559519113029103</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.640016488778298</v>
+        <v>5.640016488778389</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.097262522576702</v>
+        <v>6.097262522576825</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.963316244945485</v>
+        <v>5.963316244945779</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.338835943835982</v>
+        <v>4.338835943836247</v>
       </c>
     </row>
     <row r="8">
@@ -7290,85 +7290,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.438689084190476</v>
+        <v>6.438689084190542</v>
       </c>
       <c r="C8" t="n">
-        <v>6.470822657994601</v>
+        <v>6.47082265799479</v>
       </c>
       <c r="D8" t="n">
-        <v>6.688887452582368</v>
+        <v>6.688887452582487</v>
       </c>
       <c r="E8" t="n">
-        <v>6.77876048412102</v>
+        <v>6.778760484120895</v>
       </c>
       <c r="F8" t="n">
-        <v>6.182258292353644</v>
+        <v>6.182258292353253</v>
       </c>
       <c r="G8" t="n">
-        <v>5.928646460110191</v>
+        <v>5.928646460110241</v>
       </c>
       <c r="H8" t="n">
-        <v>6.653840982539889</v>
+        <v>6.653840982539991</v>
       </c>
       <c r="I8" t="n">
-        <v>5.963641083027448</v>
+        <v>5.963641083027502</v>
       </c>
       <c r="J8" t="n">
-        <v>6.17144165495064</v>
+        <v>6.171441654950499</v>
       </c>
       <c r="K8" t="n">
-        <v>5.907680477342878</v>
+        <v>5.907680477342999</v>
       </c>
       <c r="L8" t="n">
-        <v>6.242677622109328</v>
+        <v>6.24267762210909</v>
       </c>
       <c r="M8" t="n">
-        <v>5.768789788721725</v>
+        <v>5.768789788721673</v>
       </c>
       <c r="N8" t="n">
-        <v>6.42262455937331</v>
+        <v>6.422624559373131</v>
       </c>
       <c r="O8" t="n">
-        <v>6.566747687112132</v>
+        <v>6.566747687111731</v>
       </c>
       <c r="P8" t="n">
-        <v>6.431339644764325</v>
+        <v>6.431339644764418</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.178000510588011</v>
+        <v>6.17800051058803</v>
       </c>
       <c r="R8" t="n">
-        <v>6.173883545938173</v>
+        <v>6.173883545938168</v>
       </c>
       <c r="S8" t="n">
-        <v>6.020582054461628</v>
+        <v>6.020582054461564</v>
       </c>
       <c r="T8" t="n">
-        <v>6.460831311627754</v>
+        <v>6.460831311627908</v>
       </c>
       <c r="U8" t="n">
-        <v>6.487278929171361</v>
+        <v>6.487278929171421</v>
       </c>
       <c r="V8" t="n">
-        <v>4.837409273138288</v>
+        <v>4.837409273138303</v>
       </c>
       <c r="W8" t="n">
-        <v>6.600001167651038</v>
+        <v>6.600001167651006</v>
       </c>
       <c r="X8" t="n">
-        <v>6.158254040290493</v>
+        <v>6.158254040290735</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.464531825028864</v>
+        <v>6.464531825028791</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.593834529865911</v>
+        <v>6.593834529865944</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.556640178880483</v>
+        <v>6.556640178880818</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.096000854843025</v>
+        <v>6.096000854842725</v>
       </c>
     </row>
   </sheetData>
@@ -7534,85 +7534,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.203693779585333</v>
+        <v>9.203693779585487</v>
       </c>
       <c r="C2" t="n">
-        <v>9.318456914445289</v>
+        <v>9.318456914445242</v>
       </c>
       <c r="D2" t="n">
-        <v>9.003960261954408</v>
+        <v>9.003960261954536</v>
       </c>
       <c r="E2" t="n">
-        <v>9.458037993276587</v>
+        <v>9.458037993276479</v>
       </c>
       <c r="F2" t="n">
-        <v>9.61299717564234</v>
+        <v>9.612997175642342</v>
       </c>
       <c r="G2" t="n">
-        <v>9.210939752695486</v>
+        <v>9.210939752695554</v>
       </c>
       <c r="H2" t="n">
-        <v>8.82609786979828</v>
+        <v>8.826097869798414</v>
       </c>
       <c r="I2" t="n">
-        <v>9.356498593940881</v>
+        <v>9.356498593941053</v>
       </c>
       <c r="J2" t="n">
-        <v>9.10055465555118</v>
+        <v>9.100554655551075</v>
       </c>
       <c r="K2" t="n">
-        <v>9.298401997469902</v>
+        <v>9.298401997470041</v>
       </c>
       <c r="L2" t="n">
-        <v>9.650756537663787</v>
+        <v>9.650756537663943</v>
       </c>
       <c r="M2" t="n">
-        <v>9.017096331468403</v>
+        <v>9.017096331468288</v>
       </c>
       <c r="N2" t="n">
-        <v>8.993684592637873</v>
+        <v>8.993684592637932</v>
       </c>
       <c r="O2" t="n">
-        <v>8.854707223073165</v>
+        <v>8.854707223073286</v>
       </c>
       <c r="P2" t="n">
-        <v>8.96417009976715</v>
+        <v>8.96417009976739</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.361831949675253</v>
+        <v>9.361831949675286</v>
       </c>
       <c r="R2" t="n">
-        <v>9.652178905575729</v>
+        <v>9.652178905575839</v>
       </c>
       <c r="S2" t="n">
-        <v>9.42285118388779</v>
+        <v>9.422851183887969</v>
       </c>
       <c r="T2" t="n">
-        <v>9.128633504567414</v>
+        <v>9.128633504567084</v>
       </c>
       <c r="U2" t="n">
-        <v>8.88701168827126</v>
+        <v>8.88701168827105</v>
       </c>
       <c r="V2" t="n">
-        <v>7.294286591779849</v>
+        <v>7.294286591779846</v>
       </c>
       <c r="W2" t="n">
-        <v>9.097082315732198</v>
+        <v>9.097082315732321</v>
       </c>
       <c r="X2" t="n">
-        <v>9.173789945055272</v>
+        <v>9.173789945055365</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.153382492764486</v>
+        <v>9.153382492764432</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.996826554389367</v>
+        <v>8.996826554389498</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.938085794165481</v>
+        <v>8.938085794165536</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.168245663077572</v>
+        <v>9.168245663077624</v>
       </c>
     </row>
     <row r="3">
@@ -7622,85 +7622,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="C3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="D3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="E3" t="n">
-        <v>8.700414730010449</v>
+        <v>8.700414730010516</v>
       </c>
       <c r="F3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="G3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="H3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="I3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="J3" t="n">
-        <v>8.777914138558968</v>
+        <v>8.777914138558982</v>
       </c>
       <c r="K3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="L3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="M3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="N3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="O3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="P3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="R3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="S3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="T3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="U3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="V3" t="n">
-        <v>7.148003334530224</v>
+        <v>7.148003334530232</v>
       </c>
       <c r="W3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="X3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.823320131743733</v>
+        <v>8.823320131743534</v>
       </c>
     </row>
     <row r="4">
@@ -7710,85 +7710,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116.55005694839</v>
+        <v>116.5500569483898</v>
       </c>
       <c r="C4" t="n">
-        <v>149.7176384778714</v>
+        <v>149.717638477872</v>
       </c>
       <c r="D4" t="n">
-        <v>75.80602862574467</v>
+        <v>75.8060286257453</v>
       </c>
       <c r="E4" t="n">
-        <v>219.8745433959276</v>
+        <v>219.874543395928</v>
       </c>
       <c r="F4" t="n">
-        <v>230.3688047335889</v>
+        <v>230.3688047335896</v>
       </c>
       <c r="G4" t="n">
-        <v>111.500985996393</v>
+        <v>111.5009859963936</v>
       </c>
       <c r="H4" t="n">
-        <v>32.00323843557621</v>
+        <v>32.00323843557647</v>
       </c>
       <c r="I4" t="n">
-        <v>171.7661479241818</v>
+        <v>171.7661479241821</v>
       </c>
       <c r="J4" t="n">
-        <v>103.1156583133155</v>
+        <v>103.1156583133157</v>
       </c>
       <c r="K4" t="n">
-        <v>136.4579252591882</v>
+        <v>136.4579252591877</v>
       </c>
       <c r="L4" t="n">
-        <v>214.9008836714526</v>
+        <v>214.9008836714528</v>
       </c>
       <c r="M4" t="n">
-        <v>75.61290045087308</v>
+        <v>75.6129004508727</v>
       </c>
       <c r="N4" t="n">
-        <v>73.3950794550493</v>
+        <v>73.39507945505002</v>
       </c>
       <c r="O4" t="n">
-        <v>34.01722773294244</v>
+        <v>34.01722773294235</v>
       </c>
       <c r="P4" t="n">
-        <v>59.9467501296776</v>
+        <v>59.94675012967729</v>
       </c>
       <c r="Q4" t="n">
         <v>153.0284211495644</v>
       </c>
       <c r="R4" t="n">
-        <v>254.3736953298471</v>
+        <v>254.3736953298481</v>
       </c>
       <c r="S4" t="n">
-        <v>159.2216280038159</v>
+        <v>159.2216280038163</v>
       </c>
       <c r="T4" t="n">
-        <v>109.561487407136</v>
+        <v>109.5614874071357</v>
       </c>
       <c r="U4" t="n">
-        <v>42.50995556726158</v>
+        <v>42.50995556726208</v>
       </c>
       <c r="V4" t="n">
-        <v>54.27266386070327</v>
+        <v>54.27266386070316</v>
       </c>
       <c r="W4" t="n">
-        <v>98.40413120172755</v>
+        <v>98.40413120172695</v>
       </c>
       <c r="X4" t="n">
-        <v>117.1723607140705</v>
+        <v>117.17236071407</v>
       </c>
       <c r="Y4" t="n">
-        <v>111.5031354261811</v>
+        <v>111.5031354261809</v>
       </c>
       <c r="Z4" t="n">
-        <v>65.20359159001372</v>
+        <v>65.20359159001433</v>
       </c>
       <c r="AA4" t="n">
-        <v>58.11303414706905</v>
+        <v>58.1130341470697</v>
       </c>
       <c r="AB4" t="n">
-        <v>124.2031251090076</v>
+        <v>124.2031251090084</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.03196694504979</v>
+        <v>20.03196694505014</v>
       </c>
       <c r="C5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903477</v>
       </c>
       <c r="D5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903477</v>
       </c>
       <c r="E5" t="n">
-        <v>25.20607291632615</v>
+        <v>25.20607291632638</v>
       </c>
       <c r="F5" t="n">
-        <v>21.75606187289387</v>
+        <v>21.75606187289383</v>
       </c>
       <c r="G5" t="n">
-        <v>33.393670463991</v>
+        <v>33.39367046399084</v>
       </c>
       <c r="H5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903477</v>
       </c>
       <c r="I5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903477</v>
       </c>
       <c r="J5" t="n">
-        <v>31.09131921927039</v>
+        <v>31.09131921927043</v>
       </c>
       <c r="K5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903477</v>
       </c>
       <c r="L5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903481</v>
       </c>
       <c r="M5" t="n">
-        <v>31.09887498894284</v>
+        <v>31.09887498894345</v>
       </c>
       <c r="N5" t="n">
-        <v>73.3950794550493</v>
+        <v>22.52016979338144</v>
       </c>
       <c r="O5" t="n">
-        <v>24.87767245131572</v>
+        <v>24.87767245131555</v>
       </c>
       <c r="P5" t="n">
-        <v>24.29979158656054</v>
+        <v>24.29979158656075</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.85706693402093</v>
+        <v>17.85706693402105</v>
       </c>
       <c r="R5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903477</v>
       </c>
       <c r="S5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903477</v>
       </c>
       <c r="T5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903477</v>
       </c>
       <c r="U5" t="n">
-        <v>25.61389298657147</v>
+        <v>25.61389298657171</v>
       </c>
       <c r="V5" t="n">
-        <v>27.9364525686248</v>
+        <v>27.93645256862479</v>
       </c>
       <c r="W5" t="n">
-        <v>31.1010499201199</v>
+        <v>31.10104992012069</v>
       </c>
       <c r="X5" t="n">
-        <v>18.87137102591322</v>
+        <v>18.87137102591312</v>
       </c>
       <c r="Y5" t="n">
-        <v>41.95982472712682</v>
+        <v>41.95982472712648</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.82639344956301</v>
+        <v>19.82639344956366</v>
       </c>
       <c r="AA5" t="n">
-        <v>31.09887498903425</v>
+        <v>31.09887498903477</v>
       </c>
       <c r="AB5" t="n">
-        <v>42.65918580883255</v>
+        <v>42.65918580883289</v>
       </c>
     </row>
     <row r="6">
@@ -7886,85 +7886,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>453.23616792798</v>
+        <v>453.2361679279801</v>
       </c>
       <c r="C6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="D6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="E6" t="n">
-        <v>549.0957126047333</v>
+        <v>549.0957126047329</v>
       </c>
       <c r="F6" t="n">
         <v>290.5707950014336</v>
       </c>
       <c r="G6" t="n">
-        <v>577.8579000574275</v>
+        <v>577.857900057428</v>
       </c>
       <c r="H6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="I6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="J6" t="n">
         <v>577.8503397907878</v>
       </c>
       <c r="K6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="L6" t="n">
         <v>577.8578955605524</v>
       </c>
       <c r="M6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="N6" t="n">
-        <v>73.3950794550493</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="O6" t="n">
-        <v>619.1573789068501</v>
+        <v>619.1573789068503</v>
       </c>
       <c r="P6" t="n">
-        <v>628.1393069768984</v>
+        <v>628.1393069768982</v>
       </c>
       <c r="Q6" t="n">
-        <v>577.8579000574275</v>
+        <v>577.857900057428</v>
       </c>
       <c r="R6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="S6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="T6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="U6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="V6" t="n">
         <v>721.6230170303123</v>
       </c>
       <c r="W6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="X6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="Y6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="Z6" t="n">
-        <v>502.7220773801626</v>
+        <v>502.7220773801625</v>
       </c>
       <c r="AA6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
       <c r="AB6" t="n">
-        <v>577.8578955605522</v>
+        <v>577.8578955605523</v>
       </c>
     </row>
     <row r="7">
@@ -7974,85 +7974,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.021176058306114</v>
+        <v>6.021176058306213</v>
       </c>
       <c r="C7" t="n">
-        <v>5.388230424386247</v>
+        <v>5.388230424386272</v>
       </c>
       <c r="D7" t="n">
-        <v>7.234390907386789</v>
+        <v>7.23439090738677</v>
       </c>
       <c r="E7" t="n">
-        <v>3.686238831271278</v>
+        <v>3.686238831271403</v>
       </c>
       <c r="F7" t="n">
-        <v>3.692133703952341</v>
+        <v>3.692133703952122</v>
       </c>
       <c r="G7" t="n">
-        <v>5.979654445504898</v>
+        <v>5.979654445504815</v>
       </c>
       <c r="H7" t="n">
-        <v>8.279963274596275</v>
+        <v>8.279963274596</v>
       </c>
       <c r="I7" t="n">
-        <v>5.176239115099867</v>
+        <v>5.176239115099885</v>
       </c>
       <c r="J7" t="n">
-        <v>6.335840969880694</v>
+        <v>6.335840969880756</v>
       </c>
       <c r="K7" t="n">
-        <v>5.504982060133797</v>
+        <v>5.504982060133625</v>
       </c>
       <c r="L7" t="n">
-        <v>3.395840588180209</v>
+        <v>3.395840588180087</v>
       </c>
       <c r="M7" t="n">
-        <v>7.163793617279572</v>
+        <v>7.163793617279637</v>
       </c>
       <c r="N7" t="n">
-        <v>7.288084900090102</v>
+        <v>7.288084900090118</v>
       </c>
       <c r="O7" t="n">
-        <v>8.096559292782661</v>
+        <v>8.096559292782787</v>
       </c>
       <c r="P7" t="n">
-        <v>7.443406159856548</v>
+        <v>7.443406159856797</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.128705540468397</v>
+        <v>5.128705540468614</v>
       </c>
       <c r="R7" t="n">
-        <v>3.458678722938926</v>
+        <v>3.458678722939194</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7300685696242</v>
+        <v>4.730068569624116</v>
       </c>
       <c r="T7" t="n">
-        <v>6.50559047863434</v>
+        <v>6.5055904786342</v>
       </c>
       <c r="U7" t="n">
-        <v>7.910059749639488</v>
+        <v>7.910059749639347</v>
       </c>
       <c r="V7" t="n">
-        <v>5.882513310039567</v>
+        <v>5.882513310039569</v>
       </c>
       <c r="W7" t="n">
-        <v>6.67267882574164</v>
+        <v>6.672678825741309</v>
       </c>
       <c r="X7" t="n">
-        <v>6.237115036181796</v>
+        <v>6.237115036181733</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.344417094816592</v>
+        <v>6.344417094816578</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.253613712542742</v>
+        <v>7.253613712542839</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.612064099149401</v>
+        <v>7.612064099149548</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.272665066130759</v>
+        <v>6.272665066130553</v>
       </c>
     </row>
     <row r="8">
@@ -8062,85 +8062,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.928709296268261</v>
+        <v>7.928709296268181</v>
       </c>
       <c r="C8" t="n">
-        <v>7.755480150616226</v>
+        <v>7.755480150616327</v>
       </c>
       <c r="D8" t="n">
-        <v>8.280992401255038</v>
+        <v>8.280992401255215</v>
       </c>
       <c r="E8" t="n">
-        <v>7.176571980119692</v>
+        <v>7.176571980119701</v>
       </c>
       <c r="F8" t="n">
-        <v>7.278290998876283</v>
+        <v>7.278290998876344</v>
       </c>
       <c r="G8" t="n">
-        <v>7.917062803231957</v>
+        <v>7.917062803232093</v>
       </c>
       <c r="H8" t="n">
-        <v>8.578868768220939</v>
+        <v>8.578868768220731</v>
       </c>
       <c r="I8" t="n">
-        <v>7.697065108810795</v>
+        <v>7.697065108810614</v>
       </c>
       <c r="J8" t="n">
-        <v>7.989403581376692</v>
+        <v>7.989403581377051</v>
       </c>
       <c r="K8" t="n">
-        <v>7.788547599971679</v>
+        <v>7.788547599971553</v>
       </c>
       <c r="L8" t="n">
-        <v>7.181236048991476</v>
+        <v>7.181236048991535</v>
       </c>
       <c r="M8" t="n">
-        <v>8.262006478790068</v>
+        <v>8.262006478790015</v>
       </c>
       <c r="N8" t="n">
-        <v>8.295147669731337</v>
+        <v>8.295147669731234</v>
       </c>
       <c r="O8" t="n">
-        <v>8.52402872529629</v>
+        <v>8.524028725296777</v>
       </c>
       <c r="P8" t="n">
-        <v>8.336304845034162</v>
+        <v>8.336304845034032</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.680770536606477</v>
+        <v>7.680770536607105</v>
       </c>
       <c r="R8" t="n">
-        <v>7.211249968472059</v>
+        <v>7.211249968472077</v>
       </c>
       <c r="S8" t="n">
-        <v>7.560408678705068</v>
+        <v>7.560408678704889</v>
       </c>
       <c r="T8" t="n">
-        <v>8.074059126236419</v>
+        <v>8.074059126236182</v>
       </c>
       <c r="U8" t="n">
-        <v>8.471475304025647</v>
+        <v>8.471475304025486</v>
       </c>
       <c r="V8" t="n">
-        <v>6.718484597759175</v>
+        <v>6.718484597759176</v>
       </c>
       <c r="W8" t="n">
-        <v>8.118533667813622</v>
+        <v>8.118533667814134</v>
       </c>
       <c r="X8" t="n">
-        <v>7.997058384828383</v>
+        <v>7.99705838482812</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.025473711167869</v>
+        <v>8.02547371116742</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.282605131296085</v>
+        <v>8.282605131295639</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.386960439291089</v>
+        <v>8.386960439291334</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.007689479768239</v>
+        <v>8.007689479768318</v>
       </c>
     </row>
   </sheetData>
